--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="F14" t="n">
-        <v>7.78</v>
+        <v>7.6</v>
       </c>
       <c r="G14" t="n">
-        <v>126.8</v>
+        <v>108.3</v>
       </c>
       <c r="H14" t="n">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>-38.22</v>
       </c>
       <c r="K14" t="n">
-        <v>-44.25</v>
+        <v>58.07</v>
       </c>
       <c r="L14" t="n">
-        <v>53.46</v>
+        <v>69.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:33</t>
+          <t>06:39:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,28 +667,28 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="F15" t="n">
-        <v>7.85</v>
+        <v>7.71</v>
       </c>
       <c r="G15" t="n">
-        <v>117.5</v>
+        <v>107.9</v>
       </c>
       <c r="H15" t="n">
-        <v>17.3</v>
+        <v>23.1</v>
       </c>
       <c r="I15" t="n">
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-55.05</v>
+        <v>-68.31</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.82</v>
+        <v>129.87</v>
       </c>
       <c r="L15" t="n">
-        <v>56.3</v>
+        <v>146.74</v>
       </c>
     </row>
     <row r="16">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="F16" t="n">
-        <v>7.77</v>
+        <v>7.4</v>
       </c>
       <c r="G16" t="n">
-        <v>111.8</v>
+        <v>101.4</v>
       </c>
       <c r="H16" t="n">
-        <v>24.7</v>
+        <v>30.7</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>77.72</v>
+        <v>36.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-124.75</v>
+        <v>78.77</v>
       </c>
       <c r="L16" t="n">
-        <v>146.98</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:44:55</t>
+          <t>06:46:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.57</v>
+        <v>2.48</v>
       </c>
       <c r="F17" t="n">
         <v>7.59</v>
       </c>
       <c r="G17" t="n">
-        <v>116.6</v>
+        <v>115.8</v>
       </c>
       <c r="H17" t="n">
-        <v>20.7</v>
+        <v>23.1</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>20.74</v>
+        <v>82.31</v>
       </c>
       <c r="K17" t="n">
-        <v>-48.81</v>
+        <v>179.55</v>
       </c>
       <c r="L17" t="n">
-        <v>53.03</v>
+        <v>197.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:49</t>
+          <t>06:47:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="F18" t="n">
-        <v>7.61</v>
+        <v>7.67</v>
       </c>
       <c r="G18" t="n">
-        <v>108.3</v>
+        <v>113.9</v>
       </c>
       <c r="H18" t="n">
-        <v>27.1</v>
+        <v>30.8</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>120.13</v>
+        <v>41.26</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.62</v>
+        <v>287.7</v>
       </c>
       <c r="L18" t="n">
-        <v>120.69</v>
+        <v>290.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:48:08</t>
+          <t>06:49:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
+        <v>7.46</v>
       </c>
       <c r="G19" t="n">
-        <v>109.7</v>
+        <v>107</v>
       </c>
       <c r="H19" t="n">
-        <v>24.7</v>
+        <v>26.7</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>31.69</v>
+        <v>-98.95999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-45.12</v>
+        <v>-68.89</v>
       </c>
       <c r="L19" t="n">
-        <v>55.13</v>
+        <v>120.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:51:54</t>
+          <t>06:55:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="F20" t="n">
-        <v>8.279999999999999</v>
+        <v>7.18</v>
       </c>
       <c r="G20" t="n">
-        <v>118.7</v>
+        <v>110.4</v>
       </c>
       <c r="H20" t="n">
-        <v>27.1</v>
+        <v>25.2</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.28</v>
+        <v>197.87</v>
       </c>
       <c r="K20" t="n">
-        <v>232.23</v>
+        <v>203.66</v>
       </c>
       <c r="L20" t="n">
-        <v>232.27</v>
+        <v>283.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:53:38</t>
+          <t>06:57:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.42</v>
+        <v>3.22</v>
       </c>
       <c r="F21" t="n">
-        <v>7.79</v>
+        <v>7.31</v>
       </c>
       <c r="G21" t="n">
-        <v>90.59999999999999</v>
+        <v>114.1</v>
       </c>
       <c r="H21" t="n">
-        <v>31.4</v>
+        <v>26.2</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-200.09</v>
+        <v>-131.57</v>
       </c>
       <c r="K21" t="n">
-        <v>-77.76000000000001</v>
+        <v>63.76</v>
       </c>
       <c r="L21" t="n">
-        <v>214.67</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:55:29</t>
+          <t>06:58:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.28</v>
+        <v>2.42</v>
       </c>
       <c r="F22" t="n">
-        <v>7.7</v>
+        <v>8.16</v>
       </c>
       <c r="G22" t="n">
-        <v>128.7</v>
+        <v>109.8</v>
       </c>
       <c r="H22" t="n">
-        <v>25.5</v>
+        <v>20.8</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-282.72</v>
+        <v>92.09</v>
       </c>
       <c r="K22" t="n">
-        <v>124.73</v>
+        <v>78.16</v>
       </c>
       <c r="L22" t="n">
-        <v>309.01</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:59:10</t>
+          <t>07:03:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="F23" t="n">
-        <v>8.31</v>
+        <v>7.98</v>
       </c>
       <c r="G23" t="n">
-        <v>112</v>
+        <v>115.4</v>
       </c>
       <c r="H23" t="n">
-        <v>23.8</v>
+        <v>25.6</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-280.75</v>
+        <v>28.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-382.03</v>
+        <v>468.69</v>
       </c>
       <c r="L23" t="n">
-        <v>474.1</v>
+        <v>469.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:01:27</t>
+          <t>07:04:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="F24" t="n">
-        <v>7.54</v>
+        <v>7.74</v>
       </c>
       <c r="G24" t="n">
-        <v>116.9</v>
+        <v>107.3</v>
       </c>
       <c r="H24" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>132.37</v>
+        <v>-112.52</v>
       </c>
       <c r="K24" t="n">
-        <v>234.05</v>
+        <v>-188.13</v>
       </c>
       <c r="L24" t="n">
-        <v>268.89</v>
+        <v>219.21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:02:58</t>
+          <t>07:06:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="F25" t="n">
-        <v>6.86</v>
+        <v>7.76</v>
       </c>
       <c r="G25" t="n">
-        <v>102</v>
+        <v>105.5</v>
       </c>
       <c r="H25" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>107.86</v>
+        <v>205.74</v>
       </c>
       <c r="K25" t="n">
-        <v>56.83</v>
+        <v>-44.15</v>
       </c>
       <c r="L25" t="n">
-        <v>121.92</v>
+        <v>210.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:08:35</t>
+          <t>07:11:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="F26" t="n">
-        <v>8.5</v>
+        <v>7.57</v>
       </c>
       <c r="G26" t="n">
-        <v>95.8</v>
+        <v>109.6</v>
       </c>
       <c r="H26" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I26" t="n">
         <v>21</v>
       </c>
-      <c r="I26" t="n">
-        <v>23</v>
-      </c>
       <c r="J26" t="n">
-        <v>328.78</v>
+        <v>-228.23</v>
       </c>
       <c r="K26" t="n">
-        <v>33.28</v>
+        <v>341.92</v>
       </c>
       <c r="L26" t="n">
-        <v>330.46</v>
+        <v>411.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:11:22</t>
+          <t>07:13:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="F27" t="n">
-        <v>8.449999999999999</v>
+        <v>7.28</v>
       </c>
       <c r="G27" t="n">
-        <v>116.4</v>
+        <v>110.5</v>
       </c>
       <c r="H27" t="n">
-        <v>23.4</v>
+        <v>20.5</v>
       </c>
       <c r="I27" t="n">
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-53.3</v>
+        <v>164.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-646.4</v>
+        <v>0.2</v>
       </c>
       <c r="L27" t="n">
-        <v>648.6</v>
+        <v>164.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:12:36</t>
+          <t>07:14:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="F28" t="n">
-        <v>8.15</v>
+        <v>7.04</v>
       </c>
       <c r="G28" t="n">
-        <v>110.6</v>
+        <v>113.9</v>
       </c>
       <c r="H28" t="n">
-        <v>21.7</v>
+        <v>25.1</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-238.87</v>
+        <v>212.44</v>
       </c>
       <c r="K28" t="n">
-        <v>-37.67</v>
+        <v>354.4</v>
       </c>
       <c r="L28" t="n">
-        <v>241.82</v>
+        <v>413.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:22:27</t>
+          <t>07:24:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="F29" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>106.3</v>
+        <v>112.2</v>
       </c>
       <c r="H29" t="n">
-        <v>28.2</v>
+        <v>30.6</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.31</v>
+        <v>-45.64</v>
       </c>
       <c r="K29" t="n">
-        <v>-28.79</v>
+        <v>110.2</v>
       </c>
       <c r="L29" t="n">
-        <v>41.8</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:25:18</t>
+          <t>07:25:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="F30" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>117.6</v>
+        <v>117.4</v>
       </c>
       <c r="H30" t="n">
-        <v>20.7</v>
+        <v>29.1</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>83.56999999999999</v>
+        <v>-79.89</v>
       </c>
       <c r="K30" t="n">
-        <v>22.16</v>
+        <v>-136.2</v>
       </c>
       <c r="L30" t="n">
-        <v>86.45999999999999</v>
+        <v>157.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:27:11</t>
+          <t>07:27:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="F31" t="n">
-        <v>8.02</v>
+        <v>8.09</v>
       </c>
       <c r="G31" t="n">
-        <v>115.8</v>
+        <v>107.8</v>
       </c>
       <c r="H31" t="n">
-        <v>32</v>
+        <v>24.8</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>34.83</v>
+        <v>-36.09</v>
       </c>
       <c r="K31" t="n">
-        <v>68.62</v>
+        <v>134.44</v>
       </c>
       <c r="L31" t="n">
-        <v>76.95</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:32:55</t>
+          <t>07:30:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="F32" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="G32" t="n">
-        <v>105.6</v>
+        <v>112.2</v>
       </c>
       <c r="H32" t="n">
-        <v>17.6</v>
+        <v>22.9</v>
       </c>
       <c r="I32" t="n">
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-134.41</v>
+        <v>182.42</v>
       </c>
       <c r="K32" t="n">
-        <v>170.37</v>
+        <v>4.56</v>
       </c>
       <c r="L32" t="n">
-        <v>217.01</v>
+        <v>182.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:34:51</t>
+          <t>07:32:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="F33" t="n">
-        <v>8.140000000000001</v>
+        <v>7.26</v>
       </c>
       <c r="G33" t="n">
-        <v>123.3</v>
+        <v>107</v>
       </c>
       <c r="H33" t="n">
-        <v>16.7</v>
+        <v>22.7</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>6.09</v>
+        <v>-166.17</v>
       </c>
       <c r="K33" t="n">
-        <v>43.36</v>
+        <v>52.5</v>
       </c>
       <c r="L33" t="n">
-        <v>43.79</v>
+        <v>174.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:37:04</t>
+          <t>07:34:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="F34" t="n">
-        <v>7.97</v>
+        <v>7.94</v>
       </c>
       <c r="G34" t="n">
-        <v>111.5</v>
+        <v>110.7</v>
       </c>
       <c r="H34" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>3.24</v>
+        <v>155.99</v>
       </c>
       <c r="K34" t="n">
-        <v>33.19</v>
+        <v>-158.97</v>
       </c>
       <c r="L34" t="n">
-        <v>33.35</v>
+        <v>222.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:42:22</t>
+          <t>07:39:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="F35" t="n">
-        <v>7.75</v>
+        <v>7.31</v>
       </c>
       <c r="G35" t="n">
-        <v>118</v>
+        <v>105.4</v>
       </c>
       <c r="H35" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>38.61</v>
+        <v>135.02</v>
       </c>
       <c r="K35" t="n">
-        <v>2.98</v>
+        <v>-239.17</v>
       </c>
       <c r="L35" t="n">
-        <v>38.72</v>
+        <v>274.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:43:28</t>
+          <t>07:40:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="F36" t="n">
-        <v>7.02</v>
+        <v>7.73</v>
       </c>
       <c r="G36" t="n">
-        <v>112.3</v>
+        <v>113.8</v>
       </c>
       <c r="H36" t="n">
-        <v>19.7</v>
+        <v>15.3</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>99.40000000000001</v>
+        <v>275.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-224.84</v>
+        <v>-285.4</v>
       </c>
       <c r="L36" t="n">
-        <v>245.83</v>
+        <v>396.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:45:48</t>
+          <t>07:41:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.73</v>
+        <v>2.11</v>
       </c>
       <c r="F37" t="n">
-        <v>7.34</v>
+        <v>7.72</v>
       </c>
       <c r="G37" t="n">
-        <v>108.9</v>
+        <v>114.6</v>
       </c>
       <c r="H37" t="n">
         <v>22.4</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>104.34</v>
+        <v>75.37</v>
       </c>
       <c r="K37" t="n">
-        <v>-91.52</v>
+        <v>-76.75</v>
       </c>
       <c r="L37" t="n">
-        <v>138.79</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:51:16</t>
+          <t>07:47:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>7.72</v>
+        <v>7.76</v>
       </c>
       <c r="G38" t="n">
-        <v>110.6</v>
+        <v>84.5</v>
       </c>
       <c r="H38" t="n">
-        <v>29.1</v>
+        <v>18.8</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.01</v>
+        <v>414.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-18.71</v>
+        <v>175.79</v>
       </c>
       <c r="L38" t="n">
-        <v>20.77</v>
+        <v>449.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:53:31</t>
+          <t>07:49:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="F39" t="n">
-        <v>8.6</v>
+        <v>7.79</v>
       </c>
       <c r="G39" t="n">
-        <v>96.40000000000001</v>
+        <v>117.5</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-90.83</v>
+        <v>55.51</v>
       </c>
       <c r="K39" t="n">
-        <v>319.07</v>
+        <v>-268.59</v>
       </c>
       <c r="L39" t="n">
-        <v>331.75</v>
+        <v>274.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:55:47</t>
+          <t>07:51:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="F40" t="n">
-        <v>8.470000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="G40" t="n">
-        <v>104.5</v>
+        <v>114.3</v>
       </c>
       <c r="H40" t="n">
-        <v>26.7</v>
+        <v>25.6</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>148.64</v>
+        <v>-44.51</v>
       </c>
       <c r="K40" t="n">
-        <v>291.04</v>
+        <v>-262.42</v>
       </c>
       <c r="L40" t="n">
-        <v>326.8</v>
+        <v>266.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:00:52</t>
+          <t>07:55:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="F41" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="G41" t="n">
-        <v>104.6</v>
+        <v>117.6</v>
       </c>
       <c r="H41" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>139.72</v>
+        <v>-32.2</v>
       </c>
       <c r="K41" t="n">
-        <v>258.3</v>
+        <v>-100.35</v>
       </c>
       <c r="L41" t="n">
-        <v>293.67</v>
+        <v>105.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:01:59</t>
+          <t>07:58:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="F42" t="n">
-        <v>7.52</v>
+        <v>7.28</v>
       </c>
       <c r="G42" t="n">
-        <v>107.8</v>
+        <v>93.8</v>
       </c>
       <c r="H42" t="n">
-        <v>27.9</v>
+        <v>28.9</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>74.41</v>
+        <v>235.19</v>
       </c>
       <c r="K42" t="n">
-        <v>-458.19</v>
+        <v>793.05</v>
       </c>
       <c r="L42" t="n">
-        <v>464.19</v>
+        <v>827.1900000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:03:16</t>
+          <t>07:59:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="F43" t="n">
-        <v>7.29</v>
+        <v>7.62</v>
       </c>
       <c r="G43" t="n">
-        <v>115.1</v>
+        <v>102.8</v>
       </c>
       <c r="H43" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>131.2</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>487.41</v>
+        <v>-332.98</v>
       </c>
       <c r="L43" t="n">
-        <v>504.75</v>
+        <v>344.59</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:12:38</t>
+          <t>08:09:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1888,31 +1888,31 @@
         <v>2.65</v>
       </c>
       <c r="F44" t="n">
-        <v>7.61</v>
+        <v>6.96</v>
       </c>
       <c r="G44" t="n">
-        <v>110.6</v>
+        <v>121.7</v>
       </c>
       <c r="H44" t="n">
-        <v>25.9</v>
+        <v>28.8</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-82.14</v>
+        <v>-91.3</v>
       </c>
       <c r="K44" t="n">
-        <v>28.42</v>
+        <v>6.31</v>
       </c>
       <c r="L44" t="n">
-        <v>86.91</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:14:42</t>
+          <t>08:11:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="F45" t="n">
-        <v>7.36</v>
+        <v>7.65</v>
       </c>
       <c r="G45" t="n">
-        <v>108.2</v>
+        <v>106.1</v>
       </c>
       <c r="H45" t="n">
-        <v>26.2</v>
+        <v>24.3</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>123.64</v>
+        <v>-18.59</v>
       </c>
       <c r="K45" t="n">
-        <v>33.93</v>
+        <v>-208.07</v>
       </c>
       <c r="L45" t="n">
-        <v>128.21</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:15:41</t>
+          <t>08:12:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="F46" t="n">
-        <v>7.65</v>
+        <v>7.4</v>
       </c>
       <c r="G46" t="n">
-        <v>110.6</v>
+        <v>95.8</v>
       </c>
       <c r="H46" t="n">
-        <v>19.3</v>
+        <v>22.8</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-97.42</v>
+        <v>-4.61</v>
       </c>
       <c r="K46" t="n">
-        <v>99.87</v>
+        <v>61.54</v>
       </c>
       <c r="L46" t="n">
-        <v>139.51</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:19:41</t>
+          <t>08:16:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.44</v>
+        <v>3.13</v>
       </c>
       <c r="F47" t="n">
-        <v>7.65</v>
+        <v>7.15</v>
       </c>
       <c r="G47" t="n">
-        <v>117.7</v>
+        <v>121.1</v>
       </c>
       <c r="H47" t="n">
-        <v>24.7</v>
+        <v>27.6</v>
       </c>
       <c r="I47" t="n">
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>282.3</v>
+        <v>-198.94</v>
       </c>
       <c r="K47" t="n">
-        <v>72.53</v>
+        <v>-83.76000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>291.47</v>
+        <v>215.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:22:11</t>
+          <t>08:17:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="F48" t="n">
-        <v>6.96</v>
+        <v>7.62</v>
       </c>
       <c r="G48" t="n">
-        <v>109.2</v>
+        <v>113</v>
       </c>
       <c r="H48" t="n">
-        <v>23.6</v>
+        <v>28.5</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>126.08</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>86.40000000000001</v>
+        <v>173.13</v>
       </c>
       <c r="L48" t="n">
-        <v>152.84</v>
+        <v>184.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:24:21</t>
+          <t>08:19:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="F49" t="n">
-        <v>7.67</v>
+        <v>7.12</v>
       </c>
       <c r="G49" t="n">
-        <v>125.2</v>
+        <v>107.8</v>
       </c>
       <c r="H49" t="n">
-        <v>26.5</v>
+        <v>25.4</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>68.78</v>
+        <v>201.48</v>
       </c>
       <c r="K49" t="n">
-        <v>56.83</v>
+        <v>-6.31</v>
       </c>
       <c r="L49" t="n">
-        <v>89.22</v>
+        <v>201.58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:28:48</t>
+          <t>08:24:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>7.51</v>
       </c>
       <c r="G50" t="n">
-        <v>106.4</v>
+        <v>111.4</v>
       </c>
       <c r="H50" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-124.84</v>
+        <v>139.05</v>
       </c>
       <c r="K50" t="n">
-        <v>69.61</v>
+        <v>115.63</v>
       </c>
       <c r="L50" t="n">
-        <v>142.93</v>
+        <v>180.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:30:14</t>
+          <t>08:26:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="F51" t="n">
-        <v>7.55</v>
+        <v>7.3</v>
       </c>
       <c r="G51" t="n">
-        <v>113.2</v>
+        <v>104</v>
       </c>
       <c r="H51" t="n">
-        <v>23.7</v>
+        <v>29.3</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-131.73</v>
+        <v>-370.91</v>
       </c>
       <c r="K51" t="n">
-        <v>-88.14</v>
+        <v>-52.16</v>
       </c>
       <c r="L51" t="n">
-        <v>158.5</v>
+        <v>374.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:31:48</t>
+          <t>08:27:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.58</v>
+        <v>2.89</v>
       </c>
       <c r="F52" t="n">
-        <v>8.23</v>
+        <v>7.96</v>
       </c>
       <c r="G52" t="n">
-        <v>102.4</v>
+        <v>120.1</v>
       </c>
       <c r="H52" t="n">
-        <v>16.6</v>
+        <v>30.3</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-17.02</v>
+        <v>301.66</v>
       </c>
       <c r="K52" t="n">
-        <v>-190.62</v>
+        <v>-55.05</v>
       </c>
       <c r="L52" t="n">
-        <v>191.38</v>
+        <v>306.65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:35:34</t>
+          <t>08:32:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.63</v>
+        <v>3.16</v>
       </c>
       <c r="F53" t="n">
-        <v>7.47</v>
+        <v>6.95</v>
       </c>
       <c r="G53" t="n">
-        <v>106.6</v>
+        <v>102.4</v>
       </c>
       <c r="H53" t="n">
-        <v>31.8</v>
+        <v>25.3</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-6.27</v>
+        <v>50.32</v>
       </c>
       <c r="K53" t="n">
-        <v>-464.08</v>
+        <v>815.97</v>
       </c>
       <c r="L53" t="n">
-        <v>464.12</v>
+        <v>817.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:37:08</t>
+          <t>08:34:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="F54" t="n">
-        <v>7.9</v>
+        <v>6.96</v>
       </c>
       <c r="G54" t="n">
-        <v>105.9</v>
+        <v>98.5</v>
       </c>
       <c r="H54" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>128.1</v>
+        <v>88.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-97.59</v>
+        <v>-252.32</v>
       </c>
       <c r="L54" t="n">
-        <v>161.04</v>
+        <v>267.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:38:05</t>
+          <t>08:36:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="F55" t="n">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="G55" t="n">
-        <v>107.5</v>
+        <v>107.7</v>
       </c>
       <c r="H55" t="n">
-        <v>17.5</v>
+        <v>23.1</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-559.21</v>
+        <v>-23.45</v>
       </c>
       <c r="K55" t="n">
-        <v>-221.12</v>
+        <v>-232.47</v>
       </c>
       <c r="L55" t="n">
-        <v>601.34</v>
+        <v>233.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:43:42</t>
+          <t>08:40:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="F56" t="n">
-        <v>7.94</v>
+        <v>7.7</v>
       </c>
       <c r="G56" t="n">
-        <v>104</v>
+        <v>91.8</v>
       </c>
       <c r="H56" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>595.22</v>
+        <v>41.37</v>
       </c>
       <c r="K56" t="n">
-        <v>201.1</v>
+        <v>-143.14</v>
       </c>
       <c r="L56" t="n">
-        <v>628.27</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:45:39</t>
+          <t>08:43:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="F57" t="n">
-        <v>7.79</v>
+        <v>7.68</v>
       </c>
       <c r="G57" t="n">
-        <v>109.6</v>
+        <v>99</v>
       </c>
       <c r="H57" t="n">
-        <v>17</v>
+        <v>27.7</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>286.37</v>
+        <v>-408.35</v>
       </c>
       <c r="K57" t="n">
-        <v>-72.34</v>
+        <v>-475.47</v>
       </c>
       <c r="L57" t="n">
-        <v>295.37</v>
+        <v>626.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:47:44</t>
+          <t>08:45:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="F58" t="n">
-        <v>8.029999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="G58" t="n">
-        <v>108.4</v>
+        <v>111.6</v>
       </c>
       <c r="H58" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="I58" t="n">
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-530.41</v>
+        <v>544.64</v>
       </c>
       <c r="K58" t="n">
-        <v>108.14</v>
+        <v>755.62</v>
       </c>
       <c r="L58" t="n">
-        <v>541.3200000000001</v>
+        <v>931.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:59:52</t>
+          <t>08:54:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="F59" t="n">
-        <v>7.56</v>
+        <v>7.95</v>
       </c>
       <c r="G59" t="n">
-        <v>105.8</v>
+        <v>108.8</v>
       </c>
       <c r="H59" t="n">
-        <v>22.1</v>
+        <v>21</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.82</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.22</v>
+        <v>25.49</v>
       </c>
       <c r="L59" t="n">
-        <v>70.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:01:31</t>
+          <t>08:54:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="F60" t="n">
-        <v>7.82</v>
+        <v>7.52</v>
       </c>
       <c r="G60" t="n">
-        <v>124.9</v>
+        <v>103</v>
       </c>
       <c r="H60" t="n">
-        <v>20.8</v>
+        <v>31</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-67.17</v>
+        <v>-111.39</v>
       </c>
       <c r="K60" t="n">
-        <v>-127.28</v>
+        <v>-135.64</v>
       </c>
       <c r="L60" t="n">
-        <v>143.91</v>
+        <v>175.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:02:42</t>
+          <t>08:56:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="F61" t="n">
-        <v>7.56</v>
+        <v>7.44</v>
       </c>
       <c r="G61" t="n">
-        <v>113.2</v>
+        <v>101.1</v>
       </c>
       <c r="H61" t="n">
-        <v>20.5</v>
+        <v>29.1</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-127.41</v>
+        <v>24.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-106.84</v>
+        <v>74.47</v>
       </c>
       <c r="L61" t="n">
-        <v>166.28</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:07:51</t>
+          <t>09:00:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="F62" t="n">
-        <v>7.35</v>
+        <v>7.2</v>
       </c>
       <c r="G62" t="n">
-        <v>118.8</v>
+        <v>121.4</v>
       </c>
       <c r="H62" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-150.08</v>
+        <v>-228.39</v>
       </c>
       <c r="K62" t="n">
-        <v>-40.81</v>
+        <v>95.75</v>
       </c>
       <c r="L62" t="n">
-        <v>155.53</v>
+        <v>247.64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:09:51</t>
+          <t>09:02:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="F63" t="n">
-        <v>7.99</v>
+        <v>7.28</v>
       </c>
       <c r="G63" t="n">
-        <v>110.2</v>
+        <v>116.2</v>
       </c>
       <c r="H63" t="n">
-        <v>26.6</v>
+        <v>32.1</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>122.62</v>
+        <v>106.93</v>
       </c>
       <c r="K63" t="n">
-        <v>61.67</v>
+        <v>-141.73</v>
       </c>
       <c r="L63" t="n">
-        <v>137.26</v>
+        <v>177.54</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:11:25</t>
+          <t>09:02:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="F64" t="n">
-        <v>7.89</v>
+        <v>7.39</v>
       </c>
       <c r="G64" t="n">
-        <v>110.8</v>
+        <v>108.3</v>
       </c>
       <c r="H64" t="n">
-        <v>31.3</v>
+        <v>28.1</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-30.99</v>
+        <v>274.83</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.61</v>
+        <v>-47.73</v>
       </c>
       <c r="L64" t="n">
-        <v>31.49</v>
+        <v>278.95</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:15:18</t>
+          <t>09:08:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="F65" t="n">
-        <v>7.71</v>
+        <v>7.52</v>
       </c>
       <c r="G65" t="n">
-        <v>124.1</v>
+        <v>119.8</v>
       </c>
       <c r="H65" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>8.220000000000001</v>
+        <v>598.67</v>
       </c>
       <c r="K65" t="n">
-        <v>-44.73</v>
+        <v>155.95</v>
       </c>
       <c r="L65" t="n">
-        <v>45.48</v>
+        <v>618.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:17:35</t>
+          <t>09:09:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="F66" t="n">
-        <v>7.43</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>109.6</v>
+        <v>99.8</v>
       </c>
       <c r="H66" t="n">
-        <v>25.7</v>
+        <v>28.1</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>121.66</v>
+        <v>329.42</v>
       </c>
       <c r="K66" t="n">
-        <v>110.41</v>
+        <v>101.08</v>
       </c>
       <c r="L66" t="n">
-        <v>164.29</v>
+        <v>344.58</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:10:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="F67" t="n">
-        <v>7.67</v>
+        <v>7.83</v>
       </c>
       <c r="G67" t="n">
-        <v>97.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="H67" t="n">
-        <v>27.6</v>
+        <v>24</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-163</v>
+        <v>-135.59</v>
       </c>
       <c r="K67" t="n">
-        <v>88.29000000000001</v>
+        <v>-60.35</v>
       </c>
       <c r="L67" t="n">
-        <v>185.37</v>
+        <v>148.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:24:22</t>
+          <t>09:14:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="F68" t="n">
-        <v>7.82</v>
+        <v>7.73</v>
       </c>
       <c r="G68" t="n">
-        <v>124.4</v>
+        <v>114</v>
       </c>
       <c r="H68" t="n">
-        <v>24.9</v>
+        <v>19.9</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-445.61</v>
+        <v>326.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-62.99</v>
+        <v>48.09</v>
       </c>
       <c r="L68" t="n">
-        <v>450.04</v>
+        <v>330.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:25:42</t>
+          <t>09:16:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="F69" t="n">
-        <v>8.15</v>
+        <v>7.77</v>
       </c>
       <c r="G69" t="n">
-        <v>106.6</v>
+        <v>102.6</v>
       </c>
       <c r="H69" t="n">
-        <v>24</v>
+        <v>28.9</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>354.56</v>
+        <v>-254.77</v>
       </c>
       <c r="K69" t="n">
-        <v>203.3</v>
+        <v>-377.56</v>
       </c>
       <c r="L69" t="n">
-        <v>408.71</v>
+        <v>455.48</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:27:43</t>
+          <t>09:18:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="F70" t="n">
-        <v>7.36</v>
+        <v>7.75</v>
       </c>
       <c r="G70" t="n">
-        <v>102.9</v>
+        <v>100.3</v>
       </c>
       <c r="H70" t="n">
-        <v>27.5</v>
+        <v>22.5</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-217.79</v>
+        <v>-209.94</v>
       </c>
       <c r="K70" t="n">
-        <v>37.75</v>
+        <v>341.08</v>
       </c>
       <c r="L70" t="n">
-        <v>221.04</v>
+        <v>400.51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:30:48</t>
+          <t>09:22:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="F71" t="n">
-        <v>7.84</v>
+        <v>7.82</v>
       </c>
       <c r="G71" t="n">
-        <v>113.7</v>
+        <v>105.6</v>
       </c>
       <c r="H71" t="n">
-        <v>24.5</v>
+        <v>26.1</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-238.72</v>
+        <v>-362.15</v>
       </c>
       <c r="K71" t="n">
-        <v>537.9299999999999</v>
+        <v>-200.86</v>
       </c>
       <c r="L71" t="n">
-        <v>588.51</v>
+        <v>414.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:33:25</t>
+          <t>09:24:11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3064,31 +3064,31 @@
         <v>2.85</v>
       </c>
       <c r="F72" t="n">
-        <v>7.38</v>
+        <v>6.98</v>
       </c>
       <c r="G72" t="n">
-        <v>112.9</v>
+        <v>108.9</v>
       </c>
       <c r="H72" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>73.55</v>
+        <v>289.2</v>
       </c>
       <c r="K72" t="n">
-        <v>-278.1</v>
+        <v>64.25</v>
       </c>
       <c r="L72" t="n">
-        <v>287.66</v>
+        <v>296.25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:35:07</t>
+          <t>09:26:03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.41</v>
+        <v>2.76</v>
       </c>
       <c r="F73" t="n">
-        <v>7.82</v>
+        <v>8.15</v>
       </c>
       <c r="G73" t="n">
-        <v>130.7</v>
+        <v>105.9</v>
       </c>
       <c r="H73" t="n">
-        <v>19.6</v>
+        <v>34.3</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-46.23</v>
+        <v>370.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-116.51</v>
+        <v>-350.34</v>
       </c>
       <c r="L73" t="n">
-        <v>125.35</v>
+        <v>509.58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:44:05</t>
+          <t>09:36:23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="F74" t="n">
-        <v>7.65</v>
+        <v>7.51</v>
       </c>
       <c r="G74" t="n">
-        <v>103.2</v>
+        <v>113.2</v>
       </c>
       <c r="H74" t="n">
-        <v>24.5</v>
+        <v>33</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-42.8</v>
+        <v>-44.55</v>
       </c>
       <c r="K74" t="n">
-        <v>4.41</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>43.03</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:45:32</t>
+          <t>09:37:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="F75" t="n">
-        <v>8.51</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>105.6</v>
+        <v>104.9</v>
       </c>
       <c r="H75" t="n">
-        <v>24.2</v>
+        <v>28.3</v>
       </c>
       <c r="I75" t="n">
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-103.56</v>
+        <v>150.83</v>
       </c>
       <c r="K75" t="n">
-        <v>81.54000000000001</v>
+        <v>115.41</v>
       </c>
       <c r="L75" t="n">
-        <v>131.81</v>
+        <v>189.92</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:47:06</t>
+          <t>09:39:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="F76" t="n">
-        <v>7.97</v>
+        <v>6.31</v>
       </c>
       <c r="G76" t="n">
-        <v>107.2</v>
+        <v>114.5</v>
       </c>
       <c r="H76" t="n">
-        <v>26.1</v>
+        <v>29.3</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-21</v>
+        <v>28.61</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.31</v>
+        <v>40.9</v>
       </c>
       <c r="L76" t="n">
-        <v>24.34</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:52:18</t>
+          <t>09:44:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.36</v>
+        <v>3.09</v>
       </c>
       <c r="F77" t="n">
-        <v>7.34</v>
+        <v>8.09</v>
       </c>
       <c r="G77" t="n">
-        <v>102.4</v>
+        <v>111.5</v>
       </c>
       <c r="H77" t="n">
-        <v>29.2</v>
+        <v>16.6</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>73.86</v>
+        <v>40.68</v>
       </c>
       <c r="K77" t="n">
-        <v>15.81</v>
+        <v>-86.55</v>
       </c>
       <c r="L77" t="n">
-        <v>75.53</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:53:16</t>
+          <t>09:46:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="F78" t="n">
-        <v>7.39</v>
+        <v>7.62</v>
       </c>
       <c r="G78" t="n">
-        <v>123.8</v>
+        <v>113.3</v>
       </c>
       <c r="H78" t="n">
-        <v>21.5</v>
+        <v>27.3</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>43.55</v>
+        <v>31.97</v>
       </c>
       <c r="K78" t="n">
-        <v>8.35</v>
+        <v>169.93</v>
       </c>
       <c r="L78" t="n">
-        <v>44.34</v>
+        <v>172.91</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:55:25</t>
+          <t>09:48:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
       <c r="F79" t="n">
-        <v>7.95</v>
+        <v>7.9</v>
       </c>
       <c r="G79" t="n">
-        <v>108.8</v>
+        <v>110.4</v>
       </c>
       <c r="H79" t="n">
-        <v>26.9</v>
+        <v>21.6</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>175.34</v>
+        <v>-99.61</v>
       </c>
       <c r="K79" t="n">
-        <v>266.35</v>
+        <v>106.8</v>
       </c>
       <c r="L79" t="n">
-        <v>318.88</v>
+        <v>146.04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:00:07</t>
+          <t>09:52:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="F80" t="n">
-        <v>7.91</v>
+        <v>7.39</v>
       </c>
       <c r="G80" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="H80" t="n">
-        <v>19.4</v>
+        <v>26</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-172.19</v>
+        <v>38.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-54.43</v>
+        <v>-274</v>
       </c>
       <c r="L80" t="n">
-        <v>180.58</v>
+        <v>276.63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:01:46</t>
+          <t>09:54:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="F81" t="n">
-        <v>7.64</v>
+        <v>7.65</v>
       </c>
       <c r="G81" t="n">
-        <v>112.1</v>
+        <v>106.3</v>
       </c>
       <c r="H81" t="n">
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-110.85</v>
+        <v>41.72</v>
       </c>
       <c r="K81" t="n">
-        <v>126.1</v>
+        <v>193.49</v>
       </c>
       <c r="L81" t="n">
-        <v>167.89</v>
+        <v>197.94</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:04:01</t>
+          <t>09:56:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="F82" t="n">
-        <v>8.06</v>
+        <v>7.66</v>
       </c>
       <c r="G82" t="n">
-        <v>111.4</v>
+        <v>113.1</v>
       </c>
       <c r="H82" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>212.18</v>
+        <v>-162.81</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.71</v>
+        <v>-158</v>
       </c>
       <c r="L82" t="n">
-        <v>212.5</v>
+        <v>226.87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:08:58</t>
+          <t>10:01:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.23</v>
+        <v>2.81</v>
       </c>
       <c r="F83" t="n">
-        <v>7.3</v>
+        <v>7.71</v>
       </c>
       <c r="G83" t="n">
-        <v>122.1</v>
+        <v>121.9</v>
       </c>
       <c r="H83" t="n">
-        <v>28.2</v>
+        <v>33.5</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-295.12</v>
+        <v>603.71</v>
       </c>
       <c r="K83" t="n">
-        <v>120.22</v>
+        <v>494.71</v>
       </c>
       <c r="L83" t="n">
-        <v>318.66</v>
+        <v>780.51</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:11:37</t>
+          <t>10:03:46</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="F84" t="n">
-        <v>7.09</v>
+        <v>7.53</v>
       </c>
       <c r="G84" t="n">
-        <v>104.8</v>
+        <v>107.7</v>
       </c>
       <c r="H84" t="n">
-        <v>30.3</v>
+        <v>24.2</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>15.33</v>
+        <v>102.08</v>
       </c>
       <c r="K84" t="n">
-        <v>-209.02</v>
+        <v>61.28</v>
       </c>
       <c r="L84" t="n">
-        <v>209.58</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:13:34</t>
+          <t>10:04:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="F85" t="n">
-        <v>7.78</v>
+        <v>8.02</v>
       </c>
       <c r="G85" t="n">
-        <v>110.4</v>
+        <v>111.8</v>
       </c>
       <c r="H85" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-125.06</v>
+        <v>-83.8</v>
       </c>
       <c r="K85" t="n">
-        <v>-210.57</v>
+        <v>98.88</v>
       </c>
       <c r="L85" t="n">
-        <v>244.9</v>
+        <v>129.61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:17:17</t>
+          <t>10:09:37</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.06</v>
+        <v>3.37</v>
       </c>
       <c r="F86" t="n">
-        <v>8.029999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="G86" t="n">
-        <v>114.7</v>
+        <v>117.6</v>
       </c>
       <c r="H86" t="n">
-        <v>26.3</v>
+        <v>27.2</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>239.15</v>
+        <v>849</v>
       </c>
       <c r="K86" t="n">
-        <v>625.28</v>
+        <v>388.95</v>
       </c>
       <c r="L86" t="n">
-        <v>669.46</v>
+        <v>933.85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:18:43</t>
+          <t>10:11:42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.74</v>
+        <v>3.24</v>
       </c>
       <c r="F87" t="n">
-        <v>7.37</v>
+        <v>7.85</v>
       </c>
       <c r="G87" t="n">
-        <v>101.5</v>
+        <v>104.6</v>
       </c>
       <c r="H87" t="n">
-        <v>23.3</v>
+        <v>24.6</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>174.34</v>
+        <v>-23.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-214.61</v>
+        <v>256.17</v>
       </c>
       <c r="L87" t="n">
-        <v>276.5</v>
+        <v>257.27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:20:44</t>
+          <t>10:12:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="F88" t="n">
-        <v>7.56</v>
+        <v>6.95</v>
       </c>
       <c r="G88" t="n">
-        <v>104.2</v>
+        <v>107.4</v>
       </c>
       <c r="H88" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>540.6900000000001</v>
+        <v>232.22</v>
       </c>
       <c r="K88" t="n">
-        <v>109.74</v>
+        <v>-96.97</v>
       </c>
       <c r="L88" t="n">
-        <v>551.71</v>
+        <v>251.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-38.22</v>
+        <v>-44.44</v>
       </c>
       <c r="K14" t="n">
-        <v>58.07</v>
+        <v>67.52</v>
       </c>
       <c r="L14" t="n">
-        <v>69.52</v>
+        <v>80.83</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-68.31</v>
+        <v>-61.39</v>
       </c>
       <c r="K15" t="n">
-        <v>129.87</v>
+        <v>116.71</v>
       </c>
       <c r="L15" t="n">
-        <v>146.74</v>
+        <v>131.87</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>36.06</v>
+        <v>40.7</v>
       </c>
       <c r="K16" t="n">
-        <v>78.77</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>86.63</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>82.31</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>179.55</v>
+        <v>169.46</v>
       </c>
       <c r="L17" t="n">
-        <v>197.52</v>
+        <v>186.41</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>41.26</v>
+        <v>36.42</v>
       </c>
       <c r="K18" t="n">
-        <v>287.7</v>
+        <v>253.95</v>
       </c>
       <c r="L18" t="n">
-        <v>290.64</v>
+        <v>256.55</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-98.95999999999999</v>
+        <v>-103.95</v>
       </c>
       <c r="K19" t="n">
-        <v>-68.89</v>
+        <v>-72.36</v>
       </c>
       <c r="L19" t="n">
-        <v>120.58</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>197.87</v>
+        <v>198.65</v>
       </c>
       <c r="K20" t="n">
-        <v>203.66</v>
+        <v>204.47</v>
       </c>
       <c r="L20" t="n">
-        <v>283.95</v>
+        <v>285.08</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-131.57</v>
+        <v>-202.78</v>
       </c>
       <c r="K21" t="n">
-        <v>63.76</v>
+        <v>98.27</v>
       </c>
       <c r="L21" t="n">
-        <v>146.2</v>
+        <v>225.34</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>92.09</v>
+        <v>134.19</v>
       </c>
       <c r="K22" t="n">
-        <v>78.16</v>
+        <v>113.89</v>
       </c>
       <c r="L22" t="n">
-        <v>120.79</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>28.88</v>
+        <v>29.15</v>
       </c>
       <c r="K23" t="n">
-        <v>468.69</v>
+        <v>473.04</v>
       </c>
       <c r="L23" t="n">
-        <v>469.58</v>
+        <v>473.94</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-112.52</v>
+        <v>-183.92</v>
       </c>
       <c r="K24" t="n">
-        <v>-188.13</v>
+        <v>-307.5</v>
       </c>
       <c r="L24" t="n">
-        <v>219.21</v>
+        <v>358.31</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>205.74</v>
+        <v>300.39</v>
       </c>
       <c r="K25" t="n">
-        <v>-44.15</v>
+        <v>-64.47</v>
       </c>
       <c r="L25" t="n">
-        <v>210.43</v>
+        <v>307.23</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-228.23</v>
+        <v>-277.88</v>
       </c>
       <c r="K26" t="n">
-        <v>341.92</v>
+        <v>416.3</v>
       </c>
       <c r="L26" t="n">
-        <v>411.09</v>
+        <v>500.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>164.82</v>
+        <v>314.05</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="L27" t="n">
-        <v>164.82</v>
+        <v>314.05</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>212.44</v>
+        <v>321.29</v>
       </c>
       <c r="K28" t="n">
-        <v>354.4</v>
+        <v>535.98</v>
       </c>
       <c r="L28" t="n">
-        <v>413.19</v>
+        <v>624.9</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-45.64</v>
+        <v>-43.33</v>
       </c>
       <c r="K29" t="n">
-        <v>110.2</v>
+        <v>104.62</v>
       </c>
       <c r="L29" t="n">
-        <v>119.28</v>
+        <v>113.24</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-79.89</v>
+        <v>-82.34</v>
       </c>
       <c r="K30" t="n">
-        <v>-136.2</v>
+        <v>-140.39</v>
       </c>
       <c r="L30" t="n">
-        <v>157.9</v>
+        <v>162.76</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-36.09</v>
+        <v>-33.13</v>
       </c>
       <c r="K31" t="n">
-        <v>134.44</v>
+        <v>123.4</v>
       </c>
       <c r="L31" t="n">
-        <v>139.2</v>
+        <v>127.77</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>182.42</v>
+        <v>176.46</v>
       </c>
       <c r="K32" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="L32" t="n">
-        <v>182.47</v>
+        <v>176.51</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-166.17</v>
+        <v>-171.79</v>
       </c>
       <c r="K33" t="n">
-        <v>52.5</v>
+        <v>54.27</v>
       </c>
       <c r="L33" t="n">
-        <v>174.26</v>
+        <v>180.16</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>155.99</v>
+        <v>141.91</v>
       </c>
       <c r="K34" t="n">
-        <v>-158.97</v>
+        <v>-144.61</v>
       </c>
       <c r="L34" t="n">
-        <v>222.72</v>
+        <v>202.61</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>135.02</v>
+        <v>150.21</v>
       </c>
       <c r="K35" t="n">
-        <v>-239.17</v>
+        <v>-266.08</v>
       </c>
       <c r="L35" t="n">
-        <v>274.65</v>
+        <v>305.55</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>275.74</v>
+        <v>247.53</v>
       </c>
       <c r="K36" t="n">
-        <v>-285.4</v>
+        <v>-256.2</v>
       </c>
       <c r="L36" t="n">
-        <v>396.84</v>
+        <v>356.25</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>75.37</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-76.75</v>
+        <v>-97.09999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>107.57</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>414.04</v>
+        <v>469.03</v>
       </c>
       <c r="K38" t="n">
-        <v>175.79</v>
+        <v>199.14</v>
       </c>
       <c r="L38" t="n">
-        <v>449.82</v>
+        <v>509.56</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>55.51</v>
+        <v>78.87</v>
       </c>
       <c r="K39" t="n">
-        <v>-268.59</v>
+        <v>-381.61</v>
       </c>
       <c r="L39" t="n">
-        <v>274.27</v>
+        <v>389.68</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-44.51</v>
+        <v>-61.06</v>
       </c>
       <c r="K40" t="n">
-        <v>-262.42</v>
+        <v>-359.99</v>
       </c>
       <c r="L40" t="n">
-        <v>266.17</v>
+        <v>365.13</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-32.2</v>
+        <v>-99.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-100.35</v>
+        <v>-309.4</v>
       </c>
       <c r="L41" t="n">
-        <v>105.39</v>
+        <v>324.94</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>235.19</v>
+        <v>286.89</v>
       </c>
       <c r="K42" t="n">
-        <v>793.05</v>
+        <v>967.39</v>
       </c>
       <c r="L42" t="n">
-        <v>827.1900000000001</v>
+        <v>1009.04</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>88.68000000000001</v>
+        <v>130.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-332.98</v>
+        <v>-489.09</v>
       </c>
       <c r="L43" t="n">
-        <v>344.59</v>
+        <v>506.14</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-91.3</v>
+        <v>-106.61</v>
       </c>
       <c r="K44" t="n">
-        <v>6.31</v>
+        <v>7.36</v>
       </c>
       <c r="L44" t="n">
-        <v>91.52</v>
+        <v>106.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-18.59</v>
+        <v>-17.11</v>
       </c>
       <c r="K45" t="n">
-        <v>-208.07</v>
+        <v>-191.47</v>
       </c>
       <c r="L45" t="n">
-        <v>208.9</v>
+        <v>192.23</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.61</v>
+        <v>-4.8</v>
       </c>
       <c r="K46" t="n">
-        <v>61.54</v>
+        <v>64.09</v>
       </c>
       <c r="L46" t="n">
-        <v>61.72</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-198.94</v>
+        <v>-208.59</v>
       </c>
       <c r="K47" t="n">
-        <v>-83.76000000000001</v>
+        <v>-87.81999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>215.85</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>64.73999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="K48" t="n">
-        <v>173.13</v>
+        <v>177.99</v>
       </c>
       <c r="L48" t="n">
-        <v>184.84</v>
+        <v>190.03</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>201.48</v>
+        <v>201.68</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.31</v>
+        <v>-6.32</v>
       </c>
       <c r="L49" t="n">
-        <v>201.58</v>
+        <v>201.78</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>139.05</v>
+        <v>202.63</v>
       </c>
       <c r="K50" t="n">
-        <v>115.63</v>
+        <v>168.5</v>
       </c>
       <c r="L50" t="n">
-        <v>180.85</v>
+        <v>263.54</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-370.91</v>
+        <v>-428.52</v>
       </c>
       <c r="K51" t="n">
-        <v>-52.16</v>
+        <v>-60.26</v>
       </c>
       <c r="L51" t="n">
-        <v>374.56</v>
+        <v>432.73</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>301.66</v>
+        <v>331.83</v>
       </c>
       <c r="K52" t="n">
-        <v>-55.05</v>
+        <v>-60.55</v>
       </c>
       <c r="L52" t="n">
-        <v>306.65</v>
+        <v>337.31</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>50.32</v>
+        <v>54.79</v>
       </c>
       <c r="K53" t="n">
-        <v>815.97</v>
+        <v>888.5</v>
       </c>
       <c r="L53" t="n">
-        <v>817.52</v>
+        <v>890.1900000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>88.2</v>
+        <v>103.05</v>
       </c>
       <c r="K54" t="n">
-        <v>-252.32</v>
+        <v>-294.79</v>
       </c>
       <c r="L54" t="n">
-        <v>267.29</v>
+        <v>312.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-23.45</v>
+        <v>-33.1</v>
       </c>
       <c r="K55" t="n">
-        <v>-232.47</v>
+        <v>-328.16</v>
       </c>
       <c r="L55" t="n">
-        <v>233.65</v>
+        <v>329.82</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>41.37</v>
+        <v>96.64</v>
       </c>
       <c r="K56" t="n">
-        <v>-143.14</v>
+        <v>-334.38</v>
       </c>
       <c r="L56" t="n">
-        <v>149</v>
+        <v>348.07</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-408.35</v>
+        <v>-517.58</v>
       </c>
       <c r="K57" t="n">
-        <v>-475.47</v>
+        <v>-602.65</v>
       </c>
       <c r="L57" t="n">
-        <v>626.75</v>
+        <v>794.41</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>544.64</v>
+        <v>592.86</v>
       </c>
       <c r="K58" t="n">
-        <v>755.62</v>
+        <v>822.52</v>
       </c>
       <c r="L58" t="n">
-        <v>931.45</v>
+        <v>1013.92</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>87.54000000000001</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>25.49</v>
+        <v>28.33</v>
       </c>
       <c r="L59" t="n">
-        <v>91.18000000000001</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-111.39</v>
+        <v>-121.82</v>
       </c>
       <c r="K60" t="n">
-        <v>-135.64</v>
+        <v>-148.35</v>
       </c>
       <c r="L60" t="n">
-        <v>175.52</v>
+        <v>191.96</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>24.7</v>
+        <v>37.5</v>
       </c>
       <c r="K61" t="n">
-        <v>74.47</v>
+        <v>113.04</v>
       </c>
       <c r="L61" t="n">
-        <v>78.45999999999999</v>
+        <v>119.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-228.39</v>
+        <v>-253.45</v>
       </c>
       <c r="K62" t="n">
-        <v>95.75</v>
+        <v>106.26</v>
       </c>
       <c r="L62" t="n">
-        <v>247.64</v>
+        <v>274.83</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>106.93</v>
+        <v>107.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-141.73</v>
+        <v>-142.16</v>
       </c>
       <c r="L63" t="n">
-        <v>177.54</v>
+        <v>178.08</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>274.83</v>
+        <v>292.73</v>
       </c>
       <c r="K64" t="n">
-        <v>-47.73</v>
+        <v>-50.84</v>
       </c>
       <c r="L64" t="n">
-        <v>278.95</v>
+        <v>297.11</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>598.67</v>
+        <v>678.46</v>
       </c>
       <c r="K65" t="n">
-        <v>155.95</v>
+        <v>176.74</v>
       </c>
       <c r="L65" t="n">
-        <v>618.65</v>
+        <v>701.1</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>329.42</v>
+        <v>353.49</v>
       </c>
       <c r="K66" t="n">
-        <v>101.08</v>
+        <v>108.47</v>
       </c>
       <c r="L66" t="n">
-        <v>344.58</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-135.59</v>
+        <v>-239.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-60.35</v>
+        <v>-106.42</v>
       </c>
       <c r="L67" t="n">
-        <v>148.41</v>
+        <v>261.71</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>326.81</v>
+        <v>361.22</v>
       </c>
       <c r="K68" t="n">
-        <v>48.09</v>
+        <v>53.15</v>
       </c>
       <c r="L68" t="n">
-        <v>330.33</v>
+        <v>365.11</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-254.77</v>
+        <v>-305.21</v>
       </c>
       <c r="K69" t="n">
-        <v>-377.56</v>
+        <v>-452.32</v>
       </c>
       <c r="L69" t="n">
-        <v>455.48</v>
+        <v>545.66</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-209.94</v>
+        <v>-231.5</v>
       </c>
       <c r="K70" t="n">
-        <v>341.08</v>
+        <v>376.11</v>
       </c>
       <c r="L70" t="n">
-        <v>400.51</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-362.15</v>
+        <v>-507.85</v>
       </c>
       <c r="K71" t="n">
-        <v>-200.86</v>
+        <v>-281.67</v>
       </c>
       <c r="L71" t="n">
-        <v>414.12</v>
+        <v>580.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>289.2</v>
+        <v>489.67</v>
       </c>
       <c r="K72" t="n">
-        <v>64.25</v>
+        <v>108.79</v>
       </c>
       <c r="L72" t="n">
-        <v>296.25</v>
+        <v>501.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>370.05</v>
+        <v>504.83</v>
       </c>
       <c r="K73" t="n">
-        <v>-350.34</v>
+        <v>-477.94</v>
       </c>
       <c r="L73" t="n">
-        <v>509.58</v>
+        <v>695.1799999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.55</v>
+        <v>-62.34</v>
       </c>
       <c r="K74" t="n">
-        <v>72.73999999999999</v>
+        <v>101.81</v>
       </c>
       <c r="L74" t="n">
-        <v>85.3</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>150.83</v>
+        <v>145.4</v>
       </c>
       <c r="K75" t="n">
-        <v>115.41</v>
+        <v>111.25</v>
       </c>
       <c r="L75" t="n">
-        <v>189.92</v>
+        <v>183.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>28.61</v>
+        <v>49.4</v>
       </c>
       <c r="K76" t="n">
-        <v>40.9</v>
+        <v>70.62</v>
       </c>
       <c r="L76" t="n">
-        <v>49.92</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>40.68</v>
+        <v>64.7</v>
       </c>
       <c r="K77" t="n">
-        <v>-86.55</v>
+        <v>-137.67</v>
       </c>
       <c r="L77" t="n">
-        <v>95.63</v>
+        <v>152.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>31.97</v>
+        <v>35.04</v>
       </c>
       <c r="K78" t="n">
-        <v>169.93</v>
+        <v>186.27</v>
       </c>
       <c r="L78" t="n">
-        <v>172.91</v>
+        <v>189.54</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-99.61</v>
+        <v>-117.71</v>
       </c>
       <c r="K79" t="n">
-        <v>106.8</v>
+        <v>126.21</v>
       </c>
       <c r="L79" t="n">
-        <v>146.04</v>
+        <v>172.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>38.06</v>
+        <v>39.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-274</v>
+        <v>-281.19</v>
       </c>
       <c r="L80" t="n">
-        <v>276.63</v>
+        <v>283.89</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>41.72</v>
+        <v>55.85</v>
       </c>
       <c r="K81" t="n">
-        <v>193.49</v>
+        <v>259.03</v>
       </c>
       <c r="L81" t="n">
-        <v>197.94</v>
+        <v>264.99</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-162.81</v>
+        <v>-214.03</v>
       </c>
       <c r="K82" t="n">
-        <v>-158</v>
+        <v>-207.72</v>
       </c>
       <c r="L82" t="n">
-        <v>226.87</v>
+        <v>298.26</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>603.71</v>
+        <v>649.92</v>
       </c>
       <c r="K83" t="n">
-        <v>494.71</v>
+        <v>532.58</v>
       </c>
       <c r="L83" t="n">
-        <v>780.51</v>
+        <v>840.27</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>102.08</v>
+        <v>210.04</v>
       </c>
       <c r="K84" t="n">
-        <v>61.28</v>
+        <v>126.08</v>
       </c>
       <c r="L84" t="n">
-        <v>119.06</v>
+        <v>244.97</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-83.8</v>
+        <v>-202.02</v>
       </c>
       <c r="K85" t="n">
-        <v>98.88</v>
+        <v>238.37</v>
       </c>
       <c r="L85" t="n">
-        <v>129.61</v>
+        <v>312.47</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>849</v>
+        <v>1042.53</v>
       </c>
       <c r="K86" t="n">
-        <v>388.95</v>
+        <v>477.62</v>
       </c>
       <c r="L86" t="n">
-        <v>933.85</v>
+        <v>1146.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-23.71</v>
+        <v>-44.32</v>
       </c>
       <c r="K87" t="n">
-        <v>256.17</v>
+        <v>478.83</v>
       </c>
       <c r="L87" t="n">
-        <v>257.27</v>
+        <v>480.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>232.22</v>
+        <v>447.1</v>
       </c>
       <c r="K88" t="n">
-        <v>-96.97</v>
+        <v>-186.71</v>
       </c>
       <c r="L88" t="n">
-        <v>251.65</v>
+        <v>484.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-44.44</v>
+        <v>-33.71</v>
       </c>
       <c r="K14" t="n">
-        <v>67.52</v>
+        <v>51.21</v>
       </c>
       <c r="L14" t="n">
-        <v>80.83</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-61.39</v>
+        <v>-47.23</v>
       </c>
       <c r="K15" t="n">
-        <v>116.71</v>
+        <v>89.8</v>
       </c>
       <c r="L15" t="n">
-        <v>131.87</v>
+        <v>101.46</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>40.7</v>
+        <v>29.59</v>
       </c>
       <c r="K16" t="n">
-        <v>88.90000000000001</v>
+        <v>64.64</v>
       </c>
       <c r="L16" t="n">
-        <v>97.77</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>77.68000000000001</v>
+        <v>54.52</v>
       </c>
       <c r="K17" t="n">
-        <v>169.46</v>
+        <v>118.93</v>
       </c>
       <c r="L17" t="n">
-        <v>186.41</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>36.42</v>
+        <v>24.81</v>
       </c>
       <c r="K18" t="n">
-        <v>253.95</v>
+        <v>173</v>
       </c>
       <c r="L18" t="n">
-        <v>256.55</v>
+        <v>174.77</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-103.95</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-72.36</v>
+        <v>-53.85</v>
       </c>
       <c r="L19" t="n">
-        <v>126.66</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>198.65</v>
+        <v>124.39</v>
       </c>
       <c r="K20" t="n">
-        <v>204.47</v>
+        <v>128.04</v>
       </c>
       <c r="L20" t="n">
-        <v>285.08</v>
+        <v>178.51</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-202.78</v>
+        <v>-121.86</v>
       </c>
       <c r="K21" t="n">
-        <v>98.27</v>
+        <v>59.05</v>
       </c>
       <c r="L21" t="n">
-        <v>225.34</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>134.19</v>
+        <v>80.37</v>
       </c>
       <c r="K22" t="n">
-        <v>113.89</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>176</v>
+        <v>105.41</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>29.15</v>
+        <v>15.86</v>
       </c>
       <c r="K23" t="n">
-        <v>473.04</v>
+        <v>257.41</v>
       </c>
       <c r="L23" t="n">
-        <v>473.94</v>
+        <v>257.9</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-183.92</v>
+        <v>-88.27</v>
       </c>
       <c r="K24" t="n">
-        <v>-307.5</v>
+        <v>-147.58</v>
       </c>
       <c r="L24" t="n">
-        <v>358.31</v>
+        <v>171.97</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>300.39</v>
+        <v>163.49</v>
       </c>
       <c r="K25" t="n">
-        <v>-64.47</v>
+        <v>-35.09</v>
       </c>
       <c r="L25" t="n">
-        <v>307.23</v>
+        <v>167.21</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-277.88</v>
+        <v>-142.48</v>
       </c>
       <c r="K26" t="n">
-        <v>416.3</v>
+        <v>213.45</v>
       </c>
       <c r="L26" t="n">
-        <v>500.53</v>
+        <v>256.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>314.05</v>
+        <v>159.37</v>
       </c>
       <c r="K27" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="L27" t="n">
-        <v>314.05</v>
+        <v>159.37</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>321.29</v>
+        <v>140.45</v>
       </c>
       <c r="K28" t="n">
-        <v>535.98</v>
+        <v>234.3</v>
       </c>
       <c r="L28" t="n">
-        <v>624.9</v>
+        <v>273.17</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-43.33</v>
+        <v>-33.62</v>
       </c>
       <c r="K29" t="n">
-        <v>104.62</v>
+        <v>81.19</v>
       </c>
       <c r="L29" t="n">
-        <v>113.24</v>
+        <v>87.88</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-82.34</v>
+        <v>-55.98</v>
       </c>
       <c r="K30" t="n">
-        <v>-140.39</v>
+        <v>-95.45</v>
       </c>
       <c r="L30" t="n">
-        <v>162.76</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-33.13</v>
+        <v>-24.37</v>
       </c>
       <c r="K31" t="n">
-        <v>123.4</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>127.77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>176.46</v>
+        <v>126.09</v>
       </c>
       <c r="K32" t="n">
-        <v>4.41</v>
+        <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>176.51</v>
+        <v>126.13</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-171.79</v>
+        <v>-114.75</v>
       </c>
       <c r="K33" t="n">
-        <v>54.27</v>
+        <v>36.25</v>
       </c>
       <c r="L33" t="n">
-        <v>180.16</v>
+        <v>120.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>141.91</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-144.61</v>
+        <v>-101.73</v>
       </c>
       <c r="L34" t="n">
-        <v>202.61</v>
+        <v>142.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>150.21</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-266.08</v>
+        <v>-151.28</v>
       </c>
       <c r="L35" t="n">
-        <v>305.55</v>
+        <v>173.72</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>247.53</v>
+        <v>159.45</v>
       </c>
       <c r="K36" t="n">
-        <v>-256.2</v>
+        <v>-165.03</v>
       </c>
       <c r="L36" t="n">
-        <v>356.25</v>
+        <v>229.48</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>95.34999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="K37" t="n">
-        <v>-97.09999999999999</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>136.09</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>469.03</v>
+        <v>233.86</v>
       </c>
       <c r="K38" t="n">
-        <v>199.14</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>509.56</v>
+        <v>254.06</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>78.87</v>
+        <v>38.49</v>
       </c>
       <c r="K39" t="n">
-        <v>-381.61</v>
+        <v>-186.24</v>
       </c>
       <c r="L39" t="n">
-        <v>389.68</v>
+        <v>190.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-61.06</v>
+        <v>-32.31</v>
       </c>
       <c r="K40" t="n">
-        <v>-359.99</v>
+        <v>-190.46</v>
       </c>
       <c r="L40" t="n">
-        <v>365.13</v>
+        <v>193.18</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-99.27</v>
+        <v>-44.12</v>
       </c>
       <c r="K41" t="n">
-        <v>-309.4</v>
+        <v>-137.5</v>
       </c>
       <c r="L41" t="n">
-        <v>324.94</v>
+        <v>144.41</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>286.89</v>
+        <v>125.41</v>
       </c>
       <c r="K42" t="n">
-        <v>967.39</v>
+        <v>422.89</v>
       </c>
       <c r="L42" t="n">
-        <v>1009.04</v>
+        <v>441.09</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>130.25</v>
+        <v>59.96</v>
       </c>
       <c r="K43" t="n">
-        <v>-489.09</v>
+        <v>-225.15</v>
       </c>
       <c r="L43" t="n">
-        <v>506.14</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-106.61</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>7.36</v>
+        <v>5.42</v>
       </c>
       <c r="L44" t="n">
-        <v>106.87</v>
+        <v>78.68000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.11</v>
+        <v>-11.93</v>
       </c>
       <c r="K45" t="n">
-        <v>-191.47</v>
+        <v>-133.57</v>
       </c>
       <c r="L45" t="n">
-        <v>192.23</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.8</v>
+        <v>-4.04</v>
       </c>
       <c r="K46" t="n">
-        <v>64.09</v>
+        <v>53.92</v>
       </c>
       <c r="L46" t="n">
-        <v>64.27</v>
+        <v>54.07</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-208.59</v>
+        <v>-141.84</v>
       </c>
       <c r="K47" t="n">
-        <v>-87.81999999999999</v>
+        <v>-59.72</v>
       </c>
       <c r="L47" t="n">
-        <v>226.32</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>66.56</v>
+        <v>46.42</v>
       </c>
       <c r="K48" t="n">
-        <v>177.99</v>
+        <v>124.14</v>
       </c>
       <c r="L48" t="n">
-        <v>190.03</v>
+        <v>132.54</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>201.68</v>
+        <v>138.21</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.32</v>
+        <v>-4.33</v>
       </c>
       <c r="L49" t="n">
-        <v>201.78</v>
+        <v>138.28</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>202.63</v>
+        <v>110.87</v>
       </c>
       <c r="K50" t="n">
-        <v>168.5</v>
+        <v>92.2</v>
       </c>
       <c r="L50" t="n">
-        <v>263.54</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-428.52</v>
+        <v>-231.33</v>
       </c>
       <c r="K51" t="n">
-        <v>-60.26</v>
+        <v>-32.53</v>
       </c>
       <c r="L51" t="n">
-        <v>432.73</v>
+        <v>233.61</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>331.83</v>
+        <v>199.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-60.55</v>
+        <v>-36.31</v>
       </c>
       <c r="L52" t="n">
-        <v>337.31</v>
+        <v>202.29</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>54.79</v>
+        <v>27.03</v>
       </c>
       <c r="K53" t="n">
-        <v>888.5</v>
+        <v>438.24</v>
       </c>
       <c r="L53" t="n">
-        <v>890.1900000000001</v>
+        <v>439.08</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>103.05</v>
+        <v>57.74</v>
       </c>
       <c r="K54" t="n">
-        <v>-294.79</v>
+        <v>-165.18</v>
       </c>
       <c r="L54" t="n">
-        <v>312.28</v>
+        <v>174.98</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-33.1</v>
+        <v>-18.02</v>
       </c>
       <c r="K55" t="n">
-        <v>-328.16</v>
+        <v>-178.6</v>
       </c>
       <c r="L55" t="n">
-        <v>329.82</v>
+        <v>179.51</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>96.64</v>
+        <v>44.21</v>
       </c>
       <c r="K56" t="n">
-        <v>-334.38</v>
+        <v>-152.96</v>
       </c>
       <c r="L56" t="n">
-        <v>348.07</v>
+        <v>159.22</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-517.58</v>
+        <v>-245.14</v>
       </c>
       <c r="K57" t="n">
-        <v>-602.65</v>
+        <v>-285.43</v>
       </c>
       <c r="L57" t="n">
-        <v>794.41</v>
+        <v>376.25</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>592.86</v>
+        <v>291.49</v>
       </c>
       <c r="K58" t="n">
-        <v>822.52</v>
+        <v>404.4</v>
       </c>
       <c r="L58" t="n">
-        <v>1013.92</v>
+        <v>498.5</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>97.29000000000001</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>28.33</v>
+        <v>22</v>
       </c>
       <c r="L59" t="n">
-        <v>101.33</v>
+        <v>78.70999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-121.82</v>
+        <v>-82.52</v>
       </c>
       <c r="K60" t="n">
-        <v>-148.35</v>
+        <v>-100.49</v>
       </c>
       <c r="L60" t="n">
-        <v>191.96</v>
+        <v>130.04</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>37.5</v>
+        <v>24.82</v>
       </c>
       <c r="K61" t="n">
-        <v>113.04</v>
+        <v>74.83</v>
       </c>
       <c r="L61" t="n">
-        <v>119.09</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-253.45</v>
+        <v>-155.87</v>
       </c>
       <c r="K62" t="n">
-        <v>106.26</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>274.83</v>
+        <v>169.02</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>107.26</v>
+        <v>75.94</v>
       </c>
       <c r="K63" t="n">
-        <v>-142.16</v>
+        <v>-100.65</v>
       </c>
       <c r="L63" t="n">
-        <v>178.08</v>
+        <v>126.08</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>292.73</v>
+        <v>180.41</v>
       </c>
       <c r="K64" t="n">
-        <v>-50.84</v>
+        <v>-31.33</v>
       </c>
       <c r="L64" t="n">
-        <v>297.11</v>
+        <v>183.11</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>678.46</v>
+        <v>351.58</v>
       </c>
       <c r="K65" t="n">
-        <v>176.74</v>
+        <v>91.58</v>
       </c>
       <c r="L65" t="n">
-        <v>701.1</v>
+        <v>363.31</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>353.49</v>
+        <v>211.25</v>
       </c>
       <c r="K66" t="n">
-        <v>108.47</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>369.75</v>
+        <v>220.97</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-239.1</v>
+        <v>-127.24</v>
       </c>
       <c r="K67" t="n">
-        <v>-106.42</v>
+        <v>-56.63</v>
       </c>
       <c r="L67" t="n">
-        <v>261.71</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>361.22</v>
+        <v>197.8</v>
       </c>
       <c r="K68" t="n">
-        <v>53.15</v>
+        <v>29.1</v>
       </c>
       <c r="L68" t="n">
-        <v>365.11</v>
+        <v>199.93</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-305.21</v>
+        <v>-153.4</v>
       </c>
       <c r="K69" t="n">
-        <v>-452.32</v>
+        <v>-227.34</v>
       </c>
       <c r="L69" t="n">
-        <v>545.66</v>
+        <v>274.25</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-231.5</v>
+        <v>-125.97</v>
       </c>
       <c r="K70" t="n">
-        <v>376.11</v>
+        <v>204.66</v>
       </c>
       <c r="L70" t="n">
-        <v>441.64</v>
+        <v>240.32</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-507.85</v>
+        <v>-235.69</v>
       </c>
       <c r="K71" t="n">
-        <v>-281.67</v>
+        <v>-130.72</v>
       </c>
       <c r="L71" t="n">
-        <v>580.73</v>
+        <v>269.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>489.67</v>
+        <v>224.06</v>
       </c>
       <c r="K72" t="n">
-        <v>108.79</v>
+        <v>49.78</v>
       </c>
       <c r="L72" t="n">
-        <v>501.61</v>
+        <v>229.52</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>504.83</v>
+        <v>226.83</v>
       </c>
       <c r="K73" t="n">
-        <v>-477.94</v>
+        <v>-214.75</v>
       </c>
       <c r="L73" t="n">
-        <v>695.1799999999999</v>
+        <v>312.36</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-62.34</v>
+        <v>-42.08</v>
       </c>
       <c r="K74" t="n">
-        <v>101.81</v>
+        <v>68.72</v>
       </c>
       <c r="L74" t="n">
-        <v>119.38</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>145.4</v>
+        <v>107.37</v>
       </c>
       <c r="K75" t="n">
-        <v>111.25</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>183.08</v>
+        <v>135.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>49.4</v>
+        <v>36.63</v>
       </c>
       <c r="K76" t="n">
-        <v>70.62</v>
+        <v>52.36</v>
       </c>
       <c r="L76" t="n">
-        <v>86.18000000000001</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>64.7</v>
+        <v>39.96</v>
       </c>
       <c r="K77" t="n">
-        <v>-137.67</v>
+        <v>-85.03</v>
       </c>
       <c r="L77" t="n">
-        <v>152.12</v>
+        <v>93.95</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>35.04</v>
+        <v>24.46</v>
       </c>
       <c r="K78" t="n">
-        <v>186.27</v>
+        <v>130.03</v>
       </c>
       <c r="L78" t="n">
-        <v>189.54</v>
+        <v>132.31</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-117.71</v>
+        <v>-80.28</v>
       </c>
       <c r="K79" t="n">
-        <v>126.21</v>
+        <v>86.08</v>
       </c>
       <c r="L79" t="n">
-        <v>172.59</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>39.06</v>
+        <v>21.91</v>
       </c>
       <c r="K80" t="n">
-        <v>-281.19</v>
+        <v>-157.72</v>
       </c>
       <c r="L80" t="n">
-        <v>283.89</v>
+        <v>159.23</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>55.85</v>
+        <v>32.94</v>
       </c>
       <c r="K81" t="n">
-        <v>259.03</v>
+        <v>152.79</v>
       </c>
       <c r="L81" t="n">
-        <v>264.99</v>
+        <v>156.3</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-214.03</v>
+        <v>-118.63</v>
       </c>
       <c r="K82" t="n">
-        <v>-207.72</v>
+        <v>-115.13</v>
       </c>
       <c r="L82" t="n">
-        <v>298.26</v>
+        <v>165.31</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>649.92</v>
+        <v>314.32</v>
       </c>
       <c r="K83" t="n">
-        <v>532.58</v>
+        <v>257.57</v>
       </c>
       <c r="L83" t="n">
-        <v>840.27</v>
+        <v>406.37</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>210.04</v>
+        <v>106.74</v>
       </c>
       <c r="K84" t="n">
-        <v>126.08</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>244.97</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-202.02</v>
+        <v>-94.13</v>
       </c>
       <c r="K85" t="n">
-        <v>238.37</v>
+        <v>111.07</v>
       </c>
       <c r="L85" t="n">
-        <v>312.47</v>
+        <v>145.59</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>1042.53</v>
+        <v>463.74</v>
       </c>
       <c r="K86" t="n">
-        <v>477.62</v>
+        <v>212.45</v>
       </c>
       <c r="L86" t="n">
-        <v>1146.73</v>
+        <v>510.09</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-44.32</v>
+        <v>-20.34</v>
       </c>
       <c r="K87" t="n">
-        <v>478.83</v>
+        <v>219.74</v>
       </c>
       <c r="L87" t="n">
-        <v>480.88</v>
+        <v>220.68</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>447.1</v>
+        <v>194.22</v>
       </c>
       <c r="K88" t="n">
-        <v>-186.71</v>
+        <v>-81.11</v>
       </c>
       <c r="L88" t="n">
-        <v>484.52</v>
+        <v>210.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-33.71</v>
+        <v>-33.1</v>
       </c>
       <c r="K14" t="n">
-        <v>51.21</v>
+        <v>50.29</v>
       </c>
       <c r="L14" t="n">
-        <v>61.3</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-47.23</v>
+        <v>-45.63</v>
       </c>
       <c r="K15" t="n">
-        <v>89.8</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>101.46</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>29.59</v>
+        <v>29.27</v>
       </c>
       <c r="K16" t="n">
-        <v>64.64</v>
+        <v>63.93</v>
       </c>
       <c r="L16" t="n">
-        <v>71.09</v>
+        <v>70.31</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>54.52</v>
+        <v>54.73</v>
       </c>
       <c r="K17" t="n">
-        <v>118.93</v>
+        <v>119.4</v>
       </c>
       <c r="L17" t="n">
-        <v>130.83</v>
+        <v>131.35</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>24.81</v>
+        <v>25.31</v>
       </c>
       <c r="K18" t="n">
-        <v>173</v>
+        <v>176.47</v>
       </c>
       <c r="L18" t="n">
-        <v>174.77</v>
+        <v>178.27</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-77.34999999999999</v>
+        <v>-77.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-53.85</v>
+        <v>-53.84</v>
       </c>
       <c r="L19" t="n">
-        <v>94.25</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>124.39</v>
+        <v>129.77</v>
       </c>
       <c r="K20" t="n">
-        <v>128.04</v>
+        <v>133.57</v>
       </c>
       <c r="L20" t="n">
-        <v>178.51</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-121.86</v>
+        <v>-126.75</v>
       </c>
       <c r="K21" t="n">
-        <v>59.05</v>
+        <v>61.42</v>
       </c>
       <c r="L21" t="n">
-        <v>135.41</v>
+        <v>140.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>80.37</v>
+        <v>84.02</v>
       </c>
       <c r="K22" t="n">
-        <v>68.20999999999999</v>
+        <v>71.31</v>
       </c>
       <c r="L22" t="n">
-        <v>105.41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>15.86</v>
+        <v>17.1</v>
       </c>
       <c r="K23" t="n">
-        <v>257.41</v>
+        <v>277.53</v>
       </c>
       <c r="L23" t="n">
-        <v>257.9</v>
+        <v>278.06</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-88.27</v>
+        <v>-96.06</v>
       </c>
       <c r="K24" t="n">
-        <v>-147.58</v>
+        <v>-160.6</v>
       </c>
       <c r="L24" t="n">
-        <v>171.97</v>
+        <v>187.13</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>163.49</v>
+        <v>173.06</v>
       </c>
       <c r="K25" t="n">
-        <v>-35.09</v>
+        <v>-37.14</v>
       </c>
       <c r="L25" t="n">
-        <v>167.21</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-142.48</v>
+        <v>-155.56</v>
       </c>
       <c r="K26" t="n">
-        <v>213.45</v>
+        <v>233.04</v>
       </c>
       <c r="L26" t="n">
-        <v>256.64</v>
+        <v>280.19</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>159.37</v>
+        <v>170.72</v>
       </c>
       <c r="K27" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="L27" t="n">
-        <v>159.37</v>
+        <v>170.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>140.45</v>
+        <v>154.2</v>
       </c>
       <c r="K28" t="n">
-        <v>234.3</v>
+        <v>257.25</v>
       </c>
       <c r="L28" t="n">
-        <v>273.17</v>
+        <v>299.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.62</v>
+        <v>-32.84</v>
       </c>
       <c r="K29" t="n">
-        <v>81.19</v>
+        <v>79.3</v>
       </c>
       <c r="L29" t="n">
-        <v>87.88</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-55.98</v>
+        <v>-55.46</v>
       </c>
       <c r="K30" t="n">
-        <v>-95.45</v>
+        <v>-94.56</v>
       </c>
       <c r="L30" t="n">
-        <v>110.66</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-24.37</v>
+        <v>-23.9</v>
       </c>
       <c r="K31" t="n">
-        <v>90.79000000000001</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>94</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>126.09</v>
+        <v>126.19</v>
       </c>
       <c r="K32" t="n">
         <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>126.13</v>
+        <v>126.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-114.75</v>
+        <v>-116.09</v>
       </c>
       <c r="K33" t="n">
-        <v>36.25</v>
+        <v>36.68</v>
       </c>
       <c r="L33" t="n">
-        <v>120.34</v>
+        <v>121.74</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>99.81999999999999</v>
+        <v>100.72</v>
       </c>
       <c r="K34" t="n">
-        <v>-101.73</v>
+        <v>-102.64</v>
       </c>
       <c r="L34" t="n">
-        <v>142.52</v>
+        <v>143.8</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>85.40000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="K35" t="n">
-        <v>-151.28</v>
+        <v>-159.87</v>
       </c>
       <c r="L35" t="n">
-        <v>173.72</v>
+        <v>183.58</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>159.45</v>
+        <v>163.24</v>
       </c>
       <c r="K36" t="n">
-        <v>-165.03</v>
+        <v>-168.96</v>
       </c>
       <c r="L36" t="n">
-        <v>229.48</v>
+        <v>234.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>64.56</v>
+        <v>66.78</v>
       </c>
       <c r="K37" t="n">
-        <v>-65.73999999999999</v>
+        <v>-68</v>
       </c>
       <c r="L37" t="n">
-        <v>92.14</v>
+        <v>95.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>233.86</v>
+        <v>252.28</v>
       </c>
       <c r="K38" t="n">
-        <v>99.29000000000001</v>
+        <v>107.11</v>
       </c>
       <c r="L38" t="n">
-        <v>254.06</v>
+        <v>274.08</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>38.49</v>
+        <v>41.73</v>
       </c>
       <c r="K39" t="n">
-        <v>-186.24</v>
+        <v>-201.89</v>
       </c>
       <c r="L39" t="n">
-        <v>190.17</v>
+        <v>206.15</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-32.31</v>
+        <v>-34.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-190.46</v>
+        <v>-203.2</v>
       </c>
       <c r="L40" t="n">
-        <v>193.18</v>
+        <v>206.11</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-44.12</v>
+        <v>-48.68</v>
       </c>
       <c r="K41" t="n">
-        <v>-137.5</v>
+        <v>-151.73</v>
       </c>
       <c r="L41" t="n">
-        <v>144.41</v>
+        <v>159.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>125.41</v>
+        <v>138.45</v>
       </c>
       <c r="K42" t="n">
-        <v>422.89</v>
+        <v>466.85</v>
       </c>
       <c r="L42" t="n">
-        <v>441.09</v>
+        <v>486.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>59.96</v>
+        <v>65.52</v>
       </c>
       <c r="K43" t="n">
-        <v>-225.15</v>
+        <v>-246.02</v>
       </c>
       <c r="L43" t="n">
-        <v>233</v>
+        <v>254.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-78.48999999999999</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="L44" t="n">
-        <v>78.68000000000001</v>
+        <v>76.97</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.93</v>
+        <v>-11.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-133.57</v>
+        <v>-130.91</v>
       </c>
       <c r="L45" t="n">
-        <v>134.1</v>
+        <v>131.43</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.04</v>
+        <v>-3.9</v>
       </c>
       <c r="K46" t="n">
-        <v>53.92</v>
+        <v>52.08</v>
       </c>
       <c r="L46" t="n">
-        <v>54.07</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-141.84</v>
+        <v>-144.07</v>
       </c>
       <c r="K47" t="n">
-        <v>-59.72</v>
+        <v>-60.65</v>
       </c>
       <c r="L47" t="n">
-        <v>153.9</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>46.42</v>
+        <v>47.02</v>
       </c>
       <c r="K48" t="n">
-        <v>124.14</v>
+        <v>125.73</v>
       </c>
       <c r="L48" t="n">
-        <v>132.54</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>138.21</v>
+        <v>139.75</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.33</v>
+        <v>-4.38</v>
       </c>
       <c r="L49" t="n">
-        <v>138.28</v>
+        <v>139.82</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>110.87</v>
+        <v>117.43</v>
       </c>
       <c r="K50" t="n">
-        <v>92.2</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>144.2</v>
+        <v>152.72</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-231.33</v>
+        <v>-246.77</v>
       </c>
       <c r="K51" t="n">
-        <v>-32.53</v>
+        <v>-34.7</v>
       </c>
       <c r="L51" t="n">
-        <v>233.61</v>
+        <v>249.2</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>199.01</v>
+        <v>209.13</v>
       </c>
       <c r="K52" t="n">
-        <v>-36.31</v>
+        <v>-38.16</v>
       </c>
       <c r="L52" t="n">
-        <v>202.29</v>
+        <v>212.59</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>27.03</v>
+        <v>29.01</v>
       </c>
       <c r="K53" t="n">
-        <v>438.24</v>
+        <v>470.35</v>
       </c>
       <c r="L53" t="n">
-        <v>439.08</v>
+        <v>471.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>57.74</v>
+        <v>62.14</v>
       </c>
       <c r="K54" t="n">
-        <v>-165.18</v>
+        <v>-177.78</v>
       </c>
       <c r="L54" t="n">
-        <v>174.98</v>
+        <v>188.33</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-18.02</v>
+        <v>-19.07</v>
       </c>
       <c r="K55" t="n">
-        <v>-178.6</v>
+        <v>-189.03</v>
       </c>
       <c r="L55" t="n">
-        <v>179.51</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>44.21</v>
+        <v>48.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-152.96</v>
+        <v>-167.34</v>
       </c>
       <c r="L56" t="n">
-        <v>159.22</v>
+        <v>174.19</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-245.14</v>
+        <v>-265.09</v>
       </c>
       <c r="K57" t="n">
-        <v>-285.43</v>
+        <v>-308.66</v>
       </c>
       <c r="L57" t="n">
-        <v>376.25</v>
+        <v>406.87</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>291.49</v>
+        <v>311.49</v>
       </c>
       <c r="K58" t="n">
-        <v>404.4</v>
+        <v>432.16</v>
       </c>
       <c r="L58" t="n">
-        <v>498.5</v>
+        <v>532.72</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>75.56999999999999</v>
+        <v>72.47</v>
       </c>
       <c r="K59" t="n">
-        <v>22</v>
+        <v>21.1</v>
       </c>
       <c r="L59" t="n">
-        <v>78.70999999999999</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-82.52</v>
+        <v>-81.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-100.49</v>
+        <v>-99.04000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>130.04</v>
+        <v>128.16</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>24.82</v>
+        <v>24.59</v>
       </c>
       <c r="K61" t="n">
-        <v>74.83</v>
+        <v>74.13</v>
       </c>
       <c r="L61" t="n">
-        <v>78.83</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-155.87</v>
+        <v>-160.69</v>
       </c>
       <c r="K62" t="n">
-        <v>65.34999999999999</v>
+        <v>67.37</v>
       </c>
       <c r="L62" t="n">
-        <v>169.02</v>
+        <v>174.24</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>75.94</v>
+        <v>77.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-100.65</v>
+        <v>-102.21</v>
       </c>
       <c r="L63" t="n">
-        <v>126.08</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>180.41</v>
+        <v>186.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-31.33</v>
+        <v>-32.37</v>
       </c>
       <c r="L64" t="n">
-        <v>183.11</v>
+        <v>189.17</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>351.58</v>
+        <v>369.29</v>
       </c>
       <c r="K65" t="n">
-        <v>91.58</v>
+        <v>96.2</v>
       </c>
       <c r="L65" t="n">
-        <v>363.31</v>
+        <v>381.62</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>211.25</v>
+        <v>221.3</v>
       </c>
       <c r="K66" t="n">
-        <v>64.81999999999999</v>
+        <v>67.91</v>
       </c>
       <c r="L66" t="n">
-        <v>220.97</v>
+        <v>231.49</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-127.24</v>
+        <v>-134.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-56.63</v>
+        <v>-59.95</v>
       </c>
       <c r="L67" t="n">
-        <v>139.27</v>
+        <v>147.44</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>197.8</v>
+        <v>211.66</v>
       </c>
       <c r="K68" t="n">
-        <v>29.1</v>
+        <v>31.14</v>
       </c>
       <c r="L68" t="n">
-        <v>199.93</v>
+        <v>213.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-153.4</v>
+        <v>-165.86</v>
       </c>
       <c r="K69" t="n">
-        <v>-227.34</v>
+        <v>-245.8</v>
       </c>
       <c r="L69" t="n">
-        <v>274.25</v>
+        <v>296.52</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-125.97</v>
+        <v>-134.23</v>
       </c>
       <c r="K70" t="n">
-        <v>204.66</v>
+        <v>218.08</v>
       </c>
       <c r="L70" t="n">
-        <v>240.32</v>
+        <v>256.08</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-235.69</v>
+        <v>-257.53</v>
       </c>
       <c r="K71" t="n">
-        <v>-130.72</v>
+        <v>-142.84</v>
       </c>
       <c r="L71" t="n">
-        <v>269.51</v>
+        <v>294.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>224.06</v>
+        <v>243.98</v>
       </c>
       <c r="K72" t="n">
-        <v>49.78</v>
+        <v>54.21</v>
       </c>
       <c r="L72" t="n">
-        <v>229.52</v>
+        <v>249.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>226.83</v>
+        <v>251.51</v>
       </c>
       <c r="K73" t="n">
-        <v>-214.75</v>
+        <v>-238.12</v>
       </c>
       <c r="L73" t="n">
-        <v>312.36</v>
+        <v>346.35</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-42.08</v>
+        <v>-41.76</v>
       </c>
       <c r="K74" t="n">
-        <v>68.72</v>
+        <v>68.19</v>
       </c>
       <c r="L74" t="n">
-        <v>80.58</v>
+        <v>79.95999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>107.37</v>
+        <v>104.05</v>
       </c>
       <c r="K75" t="n">
-        <v>82.15000000000001</v>
+        <v>79.62</v>
       </c>
       <c r="L75" t="n">
-        <v>135.19</v>
+        <v>131.02</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>36.63</v>
+        <v>35.55</v>
       </c>
       <c r="K76" t="n">
-        <v>52.36</v>
+        <v>50.81</v>
       </c>
       <c r="L76" t="n">
-        <v>63.9</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>39.96</v>
+        <v>40.59</v>
       </c>
       <c r="K77" t="n">
-        <v>-85.03</v>
+        <v>-86.36</v>
       </c>
       <c r="L77" t="n">
-        <v>93.95</v>
+        <v>95.43000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>24.46</v>
+        <v>24.73</v>
       </c>
       <c r="K78" t="n">
-        <v>130.03</v>
+        <v>131.47</v>
       </c>
       <c r="L78" t="n">
-        <v>132.31</v>
+        <v>133.78</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-80.28</v>
+        <v>-80.8</v>
       </c>
       <c r="K79" t="n">
-        <v>86.08</v>
+        <v>86.63</v>
       </c>
       <c r="L79" t="n">
-        <v>117.7</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>21.91</v>
+        <v>23.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-157.72</v>
+        <v>-166.8</v>
       </c>
       <c r="L80" t="n">
-        <v>159.23</v>
+        <v>168.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>32.94</v>
+        <v>34.42</v>
       </c>
       <c r="K81" t="n">
-        <v>152.79</v>
+        <v>159.62</v>
       </c>
       <c r="L81" t="n">
-        <v>156.3</v>
+        <v>163.29</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-118.63</v>
+        <v>-125.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-115.13</v>
+        <v>-122.12</v>
       </c>
       <c r="L82" t="n">
-        <v>165.31</v>
+        <v>175.35</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>314.32</v>
+        <v>345.14</v>
       </c>
       <c r="K83" t="n">
-        <v>257.57</v>
+        <v>282.83</v>
       </c>
       <c r="L83" t="n">
-        <v>406.37</v>
+        <v>446.22</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>106.74</v>
+        <v>114.78</v>
       </c>
       <c r="K84" t="n">
-        <v>64.06999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>124.5</v>
+        <v>133.87</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-94.13</v>
+        <v>-101.14</v>
       </c>
       <c r="K85" t="n">
-        <v>111.07</v>
+        <v>119.34</v>
       </c>
       <c r="L85" t="n">
-        <v>145.59</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>463.74</v>
+        <v>506.4</v>
       </c>
       <c r="K86" t="n">
-        <v>212.45</v>
+        <v>232</v>
       </c>
       <c r="L86" t="n">
-        <v>510.09</v>
+        <v>557.02</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-20.34</v>
+        <v>-21.98</v>
       </c>
       <c r="K87" t="n">
-        <v>219.74</v>
+        <v>237.43</v>
       </c>
       <c r="L87" t="n">
-        <v>220.68</v>
+        <v>238.44</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>194.22</v>
+        <v>215.34</v>
       </c>
       <c r="K88" t="n">
-        <v>-81.11</v>
+        <v>-89.93000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>210.48</v>
+        <v>233.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="F14" t="n">
-        <v>7.6</v>
+        <v>7.64</v>
       </c>
       <c r="G14" t="n">
-        <v>108.3</v>
+        <v>98.2</v>
       </c>
       <c r="H14" t="n">
-        <v>28.6</v>
+        <v>25.2</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-33.1</v>
+        <v>93.81</v>
       </c>
       <c r="K14" t="n">
-        <v>50.29</v>
+        <v>-21.35</v>
       </c>
       <c r="L14" t="n">
-        <v>60.21</v>
+        <v>96.20999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:39:04</t>
+          <t>06:38:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="F15" t="n">
-        <v>7.71</v>
+        <v>7.3</v>
       </c>
       <c r="G15" t="n">
-        <v>107.9</v>
+        <v>109.9</v>
       </c>
       <c r="H15" t="n">
-        <v>23.1</v>
+        <v>25.4</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.63</v>
+        <v>-19.22</v>
       </c>
       <c r="K15" t="n">
-        <v>86.76000000000001</v>
+        <v>-56.24</v>
       </c>
       <c r="L15" t="n">
-        <v>98.03</v>
+        <v>59.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:07</t>
+          <t>06:39:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="F16" t="n">
-        <v>7.4</v>
+        <v>7.52</v>
       </c>
       <c r="G16" t="n">
-        <v>101.4</v>
+        <v>113.4</v>
       </c>
       <c r="H16" t="n">
-        <v>30.7</v>
+        <v>25.5</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>29.27</v>
+        <v>22.98</v>
       </c>
       <c r="K16" t="n">
-        <v>63.93</v>
+        <v>40.85</v>
       </c>
       <c r="L16" t="n">
-        <v>70.31</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:46:38</t>
+          <t>06:43:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="F17" t="n">
-        <v>7.59</v>
+        <v>7.88</v>
       </c>
       <c r="G17" t="n">
-        <v>115.8</v>
+        <v>119.1</v>
       </c>
       <c r="H17" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>54.73</v>
+        <v>87.31</v>
       </c>
       <c r="K17" t="n">
-        <v>119.4</v>
+        <v>-2.21</v>
       </c>
       <c r="L17" t="n">
-        <v>131.35</v>
+        <v>87.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:47:38</t>
+          <t>06:45:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="F18" t="n">
-        <v>7.67</v>
+        <v>7.65</v>
       </c>
       <c r="G18" t="n">
-        <v>113.9</v>
+        <v>112.5</v>
       </c>
       <c r="H18" t="n">
-        <v>30.8</v>
+        <v>29.5</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>25.31</v>
+        <v>51.44</v>
       </c>
       <c r="K18" t="n">
-        <v>176.47</v>
+        <v>-46.81</v>
       </c>
       <c r="L18" t="n">
-        <v>178.27</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:49:29</t>
+          <t>06:45:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="F19" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="G19" t="n">
-        <v>107</v>
+        <v>100.1</v>
       </c>
       <c r="H19" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-77.34</v>
+        <v>-0.75</v>
       </c>
       <c r="K19" t="n">
-        <v>-53.84</v>
+        <v>-73.48</v>
       </c>
       <c r="L19" t="n">
-        <v>94.23</v>
+        <v>73.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:55:51</t>
+          <t>06:49:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="F20" t="n">
-        <v>7.18</v>
+        <v>8.41</v>
       </c>
       <c r="G20" t="n">
-        <v>110.4</v>
+        <v>116.3</v>
       </c>
       <c r="H20" t="n">
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
       <c r="I20" t="n">
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>129.77</v>
+        <v>-15.11</v>
       </c>
       <c r="K20" t="n">
-        <v>133.57</v>
+        <v>-93.86</v>
       </c>
       <c r="L20" t="n">
-        <v>186.23</v>
+        <v>95.06999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:57:07</t>
+          <t>06:51:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.22</v>
+        <v>2.52</v>
       </c>
       <c r="F21" t="n">
-        <v>7.31</v>
+        <v>8.07</v>
       </c>
       <c r="G21" t="n">
-        <v>114.1</v>
+        <v>122.4</v>
       </c>
       <c r="H21" t="n">
-        <v>26.2</v>
+        <v>24.9</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-126.75</v>
+        <v>92.44</v>
       </c>
       <c r="K21" t="n">
-        <v>61.42</v>
+        <v>7.1</v>
       </c>
       <c r="L21" t="n">
-        <v>140.84</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:58:44</t>
+          <t>06:52:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="F22" t="n">
-        <v>8.16</v>
+        <v>7.55</v>
       </c>
       <c r="G22" t="n">
-        <v>109.8</v>
+        <v>103.5</v>
       </c>
       <c r="H22" t="n">
-        <v>20.8</v>
+        <v>26.6</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>84.02</v>
+        <v>81.62</v>
       </c>
       <c r="K22" t="n">
-        <v>71.31</v>
+        <v>-30.21</v>
       </c>
       <c r="L22" t="n">
-        <v>110.2</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:03:32</t>
+          <t>06:57:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="F23" t="n">
-        <v>7.98</v>
+        <v>7.92</v>
       </c>
       <c r="G23" t="n">
-        <v>115.4</v>
+        <v>119.3</v>
       </c>
       <c r="H23" t="n">
-        <v>25.6</v>
+        <v>19.7</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>17.1</v>
+        <v>-126.01</v>
       </c>
       <c r="K23" t="n">
-        <v>277.53</v>
+        <v>-14.67</v>
       </c>
       <c r="L23" t="n">
-        <v>278.06</v>
+        <v>126.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:04:55</t>
+          <t>06:59:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="F24" t="n">
         <v>7.74</v>
       </c>
       <c r="G24" t="n">
-        <v>107.3</v>
+        <v>112.3</v>
       </c>
       <c r="H24" t="n">
-        <v>27.8</v>
+        <v>25.2</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>-96.06</v>
+        <v>14.97</v>
       </c>
       <c r="K24" t="n">
-        <v>-160.6</v>
+        <v>129.62</v>
       </c>
       <c r="L24" t="n">
-        <v>187.13</v>
+        <v>130.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:06:52</t>
+          <t>07:01:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.92</v>
+        <v>1.98</v>
       </c>
       <c r="F25" t="n">
-        <v>7.76</v>
+        <v>7.91</v>
       </c>
       <c r="G25" t="n">
-        <v>105.5</v>
+        <v>116.4</v>
       </c>
       <c r="H25" t="n">
-        <v>23.2</v>
+        <v>30.5</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>173.06</v>
+        <v>54.83</v>
       </c>
       <c r="K25" t="n">
-        <v>-37.14</v>
+        <v>57.06</v>
       </c>
       <c r="L25" t="n">
-        <v>177</v>
+        <v>79.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:11:10</t>
+          <t>07:05:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="F26" t="n">
-        <v>7.57</v>
+        <v>7.84</v>
       </c>
       <c r="G26" t="n">
-        <v>109.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>32.8</v>
+        <v>27.4</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-155.56</v>
+        <v>200.12</v>
       </c>
       <c r="K26" t="n">
-        <v>233.04</v>
+        <v>-57.97</v>
       </c>
       <c r="L26" t="n">
-        <v>280.19</v>
+        <v>208.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:13:11</t>
+          <t>07:08:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="F27" t="n">
-        <v>7.28</v>
+        <v>6.66</v>
       </c>
       <c r="G27" t="n">
-        <v>110.5</v>
+        <v>110.6</v>
       </c>
       <c r="H27" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="I27" t="n">
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>170.72</v>
+        <v>74.37</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2</v>
+        <v>13.19</v>
       </c>
       <c r="L27" t="n">
-        <v>170.72</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:14:45</t>
+          <t>07:08:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="F28" t="n">
-        <v>7.04</v>
+        <v>7.62</v>
       </c>
       <c r="G28" t="n">
-        <v>113.9</v>
+        <v>116.8</v>
       </c>
       <c r="H28" t="n">
         <v>25.1</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>154.2</v>
+        <v>59.41</v>
       </c>
       <c r="K28" t="n">
-        <v>257.25</v>
+        <v>1.48</v>
       </c>
       <c r="L28" t="n">
-        <v>299.92</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:24:09</t>
+          <t>07:17:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.49</v>
+        <v>2.76</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>7.72</v>
       </c>
       <c r="G29" t="n">
-        <v>112.2</v>
+        <v>121.4</v>
       </c>
       <c r="H29" t="n">
-        <v>30.6</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.84</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>79.3</v>
+        <v>-32.04</v>
       </c>
       <c r="L29" t="n">
-        <v>85.83</v>
+        <v>73.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:25:52</t>
+          <t>07:20:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="F30" t="n">
-        <v>8.050000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="G30" t="n">
-        <v>117.4</v>
+        <v>98.7</v>
       </c>
       <c r="H30" t="n">
-        <v>29.1</v>
+        <v>27.4</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-55.46</v>
+        <v>-41.97</v>
       </c>
       <c r="K30" t="n">
-        <v>-94.56</v>
+        <v>-41.39</v>
       </c>
       <c r="L30" t="n">
-        <v>109.63</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:27:10</t>
+          <t>07:21:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.37</v>
+        <v>2.66</v>
       </c>
       <c r="F31" t="n">
-        <v>8.09</v>
+        <v>7.69</v>
       </c>
       <c r="G31" t="n">
-        <v>107.8</v>
+        <v>105.1</v>
       </c>
       <c r="H31" t="n">
-        <v>24.8</v>
+        <v>26.2</v>
       </c>
       <c r="I31" t="n">
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.9</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>89.04000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="L31" t="n">
-        <v>92.19</v>
+        <v>91.73999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:30:43</t>
+          <t>07:26:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="F32" t="n">
-        <v>7.47</v>
+        <v>7.87</v>
       </c>
       <c r="G32" t="n">
-        <v>112.2</v>
+        <v>118.9</v>
       </c>
       <c r="H32" t="n">
-        <v>22.9</v>
+        <v>27.5</v>
       </c>
       <c r="I32" t="n">
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>126.19</v>
+        <v>-49.02</v>
       </c>
       <c r="K32" t="n">
-        <v>3.15</v>
+        <v>-50.05</v>
       </c>
       <c r="L32" t="n">
-        <v>126.23</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:32:54</t>
+          <t>07:28:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="F33" t="n">
-        <v>7.26</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>107</v>
+        <v>117.3</v>
       </c>
       <c r="H33" t="n">
-        <v>22.7</v>
+        <v>29.8</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-116.09</v>
+        <v>-57.77</v>
       </c>
       <c r="K33" t="n">
-        <v>36.68</v>
+        <v>4.08</v>
       </c>
       <c r="L33" t="n">
-        <v>121.74</v>
+        <v>57.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:34:52</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="F34" t="n">
-        <v>7.94</v>
+        <v>7.51</v>
       </c>
       <c r="G34" t="n">
-        <v>110.7</v>
+        <v>122.6</v>
       </c>
       <c r="H34" t="n">
-        <v>26.8</v>
+        <v>26.3</v>
       </c>
       <c r="I34" t="n">
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>100.72</v>
+        <v>48.17</v>
       </c>
       <c r="K34" t="n">
-        <v>-102.64</v>
+        <v>6.84</v>
       </c>
       <c r="L34" t="n">
-        <v>143.8</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:39:33</t>
+          <t>07:34:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="F35" t="n">
-        <v>7.31</v>
+        <v>7.8</v>
       </c>
       <c r="G35" t="n">
-        <v>105.4</v>
+        <v>96.8</v>
       </c>
       <c r="H35" t="n">
-        <v>22.8</v>
+        <v>26.6</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>90.25</v>
+        <v>115.54</v>
       </c>
       <c r="K35" t="n">
-        <v>-159.87</v>
+        <v>-29.46</v>
       </c>
       <c r="L35" t="n">
-        <v>183.58</v>
+        <v>119.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:40:26</t>
+          <t>07:36:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.48</v>
+        <v>2.95</v>
       </c>
       <c r="F36" t="n">
-        <v>7.73</v>
+        <v>7.72</v>
       </c>
       <c r="G36" t="n">
-        <v>113.8</v>
+        <v>116.8</v>
       </c>
       <c r="H36" t="n">
-        <v>15.3</v>
+        <v>23.9</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>163.24</v>
+        <v>-42.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-168.96</v>
+        <v>-53.65</v>
       </c>
       <c r="L36" t="n">
-        <v>234.94</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:41:36</t>
+          <t>07:38:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.11</v>
+        <v>3.18</v>
       </c>
       <c r="F37" t="n">
-        <v>7.72</v>
+        <v>7.23</v>
       </c>
       <c r="G37" t="n">
-        <v>114.6</v>
+        <v>118.7</v>
       </c>
       <c r="H37" t="n">
-        <v>22.4</v>
+        <v>29.6</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>66.78</v>
+        <v>100.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-68</v>
+        <v>-81.04000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>95.31</v>
+        <v>128.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:47:52</t>
+          <t>07:43:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1636,31 +1636,31 @@
         <v>2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>7.76</v>
+        <v>7.61</v>
       </c>
       <c r="G38" t="n">
-        <v>84.5</v>
+        <v>117.3</v>
       </c>
       <c r="H38" t="n">
-        <v>18.8</v>
+        <v>20.6</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>252.28</v>
+        <v>-72</v>
       </c>
       <c r="K38" t="n">
-        <v>107.11</v>
+        <v>126.89</v>
       </c>
       <c r="L38" t="n">
-        <v>274.08</v>
+        <v>145.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:49:53</t>
+          <t>07:44:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="F39" t="n">
-        <v>7.79</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>117.5</v>
+        <v>115.9</v>
       </c>
       <c r="H39" t="n">
-        <v>23.8</v>
+        <v>17.9</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>41.73</v>
+        <v>-135.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-201.89</v>
+        <v>-238</v>
       </c>
       <c r="L39" t="n">
-        <v>206.15</v>
+        <v>273.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:51:24</t>
+          <t>07:45:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="F40" t="n">
-        <v>7.8</v>
+        <v>7.42</v>
       </c>
       <c r="G40" t="n">
-        <v>114.3</v>
+        <v>110.8</v>
       </c>
       <c r="H40" t="n">
-        <v>25.6</v>
+        <v>19.2</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-34.47</v>
+        <v>2.38</v>
       </c>
       <c r="K40" t="n">
-        <v>-203.2</v>
+        <v>95.91</v>
       </c>
       <c r="L40" t="n">
-        <v>206.11</v>
+        <v>95.94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:55:28</t>
+          <t>07:50:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.59</v>
+        <v>3.62</v>
       </c>
       <c r="F41" t="n">
         <v>7.45</v>
       </c>
       <c r="G41" t="n">
-        <v>117.6</v>
+        <v>111.8</v>
       </c>
       <c r="H41" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-48.68</v>
+        <v>-132.34</v>
       </c>
       <c r="K41" t="n">
-        <v>-151.73</v>
+        <v>-81.95</v>
       </c>
       <c r="L41" t="n">
-        <v>159.35</v>
+        <v>155.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:58:06</t>
+          <t>07:51:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="F42" t="n">
-        <v>7.28</v>
+        <v>7.22</v>
       </c>
       <c r="G42" t="n">
-        <v>93.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>28.9</v>
+        <v>30.2</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>138.45</v>
+        <v>188.65</v>
       </c>
       <c r="K42" t="n">
-        <v>466.85</v>
+        <v>-129</v>
       </c>
       <c r="L42" t="n">
-        <v>486.95</v>
+        <v>228.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:59:00</t>
+          <t>07:53:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="F43" t="n">
-        <v>7.62</v>
+        <v>7.12</v>
       </c>
       <c r="G43" t="n">
-        <v>102.8</v>
+        <v>111.4</v>
       </c>
       <c r="H43" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>65.52</v>
+        <v>345.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-246.02</v>
+        <v>2.26</v>
       </c>
       <c r="L43" t="n">
-        <v>254.6</v>
+        <v>345.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:09:40</t>
+          <t>08:01:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.65</v>
+        <v>3.19</v>
       </c>
       <c r="F44" t="n">
-        <v>6.96</v>
+        <v>7.08</v>
       </c>
       <c r="G44" t="n">
-        <v>121.7</v>
+        <v>112.8</v>
       </c>
       <c r="H44" t="n">
-        <v>28.8</v>
+        <v>18.4</v>
       </c>
       <c r="I44" t="n">
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-76.79000000000001</v>
+        <v>-72.94</v>
       </c>
       <c r="K44" t="n">
-        <v>5.3</v>
+        <v>-61.98</v>
       </c>
       <c r="L44" t="n">
-        <v>76.97</v>
+        <v>95.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:11:04</t>
+          <t>08:03:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="F45" t="n">
-        <v>7.65</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>106.1</v>
+        <v>111.1</v>
       </c>
       <c r="H45" t="n">
-        <v>24.3</v>
+        <v>20.8</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.7</v>
+        <v>-4.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-130.91</v>
+        <v>30.12</v>
       </c>
       <c r="L45" t="n">
-        <v>131.43</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:12:59</t>
+          <t>08:05:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="F46" t="n">
-        <v>7.4</v>
+        <v>7.91</v>
       </c>
       <c r="G46" t="n">
-        <v>95.8</v>
+        <v>122.3</v>
       </c>
       <c r="H46" t="n">
-        <v>22.8</v>
+        <v>20.1</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.9</v>
+        <v>35.56</v>
       </c>
       <c r="K46" t="n">
-        <v>52.08</v>
+        <v>-0.64</v>
       </c>
       <c r="L46" t="n">
-        <v>52.22</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:16:39</t>
+          <t>08:11:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.13</v>
+        <v>2.51</v>
       </c>
       <c r="F47" t="n">
-        <v>7.15</v>
+        <v>7.81</v>
       </c>
       <c r="G47" t="n">
-        <v>121.1</v>
+        <v>101</v>
       </c>
       <c r="H47" t="n">
-        <v>27.6</v>
+        <v>25.3</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-144.07</v>
+        <v>-18.27</v>
       </c>
       <c r="K47" t="n">
-        <v>-60.65</v>
+        <v>-55.24</v>
       </c>
       <c r="L47" t="n">
-        <v>156.31</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:17:41</t>
+          <t>08:13:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="F48" t="n">
-        <v>7.62</v>
+        <v>7.29</v>
       </c>
       <c r="G48" t="n">
-        <v>113</v>
+        <v>110.5</v>
       </c>
       <c r="H48" t="n">
-        <v>28.5</v>
+        <v>26.2</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>47.02</v>
+        <v>-34.02</v>
       </c>
       <c r="K48" t="n">
-        <v>125.73</v>
+        <v>-72.67</v>
       </c>
       <c r="L48" t="n">
-        <v>134.23</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:19:07</t>
+          <t>08:14:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="F49" t="n">
-        <v>7.12</v>
+        <v>7.44</v>
       </c>
       <c r="G49" t="n">
-        <v>107.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>25.4</v>
+        <v>30.1</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>139.75</v>
+        <v>-32.26</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.38</v>
+        <v>104.21</v>
       </c>
       <c r="L49" t="n">
-        <v>139.82</v>
+        <v>109.09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:24:30</t>
+          <t>08:17:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="F50" t="n">
-        <v>7.51</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>111.4</v>
+        <v>104.7</v>
       </c>
       <c r="H50" t="n">
-        <v>24.3</v>
+        <v>28.1</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>117.43</v>
+        <v>64.77</v>
       </c>
       <c r="K50" t="n">
-        <v>97.65000000000001</v>
+        <v>-58.73</v>
       </c>
       <c r="L50" t="n">
-        <v>152.72</v>
+        <v>87.43000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:26:48</t>
+          <t>08:19:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="F51" t="n">
-        <v>7.3</v>
+        <v>7.74</v>
       </c>
       <c r="G51" t="n">
-        <v>104</v>
+        <v>126.2</v>
       </c>
       <c r="H51" t="n">
-        <v>29.3</v>
+        <v>22.7</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-246.77</v>
+        <v>-34.19</v>
       </c>
       <c r="K51" t="n">
-        <v>-34.7</v>
+        <v>-8.82</v>
       </c>
       <c r="L51" t="n">
-        <v>249.2</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:27:42</t>
+          <t>08:20:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="F52" t="n">
-        <v>7.96</v>
+        <v>7.43</v>
       </c>
       <c r="G52" t="n">
-        <v>120.1</v>
+        <v>125.4</v>
       </c>
       <c r="H52" t="n">
-        <v>30.3</v>
+        <v>24.9</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>209.13</v>
+        <v>-30.63</v>
       </c>
       <c r="K52" t="n">
-        <v>-38.16</v>
+        <v>146.66</v>
       </c>
       <c r="L52" t="n">
-        <v>212.59</v>
+        <v>149.82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:32:10</t>
+          <t>08:25:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="F53" t="n">
-        <v>6.95</v>
+        <v>7.23</v>
       </c>
       <c r="G53" t="n">
-        <v>102.4</v>
+        <v>131</v>
       </c>
       <c r="H53" t="n">
-        <v>25.3</v>
+        <v>20.4</v>
       </c>
       <c r="I53" t="n">
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>29.01</v>
+        <v>154.16</v>
       </c>
       <c r="K53" t="n">
-        <v>470.35</v>
+        <v>-38.11</v>
       </c>
       <c r="L53" t="n">
-        <v>471.24</v>
+        <v>158.81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:34:06</t>
+          <t>08:26:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.35</v>
+        <v>2.77</v>
       </c>
       <c r="F54" t="n">
-        <v>6.96</v>
+        <v>7.43</v>
       </c>
       <c r="G54" t="n">
-        <v>98.5</v>
+        <v>118.6</v>
       </c>
       <c r="H54" t="n">
-        <v>27.2</v>
+        <v>24.7</v>
       </c>
       <c r="I54" t="n">
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>62.14</v>
+        <v>8.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-177.78</v>
+        <v>2.17</v>
       </c>
       <c r="L54" t="n">
-        <v>188.33</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:36:04</t>
+          <t>08:28:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="F55" t="n">
-        <v>7.24</v>
+        <v>7.58</v>
       </c>
       <c r="G55" t="n">
-        <v>107.7</v>
+        <v>124</v>
       </c>
       <c r="H55" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.07</v>
+        <v>-114.16</v>
       </c>
       <c r="K55" t="n">
-        <v>-189.03</v>
+        <v>-42.02</v>
       </c>
       <c r="L55" t="n">
-        <v>189.99</v>
+        <v>121.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:40:50</t>
+          <t>08:32:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2392,31 +2392,31 @@
         <v>2.51</v>
       </c>
       <c r="F56" t="n">
-        <v>7.7</v>
+        <v>7.74</v>
       </c>
       <c r="G56" t="n">
-        <v>91.8</v>
+        <v>112.9</v>
       </c>
       <c r="H56" t="n">
-        <v>23.3</v>
+        <v>18.7</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>48.37</v>
+        <v>-251.92</v>
       </c>
       <c r="K56" t="n">
-        <v>-167.34</v>
+        <v>-233.85</v>
       </c>
       <c r="L56" t="n">
-        <v>174.19</v>
+        <v>343.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:43:22</t>
+          <t>08:34:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="F57" t="n">
-        <v>7.68</v>
+        <v>7.11</v>
       </c>
       <c r="G57" t="n">
-        <v>99</v>
+        <v>101.5</v>
       </c>
       <c r="H57" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="I57" t="n">
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-265.09</v>
+        <v>-220.38</v>
       </c>
       <c r="K57" t="n">
-        <v>-308.66</v>
+        <v>-66.33</v>
       </c>
       <c r="L57" t="n">
-        <v>406.87</v>
+        <v>230.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:45:23</t>
+          <t>08:36:52</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="F58" t="n">
-        <v>7.72</v>
+        <v>7.76</v>
       </c>
       <c r="G58" t="n">
-        <v>111.6</v>
+        <v>102</v>
       </c>
       <c r="H58" t="n">
-        <v>21.7</v>
+        <v>34.4</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>311.49</v>
+        <v>144.18</v>
       </c>
       <c r="K58" t="n">
-        <v>432.16</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>532.72</v>
+        <v>167.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:54:06</t>
+          <t>08:49:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="F59" t="n">
-        <v>7.95</v>
+        <v>7.64</v>
       </c>
       <c r="G59" t="n">
-        <v>108.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>21</v>
+        <v>27.7</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>72.47</v>
+        <v>-42.11</v>
       </c>
       <c r="K59" t="n">
-        <v>21.1</v>
+        <v>-31.5</v>
       </c>
       <c r="L59" t="n">
-        <v>75.48</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:54:48</t>
+          <t>08:50:18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="F60" t="n">
-        <v>7.52</v>
+        <v>7.72</v>
       </c>
       <c r="G60" t="n">
-        <v>103</v>
+        <v>117.4</v>
       </c>
       <c r="H60" t="n">
-        <v>31</v>
+        <v>28.8</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-81.33</v>
+        <v>-27.45</v>
       </c>
       <c r="K60" t="n">
-        <v>-99.04000000000001</v>
+        <v>-23.05</v>
       </c>
       <c r="L60" t="n">
-        <v>128.16</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:56:04</t>
+          <t>08:52:53</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="F61" t="n">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
       <c r="G61" t="n">
-        <v>101.1</v>
+        <v>108.7</v>
       </c>
       <c r="H61" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>24.59</v>
+        <v>-70.94</v>
       </c>
       <c r="K61" t="n">
-        <v>74.13</v>
+        <v>37.07</v>
       </c>
       <c r="L61" t="n">
-        <v>78.09999999999999</v>
+        <v>80.04000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:00:16</t>
+          <t>08:56:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="F62" t="n">
-        <v>7.2</v>
+        <v>8.43</v>
       </c>
       <c r="G62" t="n">
-        <v>121.4</v>
+        <v>112.5</v>
       </c>
       <c r="H62" t="n">
-        <v>26.4</v>
+        <v>23</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-160.69</v>
+        <v>-57.36</v>
       </c>
       <c r="K62" t="n">
-        <v>67.37</v>
+        <v>3.93</v>
       </c>
       <c r="L62" t="n">
-        <v>174.24</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:02:00</t>
+          <t>08:58:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.65</v>
+        <v>3.19</v>
       </c>
       <c r="F63" t="n">
-        <v>7.28</v>
+        <v>7.67</v>
       </c>
       <c r="G63" t="n">
-        <v>116.2</v>
+        <v>101.9</v>
       </c>
       <c r="H63" t="n">
-        <v>32.1</v>
+        <v>25.6</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>77.12</v>
+        <v>77.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-102.21</v>
+        <v>44.74</v>
       </c>
       <c r="L63" t="n">
-        <v>128.04</v>
+        <v>89.12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:02:52</t>
+          <t>09:00:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="F64" t="n">
-        <v>7.39</v>
+        <v>7.17</v>
       </c>
       <c r="G64" t="n">
-        <v>108.3</v>
+        <v>102</v>
       </c>
       <c r="H64" t="n">
-        <v>28.1</v>
+        <v>27</v>
       </c>
       <c r="I64" t="n">
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>186.38</v>
+        <v>23.08</v>
       </c>
       <c r="K64" t="n">
-        <v>-32.37</v>
+        <v>63.51</v>
       </c>
       <c r="L64" t="n">
-        <v>189.17</v>
+        <v>67.56999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:08:22</t>
+          <t>09:05:24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.59</v>
+        <v>2.89</v>
       </c>
       <c r="F65" t="n">
-        <v>7.52</v>
+        <v>8.24</v>
       </c>
       <c r="G65" t="n">
-        <v>119.8</v>
+        <v>101</v>
       </c>
       <c r="H65" t="n">
-        <v>18.6</v>
+        <v>27.9</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>369.29</v>
+        <v>51.92</v>
       </c>
       <c r="K65" t="n">
-        <v>96.2</v>
+        <v>-116.28</v>
       </c>
       <c r="L65" t="n">
-        <v>381.62</v>
+        <v>127.34</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:09:15</t>
+          <t>09:07:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="F66" t="n">
-        <v>8.130000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="G66" t="n">
-        <v>99.8</v>
+        <v>98.3</v>
       </c>
       <c r="H66" t="n">
-        <v>28.1</v>
+        <v>26.7</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>221.3</v>
+        <v>-69.34</v>
       </c>
       <c r="K66" t="n">
-        <v>67.91</v>
+        <v>57.24</v>
       </c>
       <c r="L66" t="n">
-        <v>231.49</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:10:30</t>
+          <t>09:09:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="F67" t="n">
-        <v>7.83</v>
+        <v>6.88</v>
       </c>
       <c r="G67" t="n">
-        <v>97.8</v>
+        <v>112.1</v>
       </c>
       <c r="H67" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="I67" t="n">
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-134.7</v>
+        <v>12.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-59.95</v>
+        <v>94.39</v>
       </c>
       <c r="L67" t="n">
-        <v>147.44</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:14:55</t>
+          <t>09:13:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="F68" t="n">
-        <v>7.73</v>
+        <v>7.85</v>
       </c>
       <c r="G68" t="n">
-        <v>114</v>
+        <v>117.6</v>
       </c>
       <c r="H68" t="n">
-        <v>19.9</v>
+        <v>24.7</v>
       </c>
       <c r="I68" t="n">
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>211.66</v>
+        <v>53.83</v>
       </c>
       <c r="K68" t="n">
-        <v>31.14</v>
+        <v>-158</v>
       </c>
       <c r="L68" t="n">
-        <v>213.94</v>
+        <v>166.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:16:55</t>
+          <t>09:15:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="F69" t="n">
-        <v>7.77</v>
+        <v>8.17</v>
       </c>
       <c r="G69" t="n">
-        <v>102.6</v>
+        <v>112.2</v>
       </c>
       <c r="H69" t="n">
-        <v>28.9</v>
+        <v>26.2</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-165.86</v>
+        <v>37.87</v>
       </c>
       <c r="K69" t="n">
-        <v>-245.8</v>
+        <v>167.97</v>
       </c>
       <c r="L69" t="n">
-        <v>296.52</v>
+        <v>172.18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:18:40</t>
+          <t>09:16:49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.61</v>
+        <v>3.32</v>
       </c>
       <c r="F70" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="G70" t="n">
-        <v>100.3</v>
+        <v>106.2</v>
       </c>
       <c r="H70" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-134.23</v>
+        <v>-157.03</v>
       </c>
       <c r="K70" t="n">
-        <v>218.08</v>
+        <v>104.8</v>
       </c>
       <c r="L70" t="n">
-        <v>256.08</v>
+        <v>188.78</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:22:41</t>
+          <t>09:21:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.64</v>
+        <v>3.07</v>
       </c>
       <c r="F71" t="n">
-        <v>7.82</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>105.6</v>
+        <v>112</v>
       </c>
       <c r="H71" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-257.53</v>
+        <v>-92.14</v>
       </c>
       <c r="K71" t="n">
-        <v>-142.84</v>
+        <v>-50.31</v>
       </c>
       <c r="L71" t="n">
-        <v>294.49</v>
+        <v>104.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:24:11</t>
+          <t>09:22:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="F72" t="n">
-        <v>6.98</v>
+        <v>7.79</v>
       </c>
       <c r="G72" t="n">
-        <v>108.9</v>
+        <v>106.5</v>
       </c>
       <c r="H72" t="n">
-        <v>25</v>
+        <v>22.1</v>
       </c>
       <c r="I72" t="n">
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>243.98</v>
+        <v>-7.36</v>
       </c>
       <c r="K72" t="n">
-        <v>54.21</v>
+        <v>-32.97</v>
       </c>
       <c r="L72" t="n">
-        <v>249.93</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:26:03</t>
+          <t>09:23:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="F73" t="n">
-        <v>8.15</v>
+        <v>7.41</v>
       </c>
       <c r="G73" t="n">
-        <v>105.9</v>
+        <v>110.1</v>
       </c>
       <c r="H73" t="n">
-        <v>34.3</v>
+        <v>25.6</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>251.51</v>
+        <v>107.51</v>
       </c>
       <c r="K73" t="n">
-        <v>-238.12</v>
+        <v>64.63</v>
       </c>
       <c r="L73" t="n">
-        <v>346.35</v>
+        <v>125.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:36:23</t>
+          <t>09:33:25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="F74" t="n">
-        <v>7.51</v>
+        <v>7.47</v>
       </c>
       <c r="G74" t="n">
-        <v>113.2</v>
+        <v>106.5</v>
       </c>
       <c r="H74" t="n">
-        <v>33</v>
+        <v>20.8</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-41.76</v>
+        <v>-20.54</v>
       </c>
       <c r="K74" t="n">
-        <v>68.19</v>
+        <v>-46.52</v>
       </c>
       <c r="L74" t="n">
-        <v>79.95999999999999</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:37:39</t>
+          <t>09:34:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="F75" t="n">
-        <v>8.050000000000001</v>
+        <v>7.24</v>
       </c>
       <c r="G75" t="n">
-        <v>104.9</v>
+        <v>104.4</v>
       </c>
       <c r="H75" t="n">
-        <v>28.3</v>
+        <v>23.4</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>104.05</v>
+        <v>103.35</v>
       </c>
       <c r="K75" t="n">
-        <v>79.62</v>
+        <v>15.08</v>
       </c>
       <c r="L75" t="n">
-        <v>131.02</v>
+        <v>104.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:39:12</t>
+          <t>09:35:31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="F76" t="n">
-        <v>6.31</v>
+        <v>7.83</v>
       </c>
       <c r="G76" t="n">
-        <v>114.5</v>
+        <v>116.2</v>
       </c>
       <c r="H76" t="n">
-        <v>29.3</v>
+        <v>25.4</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>35.55</v>
+        <v>4.01</v>
       </c>
       <c r="K76" t="n">
-        <v>50.81</v>
+        <v>-39.96</v>
       </c>
       <c r="L76" t="n">
-        <v>62.01</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:44:34</t>
+          <t>09:40:43</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="F77" t="n">
-        <v>8.09</v>
+        <v>7.13</v>
       </c>
       <c r="G77" t="n">
-        <v>111.5</v>
+        <v>104.5</v>
       </c>
       <c r="H77" t="n">
-        <v>16.6</v>
+        <v>29.1</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>40.59</v>
+        <v>-64.95</v>
       </c>
       <c r="K77" t="n">
-        <v>-86.36</v>
+        <v>-29</v>
       </c>
       <c r="L77" t="n">
-        <v>95.43000000000001</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:46:16</t>
+          <t>09:42:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.16</v>
+        <v>2.68</v>
       </c>
       <c r="F78" t="n">
-        <v>7.62</v>
+        <v>7.52</v>
       </c>
       <c r="G78" t="n">
-        <v>113.3</v>
+        <v>111.1</v>
       </c>
       <c r="H78" t="n">
-        <v>27.3</v>
+        <v>23.6</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>24.73</v>
+        <v>74.56</v>
       </c>
       <c r="K78" t="n">
-        <v>131.47</v>
+        <v>23.41</v>
       </c>
       <c r="L78" t="n">
-        <v>133.78</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:48:45</t>
+          <t>09:44:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.09</v>
+        <v>2.79</v>
       </c>
       <c r="F79" t="n">
-        <v>7.9</v>
+        <v>7.98</v>
       </c>
       <c r="G79" t="n">
-        <v>110.4</v>
+        <v>118.3</v>
       </c>
       <c r="H79" t="n">
-        <v>21.6</v>
+        <v>18.7</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-80.8</v>
+        <v>79.17</v>
       </c>
       <c r="K79" t="n">
-        <v>86.63</v>
+        <v>34.04</v>
       </c>
       <c r="L79" t="n">
-        <v>118.46</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:52:55</t>
+          <t>09:50:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="F80" t="n">
-        <v>7.39</v>
+        <v>7.5</v>
       </c>
       <c r="G80" t="n">
-        <v>108.1</v>
+        <v>111.1</v>
       </c>
       <c r="H80" t="n">
-        <v>26</v>
+        <v>27.4</v>
       </c>
       <c r="I80" t="n">
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>23.17</v>
+        <v>-117.92</v>
       </c>
       <c r="K80" t="n">
-        <v>-166.8</v>
+        <v>-63.35</v>
       </c>
       <c r="L80" t="n">
-        <v>168.4</v>
+        <v>133.86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:54:32</t>
+          <t>09:51:31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.09</v>
+        <v>3.37</v>
       </c>
       <c r="F81" t="n">
-        <v>7.65</v>
+        <v>7.72</v>
       </c>
       <c r="G81" t="n">
-        <v>106.3</v>
+        <v>111.9</v>
       </c>
       <c r="H81" t="n">
-        <v>26.2</v>
+        <v>28.5</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>34.42</v>
+        <v>73.25</v>
       </c>
       <c r="K81" t="n">
-        <v>159.62</v>
+        <v>111.15</v>
       </c>
       <c r="L81" t="n">
-        <v>163.29</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:56:49</t>
+          <t>09:53:28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="F82" t="n">
-        <v>7.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>113.1</v>
+        <v>105.3</v>
       </c>
       <c r="H82" t="n">
-        <v>28.1</v>
+        <v>29.4</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.84</v>
+        <v>-79.29000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-122.12</v>
+        <v>106.38</v>
       </c>
       <c r="L82" t="n">
-        <v>175.35</v>
+        <v>132.68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:01:47</t>
+          <t>09:58:55</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="F83" t="n">
-        <v>7.71</v>
+        <v>7.35</v>
       </c>
       <c r="G83" t="n">
-        <v>121.9</v>
+        <v>110.7</v>
       </c>
       <c r="H83" t="n">
-        <v>33.5</v>
+        <v>29.1</v>
       </c>
       <c r="I83" t="n">
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>345.14</v>
+        <v>-40.35</v>
       </c>
       <c r="K83" t="n">
-        <v>282.83</v>
+        <v>113.54</v>
       </c>
       <c r="L83" t="n">
-        <v>446.22</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:03:46</t>
+          <t>10:01:11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="F84" t="n">
-        <v>7.53</v>
+        <v>7.55</v>
       </c>
       <c r="G84" t="n">
-        <v>107.7</v>
+        <v>105.1</v>
       </c>
       <c r="H84" t="n">
-        <v>24.2</v>
+        <v>19</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>114.78</v>
+        <v>-167.36</v>
       </c>
       <c r="K84" t="n">
-        <v>68.90000000000001</v>
+        <v>97.02</v>
       </c>
       <c r="L84" t="n">
-        <v>133.87</v>
+        <v>193.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:04:55</t>
+          <t>10:02:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.31</v>
+        <v>2.71</v>
       </c>
       <c r="F85" t="n">
-        <v>8.02</v>
+        <v>7.8</v>
       </c>
       <c r="G85" t="n">
-        <v>111.8</v>
+        <v>118.1</v>
       </c>
       <c r="H85" t="n">
-        <v>20.6</v>
+        <v>28.3</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-101.14</v>
+        <v>113.8</v>
       </c>
       <c r="K85" t="n">
-        <v>119.34</v>
+        <v>-45.86</v>
       </c>
       <c r="L85" t="n">
-        <v>156.43</v>
+        <v>122.69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:09:37</t>
+          <t>10:08:05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.37</v>
+        <v>2.71</v>
       </c>
       <c r="F86" t="n">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
       <c r="G86" t="n">
-        <v>117.6</v>
+        <v>101.1</v>
       </c>
       <c r="H86" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>506.4</v>
+        <v>200.12</v>
       </c>
       <c r="K86" t="n">
-        <v>232</v>
+        <v>-201.1</v>
       </c>
       <c r="L86" t="n">
-        <v>557.02</v>
+        <v>283.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:11:42</t>
+          <t>10:09:10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="F87" t="n">
-        <v>7.85</v>
+        <v>7.49</v>
       </c>
       <c r="G87" t="n">
-        <v>104.6</v>
+        <v>103.1</v>
       </c>
       <c r="H87" t="n">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-21.98</v>
+        <v>154.12</v>
       </c>
       <c r="K87" t="n">
-        <v>237.43</v>
+        <v>-106.15</v>
       </c>
       <c r="L87" t="n">
-        <v>238.44</v>
+        <v>187.14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:12:48</t>
+          <t>10:11:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.93</v>
+        <v>3.28</v>
       </c>
       <c r="F88" t="n">
-        <v>6.95</v>
+        <v>7.9</v>
       </c>
       <c r="G88" t="n">
-        <v>107.4</v>
+        <v>108.4</v>
       </c>
       <c r="H88" t="n">
-        <v>32.5</v>
+        <v>26.8</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>215.34</v>
+        <v>-42.45</v>
       </c>
       <c r="K88" t="n">
-        <v>-89.93000000000001</v>
+        <v>-22.86</v>
       </c>
       <c r="L88" t="n">
-        <v>233.36</v>
+        <v>48.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>93.81</v>
+        <v>89.77</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.35</v>
+        <v>-20.43</v>
       </c>
       <c r="L14" t="n">
-        <v>96.20999999999999</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.22</v>
+        <v>-19.27</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.24</v>
+        <v>-56.38</v>
       </c>
       <c r="L15" t="n">
-        <v>59.44</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>22.98</v>
+        <v>23.52</v>
       </c>
       <c r="K16" t="n">
-        <v>40.85</v>
+        <v>41.81</v>
       </c>
       <c r="L16" t="n">
-        <v>46.87</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>87.31</v>
+        <v>84.8</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.21</v>
+        <v>-2.14</v>
       </c>
       <c r="L17" t="n">
-        <v>87.34</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>51.44</v>
+        <v>51.62</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.81</v>
+        <v>-46.97</v>
       </c>
       <c r="L18" t="n">
-        <v>69.55</v>
+        <v>69.79000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="K19" t="n">
-        <v>-73.48</v>
+        <v>-73.56999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>73.48</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.11</v>
+        <v>-15.21</v>
       </c>
       <c r="K20" t="n">
-        <v>-93.86</v>
+        <v>-94.45</v>
       </c>
       <c r="L20" t="n">
-        <v>95.06999999999999</v>
+        <v>95.66</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>92.44</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>7.1</v>
+        <v>7.15</v>
       </c>
       <c r="L21" t="n">
-        <v>92.70999999999999</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>81.62</v>
+        <v>83.5</v>
       </c>
       <c r="K22" t="n">
-        <v>-30.21</v>
+        <v>-30.91</v>
       </c>
       <c r="L22" t="n">
-        <v>87.03</v>
+        <v>89.04000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-126.01</v>
+        <v>-126.31</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.67</v>
+        <v>-14.71</v>
       </c>
       <c r="L23" t="n">
-        <v>126.86</v>
+        <v>127.16</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>14.97</v>
+        <v>14.96</v>
       </c>
       <c r="K24" t="n">
-        <v>129.62</v>
+        <v>129.59</v>
       </c>
       <c r="L24" t="n">
-        <v>130.48</v>
+        <v>130.45</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>54.83</v>
+        <v>58.52</v>
       </c>
       <c r="K25" t="n">
-        <v>57.06</v>
+        <v>60.9</v>
       </c>
       <c r="L25" t="n">
-        <v>79.13</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>200.12</v>
+        <v>197.32</v>
       </c>
       <c r="K26" t="n">
-        <v>-57.97</v>
+        <v>-57.16</v>
       </c>
       <c r="L26" t="n">
-        <v>208.35</v>
+        <v>205.44</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>74.37</v>
+        <v>72.64</v>
       </c>
       <c r="K27" t="n">
-        <v>13.19</v>
+        <v>12.88</v>
       </c>
       <c r="L27" t="n">
-        <v>75.53</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>59.41</v>
+        <v>58.11</v>
       </c>
       <c r="K28" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="L28" t="n">
-        <v>59.42</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>66.01000000000001</v>
+        <v>64.58</v>
       </c>
       <c r="K29" t="n">
-        <v>-32.04</v>
+        <v>-31.35</v>
       </c>
       <c r="L29" t="n">
-        <v>73.38</v>
+        <v>71.78</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.97</v>
+        <v>-41.34</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.39</v>
+        <v>-40.77</v>
       </c>
       <c r="L30" t="n">
-        <v>58.94</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.960000000000001</v>
+        <v>-8.58</v>
       </c>
       <c r="K31" t="n">
-        <v>91.3</v>
+        <v>87.34</v>
       </c>
       <c r="L31" t="n">
-        <v>91.73999999999999</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-49.02</v>
+        <v>-48.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-50.05</v>
+        <v>-50</v>
       </c>
       <c r="L32" t="n">
-        <v>70.05</v>
+        <v>69.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-57.77</v>
+        <v>-59.15</v>
       </c>
       <c r="K33" t="n">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
       <c r="L33" t="n">
-        <v>57.92</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>48.17</v>
+        <v>50.94</v>
       </c>
       <c r="K34" t="n">
-        <v>6.84</v>
+        <v>7.24</v>
       </c>
       <c r="L34" t="n">
-        <v>48.65</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>115.54</v>
+        <v>113.43</v>
       </c>
       <c r="K35" t="n">
-        <v>-29.46</v>
+        <v>-28.92</v>
       </c>
       <c r="L35" t="n">
-        <v>119.24</v>
+        <v>117.06</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-42.6</v>
+        <v>-45.09</v>
       </c>
       <c r="K36" t="n">
-        <v>-53.65</v>
+        <v>-56.78</v>
       </c>
       <c r="L36" t="n">
-        <v>68.51000000000001</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>100.22</v>
+        <v>98.05</v>
       </c>
       <c r="K37" t="n">
-        <v>-81.04000000000001</v>
+        <v>-79.29000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>128.89</v>
+        <v>126.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-72</v>
+        <v>-71.3</v>
       </c>
       <c r="K38" t="n">
-        <v>126.89</v>
+        <v>125.66</v>
       </c>
       <c r="L38" t="n">
-        <v>145.9</v>
+        <v>144.48</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-135.08</v>
+        <v>-126.38</v>
       </c>
       <c r="K39" t="n">
-        <v>-238</v>
+        <v>-222.67</v>
       </c>
       <c r="L39" t="n">
-        <v>273.66</v>
+        <v>256.04</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="K40" t="n">
-        <v>95.91</v>
+        <v>101.68</v>
       </c>
       <c r="L40" t="n">
-        <v>95.94</v>
+        <v>101.71</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-132.34</v>
+        <v>-140.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-81.95</v>
+        <v>-87.27</v>
       </c>
       <c r="L41" t="n">
-        <v>155.66</v>
+        <v>165.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>188.65</v>
+        <v>184.42</v>
       </c>
       <c r="K42" t="n">
-        <v>-129</v>
+        <v>-126.11</v>
       </c>
       <c r="L42" t="n">
-        <v>228.54</v>
+        <v>223.41</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>345.88</v>
+        <v>325.81</v>
       </c>
       <c r="K43" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="L43" t="n">
-        <v>345.88</v>
+        <v>325.82</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-72.94</v>
+        <v>-69.79000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.98</v>
+        <v>-59.31</v>
       </c>
       <c r="L44" t="n">
-        <v>95.72</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.52</v>
+        <v>-4.92</v>
       </c>
       <c r="K45" t="n">
-        <v>30.12</v>
+        <v>32.75</v>
       </c>
       <c r="L45" t="n">
-        <v>30.46</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>35.56</v>
+        <v>37.35</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.64</v>
+        <v>-0.67</v>
       </c>
       <c r="L46" t="n">
-        <v>35.56</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-18.27</v>
+        <v>-18.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-55.24</v>
+        <v>-56.31</v>
       </c>
       <c r="L47" t="n">
-        <v>58.18</v>
+        <v>59.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-34.02</v>
+        <v>-33.73</v>
       </c>
       <c r="K48" t="n">
-        <v>-72.67</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>80.23999999999999</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-32.26</v>
+        <v>-30.96</v>
       </c>
       <c r="K49" t="n">
-        <v>104.21</v>
+        <v>100.02</v>
       </c>
       <c r="L49" t="n">
-        <v>109.09</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>64.77</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-58.73</v>
+        <v>-59.26</v>
       </c>
       <c r="L50" t="n">
-        <v>87.43000000000001</v>
+        <v>88.22</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-34.19</v>
+        <v>-33.41</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.82</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>35.31</v>
+        <v>34.51</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-30.63</v>
+        <v>-24.84</v>
       </c>
       <c r="K52" t="n">
-        <v>146.66</v>
+        <v>118.92</v>
       </c>
       <c r="L52" t="n">
-        <v>149.82</v>
+        <v>121.49</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>154.16</v>
+        <v>150.38</v>
       </c>
       <c r="K53" t="n">
-        <v>-38.11</v>
+        <v>-37.18</v>
       </c>
       <c r="L53" t="n">
-        <v>158.81</v>
+        <v>154.9</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>8.82</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="L54" t="n">
-        <v>9.09</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-114.16</v>
+        <v>-115.9</v>
       </c>
       <c r="K55" t="n">
-        <v>-42.02</v>
+        <v>-42.66</v>
       </c>
       <c r="L55" t="n">
-        <v>121.65</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-251.92</v>
+        <v>-238.04</v>
       </c>
       <c r="K56" t="n">
-        <v>-233.85</v>
+        <v>-220.96</v>
       </c>
       <c r="L56" t="n">
-        <v>343.74</v>
+        <v>324.79</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-220.38</v>
+        <v>-214.6</v>
       </c>
       <c r="K57" t="n">
-        <v>-66.33</v>
+        <v>-64.59</v>
       </c>
       <c r="L57" t="n">
-        <v>230.14</v>
+        <v>224.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>144.18</v>
+        <v>146.02</v>
       </c>
       <c r="K58" t="n">
-        <v>85.34999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="L58" t="n">
-        <v>167.55</v>
+        <v>169.69</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.11</v>
+        <v>-42.63</v>
       </c>
       <c r="K59" t="n">
-        <v>-31.5</v>
+        <v>-31.89</v>
       </c>
       <c r="L59" t="n">
-        <v>52.58</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-27.45</v>
+        <v>-29.59</v>
       </c>
       <c r="K60" t="n">
-        <v>-23.05</v>
+        <v>-24.84</v>
       </c>
       <c r="L60" t="n">
-        <v>35.84</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-70.94</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>37.07</v>
+        <v>35.67</v>
       </c>
       <c r="L61" t="n">
-        <v>80.04000000000001</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-57.36</v>
+        <v>-58.39</v>
       </c>
       <c r="K62" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="L62" t="n">
-        <v>57.5</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>77.08</v>
+        <v>75.88</v>
       </c>
       <c r="K63" t="n">
-        <v>44.74</v>
+        <v>44.04</v>
       </c>
       <c r="L63" t="n">
-        <v>89.12</v>
+        <v>87.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>23.08</v>
+        <v>23.29</v>
       </c>
       <c r="K64" t="n">
-        <v>63.51</v>
+        <v>64.11</v>
       </c>
       <c r="L64" t="n">
-        <v>67.56999999999999</v>
+        <v>68.20999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>51.92</v>
+        <v>50.44</v>
       </c>
       <c r="K65" t="n">
-        <v>-116.28</v>
+        <v>-112.97</v>
       </c>
       <c r="L65" t="n">
-        <v>127.34</v>
+        <v>123.72</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-69.34</v>
+        <v>-70.89</v>
       </c>
       <c r="K66" t="n">
-        <v>57.24</v>
+        <v>58.52</v>
       </c>
       <c r="L66" t="n">
-        <v>89.91</v>
+        <v>91.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>12.59</v>
+        <v>12.79</v>
       </c>
       <c r="K67" t="n">
-        <v>94.39</v>
+        <v>95.84</v>
       </c>
       <c r="L67" t="n">
-        <v>95.23</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>53.83</v>
+        <v>52.75</v>
       </c>
       <c r="K68" t="n">
-        <v>-158</v>
+        <v>-154.84</v>
       </c>
       <c r="L68" t="n">
-        <v>166.92</v>
+        <v>163.58</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>37.87</v>
+        <v>35.21</v>
       </c>
       <c r="K69" t="n">
-        <v>167.97</v>
+        <v>156.2</v>
       </c>
       <c r="L69" t="n">
-        <v>172.18</v>
+        <v>160.12</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-157.03</v>
+        <v>-152.41</v>
       </c>
       <c r="K70" t="n">
-        <v>104.8</v>
+        <v>101.72</v>
       </c>
       <c r="L70" t="n">
-        <v>188.78</v>
+        <v>183.24</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-92.14</v>
+        <v>-89.89</v>
       </c>
       <c r="K71" t="n">
-        <v>-50.31</v>
+        <v>-49.08</v>
       </c>
       <c r="L71" t="n">
-        <v>104.98</v>
+        <v>102.42</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-7.36</v>
+        <v>-7.22</v>
       </c>
       <c r="K72" t="n">
-        <v>-32.97</v>
+        <v>-32.36</v>
       </c>
       <c r="L72" t="n">
-        <v>33.78</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>107.51</v>
+        <v>113.51</v>
       </c>
       <c r="K73" t="n">
-        <v>64.63</v>
+        <v>68.23</v>
       </c>
       <c r="L73" t="n">
-        <v>125.44</v>
+        <v>132.43</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-20.54</v>
+        <v>-21.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.52</v>
+        <v>-47.71</v>
       </c>
       <c r="L74" t="n">
-        <v>50.85</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>103.35</v>
+        <v>98.5</v>
       </c>
       <c r="K75" t="n">
-        <v>15.08</v>
+        <v>14.37</v>
       </c>
       <c r="L75" t="n">
-        <v>104.44</v>
+        <v>99.54000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>4.01</v>
+        <v>4.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.96</v>
+        <v>-43.29</v>
       </c>
       <c r="L76" t="n">
-        <v>40.16</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-64.95</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-29</v>
+        <v>-29.18</v>
       </c>
       <c r="L77" t="n">
-        <v>71.13</v>
+        <v>71.56999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>74.56</v>
+        <v>74.34</v>
       </c>
       <c r="K78" t="n">
-        <v>23.41</v>
+        <v>23.34</v>
       </c>
       <c r="L78" t="n">
-        <v>78.15000000000001</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>79.17</v>
+        <v>78.11</v>
       </c>
       <c r="K79" t="n">
-        <v>34.04</v>
+        <v>33.59</v>
       </c>
       <c r="L79" t="n">
-        <v>86.18000000000001</v>
+        <v>85.03</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-117.92</v>
+        <v>-115.26</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.35</v>
+        <v>-61.93</v>
       </c>
       <c r="L80" t="n">
-        <v>133.86</v>
+        <v>130.84</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>73.25</v>
+        <v>71.37</v>
       </c>
       <c r="K81" t="n">
-        <v>111.15</v>
+        <v>108.29</v>
       </c>
       <c r="L81" t="n">
-        <v>133.12</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.29000000000001</v>
+        <v>-76.91</v>
       </c>
       <c r="K82" t="n">
-        <v>106.38</v>
+        <v>103.18</v>
       </c>
       <c r="L82" t="n">
-        <v>132.68</v>
+        <v>128.69</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-40.35</v>
+        <v>-41.44</v>
       </c>
       <c r="K83" t="n">
-        <v>113.54</v>
+        <v>116.62</v>
       </c>
       <c r="L83" t="n">
-        <v>120.5</v>
+        <v>123.76</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-167.36</v>
+        <v>-162.69</v>
       </c>
       <c r="K84" t="n">
-        <v>97.02</v>
+        <v>94.31</v>
       </c>
       <c r="L84" t="n">
-        <v>193.44</v>
+        <v>188.05</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>113.8</v>
+        <v>115.24</v>
       </c>
       <c r="K85" t="n">
-        <v>-45.86</v>
+        <v>-46.44</v>
       </c>
       <c r="L85" t="n">
-        <v>122.69</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>200.12</v>
+        <v>192.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-201.1</v>
+        <v>-193.85</v>
       </c>
       <c r="L86" t="n">
-        <v>283.71</v>
+        <v>273.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>154.12</v>
+        <v>156.32</v>
       </c>
       <c r="K87" t="n">
-        <v>-106.15</v>
+        <v>-107.67</v>
       </c>
       <c r="L87" t="n">
-        <v>187.14</v>
+        <v>189.81</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-42.45</v>
+        <v>-41.66</v>
       </c>
       <c r="K88" t="n">
-        <v>-22.86</v>
+        <v>-22.44</v>
       </c>
       <c r="L88" t="n">
-        <v>48.21</v>
+        <v>47.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>89.77</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-20.43</v>
+        <v>-19.38</v>
       </c>
       <c r="L14" t="n">
-        <v>92.06</v>
+        <v>87.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.27</v>
+        <v>-19.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.38</v>
+        <v>-56.54</v>
       </c>
       <c r="L15" t="n">
-        <v>59.58</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>23.52</v>
+        <v>24.14</v>
       </c>
       <c r="K16" t="n">
-        <v>41.81</v>
+        <v>42.91</v>
       </c>
       <c r="L16" t="n">
-        <v>47.97</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>84.8</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.14</v>
+        <v>-2.07</v>
       </c>
       <c r="L17" t="n">
-        <v>84.83</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>51.62</v>
+        <v>51.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.97</v>
+        <v>-47.16</v>
       </c>
       <c r="L18" t="n">
-        <v>69.79000000000001</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -853,10 +853,10 @@
         <v>-0.76</v>
       </c>
       <c r="K19" t="n">
-        <v>-73.56999999999999</v>
+        <v>-73.68000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>73.58</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.21</v>
+        <v>-15.32</v>
       </c>
       <c r="K20" t="n">
-        <v>-94.45</v>
+        <v>-95.12</v>
       </c>
       <c r="L20" t="n">
-        <v>95.66</v>
+        <v>96.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>93.18000000000001</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>7.15</v>
+        <v>7.22</v>
       </c>
       <c r="L21" t="n">
-        <v>93.45999999999999</v>
+        <v>94.31999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>83.5</v>
+        <v>85.66</v>
       </c>
       <c r="K22" t="n">
-        <v>-30.91</v>
+        <v>-31.71</v>
       </c>
       <c r="L22" t="n">
-        <v>89.04000000000001</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-126.31</v>
+        <v>-126.66</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.71</v>
+        <v>-14.75</v>
       </c>
       <c r="L23" t="n">
-        <v>127.16</v>
+        <v>127.51</v>
       </c>
     </row>
     <row r="24">
@@ -1063,10 +1063,10 @@
         <v>14.96</v>
       </c>
       <c r="K24" t="n">
-        <v>129.59</v>
+        <v>129.54</v>
       </c>
       <c r="L24" t="n">
-        <v>130.45</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>58.52</v>
+        <v>62.74</v>
       </c>
       <c r="K25" t="n">
-        <v>60.9</v>
+        <v>65.28</v>
       </c>
       <c r="L25" t="n">
-        <v>84.45999999999999</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>197.32</v>
+        <v>194.13</v>
       </c>
       <c r="K26" t="n">
-        <v>-57.16</v>
+        <v>-56.23</v>
       </c>
       <c r="L26" t="n">
-        <v>205.44</v>
+        <v>202.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>72.64</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>12.88</v>
+        <v>14.09</v>
       </c>
       <c r="L27" t="n">
-        <v>73.77</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>58.11</v>
+        <v>63.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="L28" t="n">
-        <v>58.13</v>
+        <v>63.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>64.58</v>
+        <v>62.94</v>
       </c>
       <c r="K29" t="n">
-        <v>-31.35</v>
+        <v>-30.55</v>
       </c>
       <c r="L29" t="n">
-        <v>71.78</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.34</v>
+        <v>-40.63</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.77</v>
+        <v>-40.07</v>
       </c>
       <c r="L30" t="n">
-        <v>58.06</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.58</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>87.34</v>
+        <v>82.81</v>
       </c>
       <c r="L31" t="n">
-        <v>87.76000000000001</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.97</v>
+        <v>-48.91</v>
       </c>
       <c r="K32" t="n">
-        <v>-50</v>
+        <v>-49.94</v>
       </c>
       <c r="L32" t="n">
-        <v>69.98</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-59.15</v>
+        <v>-60.73</v>
       </c>
       <c r="K33" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
       <c r="L33" t="n">
-        <v>59.3</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>50.94</v>
+        <v>54.12</v>
       </c>
       <c r="K34" t="n">
-        <v>7.24</v>
+        <v>7.69</v>
       </c>
       <c r="L34" t="n">
-        <v>51.46</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>113.43</v>
+        <v>111.03</v>
       </c>
       <c r="K35" t="n">
-        <v>-28.92</v>
+        <v>-28.31</v>
       </c>
       <c r="L35" t="n">
-        <v>117.06</v>
+        <v>114.58</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-45.09</v>
+        <v>-47.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-56.78</v>
+        <v>-60.35</v>
       </c>
       <c r="L36" t="n">
-        <v>72.5</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>98.05</v>
+        <v>95.56</v>
       </c>
       <c r="K37" t="n">
-        <v>-79.29000000000001</v>
+        <v>-77.28</v>
       </c>
       <c r="L37" t="n">
-        <v>126.09</v>
+        <v>122.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-71.3</v>
+        <v>-70.5</v>
       </c>
       <c r="K38" t="n">
-        <v>125.66</v>
+        <v>124.25</v>
       </c>
       <c r="L38" t="n">
-        <v>144.48</v>
+        <v>142.85</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-126.38</v>
+        <v>-116.43</v>
       </c>
       <c r="K39" t="n">
-        <v>-222.67</v>
+        <v>-205.15</v>
       </c>
       <c r="L39" t="n">
-        <v>256.04</v>
+        <v>235.89</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="K40" t="n">
-        <v>101.68</v>
+        <v>108.27</v>
       </c>
       <c r="L40" t="n">
-        <v>101.71</v>
+        <v>108.31</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-140.95</v>
+        <v>-147.89</v>
       </c>
       <c r="K41" t="n">
-        <v>-87.27</v>
+        <v>-91.58</v>
       </c>
       <c r="L41" t="n">
-        <v>165.78</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>184.42</v>
+        <v>179.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-126.11</v>
+        <v>-122.8</v>
       </c>
       <c r="L42" t="n">
-        <v>223.41</v>
+        <v>217.55</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>325.81</v>
+        <v>302.88</v>
       </c>
       <c r="K43" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="L43" t="n">
-        <v>325.82</v>
+        <v>302.89</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-69.79000000000001</v>
+        <v>-66.19</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.31</v>
+        <v>-56.25</v>
       </c>
       <c r="L44" t="n">
-        <v>91.59</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.92</v>
+        <v>-5.37</v>
       </c>
       <c r="K45" t="n">
-        <v>32.75</v>
+        <v>35.76</v>
       </c>
       <c r="L45" t="n">
-        <v>33.12</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>37.35</v>
+        <v>39.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
       <c r="L46" t="n">
-        <v>37.35</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-18.63</v>
+        <v>-19.04</v>
       </c>
       <c r="K47" t="n">
-        <v>-56.31</v>
+        <v>-57.54</v>
       </c>
       <c r="L47" t="n">
-        <v>59.31</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-33.73</v>
+        <v>-33.39</v>
       </c>
       <c r="K48" t="n">
-        <v>-72.04000000000001</v>
+        <v>-71.33</v>
       </c>
       <c r="L48" t="n">
-        <v>79.55</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-30.96</v>
+        <v>-29.48</v>
       </c>
       <c r="K49" t="n">
-        <v>100.02</v>
+        <v>95.23</v>
       </c>
       <c r="L49" t="n">
-        <v>104.7</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>65.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.26</v>
+        <v>-59.86</v>
       </c>
       <c r="L50" t="n">
-        <v>88.22</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-33.41</v>
+        <v>-36.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.619999999999999</v>
+        <v>-9.41</v>
       </c>
       <c r="L51" t="n">
-        <v>34.51</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.84</v>
+        <v>-24.05</v>
       </c>
       <c r="K52" t="n">
-        <v>118.92</v>
+        <v>115.15</v>
       </c>
       <c r="L52" t="n">
-        <v>121.49</v>
+        <v>117.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>150.38</v>
+        <v>146.05</v>
       </c>
       <c r="K53" t="n">
-        <v>-37.18</v>
+        <v>-36.11</v>
       </c>
       <c r="L53" t="n">
-        <v>154.9</v>
+        <v>150.45</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>8.710000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="K54" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="L54" t="n">
-        <v>8.970000000000001</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-115.9</v>
+        <v>-117.89</v>
       </c>
       <c r="K55" t="n">
-        <v>-42.66</v>
+        <v>-43.39</v>
       </c>
       <c r="L55" t="n">
-        <v>123.5</v>
+        <v>125.62</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-238.04</v>
+        <v>-222.17</v>
       </c>
       <c r="K56" t="n">
-        <v>-220.96</v>
+        <v>-206.23</v>
       </c>
       <c r="L56" t="n">
-        <v>324.79</v>
+        <v>303.13</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-214.6</v>
+        <v>-208</v>
       </c>
       <c r="K57" t="n">
-        <v>-64.59</v>
+        <v>-62.6</v>
       </c>
       <c r="L57" t="n">
-        <v>224.11</v>
+        <v>217.22</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>146.02</v>
+        <v>148.11</v>
       </c>
       <c r="K58" t="n">
-        <v>86.44</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>169.69</v>
+        <v>172.12</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.63</v>
+        <v>-43.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-31.89</v>
+        <v>-32.34</v>
       </c>
       <c r="L59" t="n">
-        <v>53.24</v>
+        <v>53.98</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.59</v>
+        <v>-32.04</v>
       </c>
       <c r="K60" t="n">
-        <v>-24.84</v>
+        <v>-26.9</v>
       </c>
       <c r="L60" t="n">
-        <v>38.64</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-68.23999999999999</v>
+        <v>-65.16</v>
       </c>
       <c r="K61" t="n">
-        <v>35.67</v>
+        <v>34.05</v>
       </c>
       <c r="L61" t="n">
-        <v>77</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-58.39</v>
+        <v>-59.56</v>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="L62" t="n">
-        <v>58.52</v>
+        <v>59.69</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>75.88</v>
+        <v>74.5</v>
       </c>
       <c r="K63" t="n">
-        <v>44.04</v>
+        <v>43.24</v>
       </c>
       <c r="L63" t="n">
-        <v>87.73</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>23.29</v>
+        <v>23.54</v>
       </c>
       <c r="K64" t="n">
-        <v>64.11</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>68.20999999999999</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>50.44</v>
+        <v>48.75</v>
       </c>
       <c r="K65" t="n">
-        <v>-112.97</v>
+        <v>-109.19</v>
       </c>
       <c r="L65" t="n">
-        <v>123.72</v>
+        <v>119.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-70.89</v>
+        <v>-72.66</v>
       </c>
       <c r="K66" t="n">
-        <v>58.52</v>
+        <v>59.98</v>
       </c>
       <c r="L66" t="n">
-        <v>91.92</v>
+        <v>94.22</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>12.79</v>
+        <v>13.01</v>
       </c>
       <c r="K67" t="n">
-        <v>95.84</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>96.69</v>
+        <v>98.36</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>52.75</v>
+        <v>51.52</v>
       </c>
       <c r="K68" t="n">
-        <v>-154.84</v>
+        <v>-151.22</v>
       </c>
       <c r="L68" t="n">
-        <v>163.58</v>
+        <v>159.75</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>35.21</v>
+        <v>35.07</v>
       </c>
       <c r="K69" t="n">
-        <v>156.2</v>
+        <v>155.54</v>
       </c>
       <c r="L69" t="n">
-        <v>160.12</v>
+        <v>159.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-152.41</v>
+        <v>-147.05</v>
       </c>
       <c r="K70" t="n">
-        <v>101.72</v>
+        <v>98.14</v>
       </c>
       <c r="L70" t="n">
-        <v>183.24</v>
+        <v>176.79</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-89.89</v>
+        <v>-98.76000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-49.08</v>
+        <v>-53.92</v>
       </c>
       <c r="L71" t="n">
-        <v>102.42</v>
+        <v>112.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-7.22</v>
+        <v>-7.75</v>
       </c>
       <c r="K72" t="n">
-        <v>-32.36</v>
+        <v>-34.75</v>
       </c>
       <c r="L72" t="n">
-        <v>33.16</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>113.51</v>
+        <v>120.35</v>
       </c>
       <c r="K73" t="n">
-        <v>68.23</v>
+        <v>72.34</v>
       </c>
       <c r="L73" t="n">
-        <v>132.43</v>
+        <v>140.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.06</v>
+        <v>-21.67</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.71</v>
+        <v>-49.08</v>
       </c>
       <c r="L74" t="n">
-        <v>52.16</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>98.5</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>14.37</v>
+        <v>13.57</v>
       </c>
       <c r="L75" t="n">
-        <v>99.54000000000001</v>
+        <v>93.95</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>4.34</v>
+        <v>4.72</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.29</v>
+        <v>-47.1</v>
       </c>
       <c r="L76" t="n">
-        <v>43.5</v>
+        <v>47.33</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.34999999999999</v>
+        <v>-65.81</v>
       </c>
       <c r="K77" t="n">
-        <v>-29.18</v>
+        <v>-29.39</v>
       </c>
       <c r="L77" t="n">
-        <v>71.56999999999999</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>74.34</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>23.34</v>
+        <v>23.27</v>
       </c>
       <c r="L78" t="n">
-        <v>77.92</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>78.11</v>
+        <v>76.91</v>
       </c>
       <c r="K79" t="n">
-        <v>33.59</v>
+        <v>33.07</v>
       </c>
       <c r="L79" t="n">
-        <v>85.03</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-115.26</v>
+        <v>-112.22</v>
       </c>
       <c r="K80" t="n">
-        <v>-61.93</v>
+        <v>-60.29</v>
       </c>
       <c r="L80" t="n">
-        <v>130.84</v>
+        <v>127.39</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>71.37</v>
+        <v>69.33</v>
       </c>
       <c r="K81" t="n">
-        <v>108.29</v>
+        <v>105.2</v>
       </c>
       <c r="L81" t="n">
-        <v>129.69</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-76.91</v>
+        <v>-74.18000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>103.18</v>
+        <v>99.52</v>
       </c>
       <c r="L82" t="n">
-        <v>128.69</v>
+        <v>124.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-41.44</v>
+        <v>-42.69</v>
       </c>
       <c r="K83" t="n">
-        <v>116.62</v>
+        <v>120.13</v>
       </c>
       <c r="L83" t="n">
-        <v>123.76</v>
+        <v>127.49</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-162.69</v>
+        <v>-157.36</v>
       </c>
       <c r="K84" t="n">
-        <v>94.31</v>
+        <v>91.22</v>
       </c>
       <c r="L84" t="n">
-        <v>188.05</v>
+        <v>181.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>115.24</v>
+        <v>116.89</v>
       </c>
       <c r="K85" t="n">
-        <v>-46.44</v>
+        <v>-47.11</v>
       </c>
       <c r="L85" t="n">
-        <v>124.25</v>
+        <v>126.03</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>192.91</v>
+        <v>184.66</v>
       </c>
       <c r="K86" t="n">
-        <v>-193.85</v>
+        <v>-185.56</v>
       </c>
       <c r="L86" t="n">
-        <v>273.48</v>
+        <v>261.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>156.32</v>
+        <v>158.84</v>
       </c>
       <c r="K87" t="n">
-        <v>-107.67</v>
+        <v>-109.4</v>
       </c>
       <c r="L87" t="n">
-        <v>189.81</v>
+        <v>192.87</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-41.66</v>
+        <v>-45.06</v>
       </c>
       <c r="K88" t="n">
-        <v>-22.44</v>
+        <v>-24.27</v>
       </c>
       <c r="L88" t="n">
-        <v>47.32</v>
+        <v>51.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -628,25 +628,25 @@
         <v>2.72</v>
       </c>
       <c r="F14" t="n">
-        <v>7.64</v>
+        <v>7.3</v>
       </c>
       <c r="G14" t="n">
-        <v>98.2</v>
+        <v>110.6</v>
       </c>
       <c r="H14" t="n">
-        <v>25.2</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>85.15000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.38</v>
+        <v>-21.05</v>
       </c>
       <c r="L14" t="n">
-        <v>87.33</v>
+        <v>93.81</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>2.67</v>
       </c>
       <c r="F15" t="n">
-        <v>7.3</v>
+        <v>6.71</v>
       </c>
       <c r="G15" t="n">
-        <v>109.9</v>
+        <v>103.9</v>
       </c>
       <c r="H15" t="n">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.32</v>
+        <v>-20.89</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.54</v>
+        <v>-63.62</v>
       </c>
       <c r="L15" t="n">
-        <v>59.75</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>2.3</v>
       </c>
       <c r="F16" t="n">
-        <v>7.52</v>
+        <v>6.34</v>
       </c>
       <c r="G16" t="n">
-        <v>113.4</v>
+        <v>108.3</v>
       </c>
       <c r="H16" t="n">
-        <v>25.5</v>
+        <v>26.7</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>24.14</v>
+        <v>26.88</v>
       </c>
       <c r="K16" t="n">
-        <v>42.91</v>
+        <v>46.32</v>
       </c>
       <c r="L16" t="n">
-        <v>49.23</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>2.32</v>
       </c>
       <c r="F17" t="n">
-        <v>7.88</v>
+        <v>5.39</v>
       </c>
       <c r="G17" t="n">
-        <v>119.1</v>
+        <v>115.5</v>
       </c>
       <c r="H17" t="n">
-        <v>24.2</v>
+        <v>29.5</v>
       </c>
       <c r="I17" t="n">
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>81.93000000000001</v>
+        <v>87.98</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.07</v>
+        <v>-2.69</v>
       </c>
       <c r="L17" t="n">
-        <v>81.95</v>
+        <v>88.02</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.78</v>
       </c>
       <c r="F18" t="n">
-        <v>7.65</v>
+        <v>8.74</v>
       </c>
       <c r="G18" t="n">
-        <v>112.5</v>
+        <v>110.8</v>
       </c>
       <c r="H18" t="n">
-        <v>29.5</v>
+        <v>26.2</v>
       </c>
       <c r="I18" t="n">
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>51.83</v>
+        <v>61.42</v>
       </c>
       <c r="K18" t="n">
-        <v>-47.16</v>
+        <v>-54.63</v>
       </c>
       <c r="L18" t="n">
-        <v>70.06999999999999</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>2.38</v>
       </c>
       <c r="F19" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="G19" t="n">
-        <v>100.1</v>
+        <v>106.4</v>
       </c>
       <c r="H19" t="n">
-        <v>28.7</v>
+        <v>20</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.76</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>-73.68000000000001</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>73.68000000000001</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>2.64</v>
       </c>
       <c r="F20" t="n">
-        <v>8.41</v>
+        <v>6.54</v>
       </c>
       <c r="G20" t="n">
-        <v>116.3</v>
+        <v>126.1</v>
       </c>
       <c r="H20" t="n">
-        <v>23.8</v>
+        <v>28.1</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.32</v>
+        <v>-10.24</v>
       </c>
       <c r="K20" t="n">
-        <v>-95.12</v>
+        <v>-112.31</v>
       </c>
       <c r="L20" t="n">
-        <v>96.34</v>
+        <v>112.78</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>2.52</v>
       </c>
       <c r="F21" t="n">
-        <v>8.07</v>
+        <v>8.74</v>
       </c>
       <c r="G21" t="n">
-        <v>122.4</v>
+        <v>119.2</v>
       </c>
       <c r="H21" t="n">
-        <v>24.9</v>
+        <v>31.1</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>94.04000000000001</v>
+        <v>121.64</v>
       </c>
       <c r="K21" t="n">
-        <v>7.22</v>
+        <v>4.38</v>
       </c>
       <c r="L21" t="n">
-        <v>94.31999999999999</v>
+        <v>121.72</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>2.25</v>
       </c>
       <c r="F22" t="n">
-        <v>7.55</v>
+        <v>6.7</v>
       </c>
       <c r="G22" t="n">
-        <v>103.5</v>
+        <v>108.9</v>
       </c>
       <c r="H22" t="n">
-        <v>26.6</v>
+        <v>21.7</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>85.66</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>-31.71</v>
+        <v>-37.38</v>
       </c>
       <c r="L22" t="n">
-        <v>91.34</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>2.07</v>
       </c>
       <c r="F23" t="n">
-        <v>7.92</v>
+        <v>3.94</v>
       </c>
       <c r="G23" t="n">
-        <v>119.3</v>
+        <v>116.3</v>
       </c>
       <c r="H23" t="n">
-        <v>19.7</v>
+        <v>29.6</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-126.66</v>
+        <v>-125.7</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.75</v>
+        <v>-23.16</v>
       </c>
       <c r="L23" t="n">
-        <v>127.51</v>
+        <v>127.81</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>2.16</v>
       </c>
       <c r="F24" t="n">
-        <v>7.74</v>
+        <v>5.91</v>
       </c>
       <c r="G24" t="n">
-        <v>112.3</v>
+        <v>112.6</v>
       </c>
       <c r="H24" t="n">
-        <v>25.2</v>
+        <v>26.1</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>14.96</v>
+        <v>34.17</v>
       </c>
       <c r="K24" t="n">
-        <v>129.54</v>
+        <v>146.53</v>
       </c>
       <c r="L24" t="n">
-        <v>130.4</v>
+        <v>150.46</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>1.98</v>
       </c>
       <c r="F25" t="n">
-        <v>7.91</v>
+        <v>3.32</v>
       </c>
       <c r="G25" t="n">
-        <v>116.4</v>
+        <v>116.2</v>
       </c>
       <c r="H25" t="n">
-        <v>30.5</v>
+        <v>28.2</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>62.74</v>
+        <v>81.08</v>
       </c>
       <c r="K25" t="n">
-        <v>65.28</v>
+        <v>51.29</v>
       </c>
       <c r="L25" t="n">
-        <v>90.54000000000001</v>
+        <v>95.94</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>1.93</v>
       </c>
       <c r="F26" t="n">
-        <v>7.84</v>
+        <v>6.24</v>
       </c>
       <c r="G26" t="n">
-        <v>98.59999999999999</v>
+        <v>114.7</v>
       </c>
       <c r="H26" t="n">
-        <v>27.4</v>
+        <v>19.2</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>194.13</v>
+        <v>236.56</v>
       </c>
       <c r="K26" t="n">
-        <v>-56.23</v>
+        <v>-76.89</v>
       </c>
       <c r="L26" t="n">
-        <v>202.11</v>
+        <v>248.74</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>2.55</v>
       </c>
       <c r="F27" t="n">
-        <v>6.66</v>
+        <v>2.85</v>
       </c>
       <c r="G27" t="n">
-        <v>110.6</v>
+        <v>91</v>
       </c>
       <c r="H27" t="n">
-        <v>23.5</v>
+        <v>25.2</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>79.45999999999999</v>
+        <v>146.49</v>
       </c>
       <c r="K27" t="n">
-        <v>14.09</v>
+        <v>22.8</v>
       </c>
       <c r="L27" t="n">
-        <v>80.7</v>
+        <v>148.26</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.69</v>
       </c>
       <c r="F28" t="n">
-        <v>7.62</v>
+        <v>7.34</v>
       </c>
       <c r="G28" t="n">
-        <v>116.8</v>
+        <v>110.3</v>
       </c>
       <c r="H28" t="n">
-        <v>25.1</v>
+        <v>28.4</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>63.2</v>
+        <v>169.44</v>
       </c>
       <c r="K28" t="n">
-        <v>1.57</v>
+        <v>-29.72</v>
       </c>
       <c r="L28" t="n">
-        <v>63.22</v>
+        <v>172.02</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.76</v>
       </c>
       <c r="F29" t="n">
-        <v>7.72</v>
+        <v>5.85</v>
       </c>
       <c r="G29" t="n">
-        <v>121.4</v>
+        <v>112.2</v>
       </c>
       <c r="H29" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I29" t="n">
         <v>21</v>
       </c>
-      <c r="I29" t="n">
-        <v>17</v>
-      </c>
       <c r="J29" t="n">
-        <v>62.94</v>
+        <v>62.31</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.55</v>
+        <v>-30.06</v>
       </c>
       <c r="L29" t="n">
-        <v>69.95999999999999</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>2.35</v>
       </c>
       <c r="F30" t="n">
-        <v>7.78</v>
+        <v>7.45</v>
       </c>
       <c r="G30" t="n">
-        <v>98.7</v>
+        <v>113.5</v>
       </c>
       <c r="H30" t="n">
-        <v>27.4</v>
+        <v>19.3</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-40.63</v>
+        <v>-45.07</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.07</v>
+        <v>-45.26</v>
       </c>
       <c r="L30" t="n">
-        <v>57.06</v>
+        <v>63.87</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>2.66</v>
       </c>
       <c r="F31" t="n">
-        <v>7.69</v>
+        <v>6.76</v>
       </c>
       <c r="G31" t="n">
-        <v>105.1</v>
+        <v>111.8</v>
       </c>
       <c r="H31" t="n">
-        <v>26.2</v>
+        <v>22.5</v>
       </c>
       <c r="I31" t="n">
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.130000000000001</v>
+        <v>-8.18</v>
       </c>
       <c r="K31" t="n">
-        <v>82.81</v>
+        <v>87.7</v>
       </c>
       <c r="L31" t="n">
-        <v>83.2</v>
+        <v>88.08</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>2.59</v>
       </c>
       <c r="F32" t="n">
-        <v>7.87</v>
+        <v>8.18</v>
       </c>
       <c r="G32" t="n">
-        <v>118.9</v>
+        <v>115.3</v>
       </c>
       <c r="H32" t="n">
-        <v>27.5</v>
+        <v>29.4</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.91</v>
+        <v>-59.62</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.94</v>
+        <v>-63.9</v>
       </c>
       <c r="L32" t="n">
-        <v>69.91</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>2.53</v>
       </c>
       <c r="F33" t="n">
-        <v>8.109999999999999</v>
+        <v>5.99</v>
       </c>
       <c r="G33" t="n">
-        <v>117.3</v>
+        <v>120</v>
       </c>
       <c r="H33" t="n">
-        <v>29.8</v>
+        <v>28.6</v>
       </c>
       <c r="I33" t="n">
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-60.73</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>4.29</v>
+        <v>3.51</v>
       </c>
       <c r="L33" t="n">
-        <v>60.88</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>2.68</v>
       </c>
       <c r="F34" t="n">
-        <v>7.51</v>
+        <v>7.95</v>
       </c>
       <c r="G34" t="n">
-        <v>122.6</v>
+        <v>108.2</v>
       </c>
       <c r="H34" t="n">
-        <v>26.3</v>
+        <v>31.2</v>
       </c>
       <c r="I34" t="n">
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>54.12</v>
+        <v>65.75</v>
       </c>
       <c r="K34" t="n">
-        <v>7.69</v>
+        <v>8.41</v>
       </c>
       <c r="L34" t="n">
-        <v>54.66</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>2.78</v>
       </c>
       <c r="F35" t="n">
-        <v>7.8</v>
+        <v>6.02</v>
       </c>
       <c r="G35" t="n">
-        <v>96.8</v>
+        <v>114</v>
       </c>
       <c r="H35" t="n">
-        <v>26.6</v>
+        <v>18.3</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>111.03</v>
+        <v>119.97</v>
       </c>
       <c r="K35" t="n">
-        <v>-28.31</v>
+        <v>-33.38</v>
       </c>
       <c r="L35" t="n">
-        <v>114.58</v>
+        <v>124.52</v>
       </c>
     </row>
     <row r="36">
@@ -1555,22 +1555,22 @@
         <v>7.72</v>
       </c>
       <c r="G36" t="n">
-        <v>116.8</v>
+        <v>112.2</v>
       </c>
       <c r="H36" t="n">
-        <v>23.9</v>
+        <v>28.4</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-47.92</v>
+        <v>-43.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-60.35</v>
+        <v>-84.75</v>
       </c>
       <c r="L36" t="n">
-        <v>77.06999999999999</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.18</v>
       </c>
       <c r="F37" t="n">
-        <v>7.23</v>
+        <v>6.75</v>
       </c>
       <c r="G37" t="n">
-        <v>118.7</v>
+        <v>102.5</v>
       </c>
       <c r="H37" t="n">
-        <v>29.6</v>
+        <v>29.3</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>95.56</v>
+        <v>111.41</v>
       </c>
       <c r="K37" t="n">
-        <v>-77.28</v>
+        <v>-82.92</v>
       </c>
       <c r="L37" t="n">
-        <v>122.9</v>
+        <v>138.88</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>7.61</v>
+        <v>5.12</v>
       </c>
       <c r="G38" t="n">
-        <v>117.3</v>
+        <v>110.1</v>
       </c>
       <c r="H38" t="n">
-        <v>20.6</v>
+        <v>28.6</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-70.5</v>
+        <v>-57.38</v>
       </c>
       <c r="K38" t="n">
-        <v>124.25</v>
+        <v>126.16</v>
       </c>
       <c r="L38" t="n">
-        <v>142.85</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>2.55</v>
       </c>
       <c r="F39" t="n">
-        <v>8.029999999999999</v>
+        <v>7.07</v>
       </c>
       <c r="G39" t="n">
-        <v>115.9</v>
+        <v>118.5</v>
       </c>
       <c r="H39" t="n">
-        <v>17.9</v>
+        <v>27.9</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-116.43</v>
+        <v>-113.52</v>
       </c>
       <c r="K39" t="n">
-        <v>-205.15</v>
+        <v>-223.73</v>
       </c>
       <c r="L39" t="n">
-        <v>235.89</v>
+        <v>250.88</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.78</v>
       </c>
       <c r="F40" t="n">
-        <v>7.42</v>
+        <v>5.3</v>
       </c>
       <c r="G40" t="n">
-        <v>110.8</v>
+        <v>106.3</v>
       </c>
       <c r="H40" t="n">
-        <v>19.2</v>
+        <v>25.3</v>
       </c>
       <c r="I40" t="n">
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>2.69</v>
+        <v>43.97</v>
       </c>
       <c r="K40" t="n">
-        <v>108.27</v>
+        <v>109.2</v>
       </c>
       <c r="L40" t="n">
-        <v>108.31</v>
+        <v>117.72</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>3.62</v>
       </c>
       <c r="F41" t="n">
-        <v>7.45</v>
+        <v>7.23</v>
       </c>
       <c r="G41" t="n">
-        <v>111.8</v>
+        <v>106.9</v>
       </c>
       <c r="H41" t="n">
-        <v>24.7</v>
+        <v>25.9</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-147.89</v>
+        <v>-116.65</v>
       </c>
       <c r="K41" t="n">
-        <v>-91.58</v>
+        <v>-131.48</v>
       </c>
       <c r="L41" t="n">
-        <v>173.95</v>
+        <v>175.77</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>2.86</v>
       </c>
       <c r="F42" t="n">
-        <v>7.22</v>
+        <v>8.74</v>
       </c>
       <c r="G42" t="n">
-        <v>97.40000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="H42" t="n">
-        <v>30.2</v>
+        <v>18.7</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>179.58</v>
+        <v>240.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-122.8</v>
+        <v>-149.53</v>
       </c>
       <c r="L42" t="n">
-        <v>217.55</v>
+        <v>282.98</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>2.69</v>
       </c>
       <c r="F43" t="n">
-        <v>7.12</v>
+        <v>7.99</v>
       </c>
       <c r="G43" t="n">
-        <v>111.4</v>
+        <v>100.2</v>
       </c>
       <c r="H43" t="n">
-        <v>22.3</v>
+        <v>25.6</v>
       </c>
       <c r="I43" t="n">
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>302.88</v>
+        <v>349.35</v>
       </c>
       <c r="K43" t="n">
-        <v>1.98</v>
+        <v>-0.15</v>
       </c>
       <c r="L43" t="n">
-        <v>302.89</v>
+        <v>349.35</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>3.19</v>
       </c>
       <c r="F44" t="n">
-        <v>7.08</v>
+        <v>6.2</v>
       </c>
       <c r="G44" t="n">
-        <v>112.8</v>
+        <v>99.5</v>
       </c>
       <c r="H44" t="n">
-        <v>18.4</v>
+        <v>26.3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-66.19</v>
+        <v>-70.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-56.25</v>
+        <v>-60.63</v>
       </c>
       <c r="L44" t="n">
-        <v>86.86</v>
+        <v>93.16</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.47</v>
       </c>
       <c r="F45" t="n">
-        <v>8.050000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="G45" t="n">
-        <v>111.1</v>
+        <v>119</v>
       </c>
       <c r="H45" t="n">
-        <v>20.8</v>
+        <v>25.5</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.37</v>
+        <v>-5.11</v>
       </c>
       <c r="K45" t="n">
-        <v>35.76</v>
+        <v>42.2</v>
       </c>
       <c r="L45" t="n">
-        <v>36.16</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2.33</v>
       </c>
       <c r="F46" t="n">
-        <v>7.91</v>
+        <v>4.54</v>
       </c>
       <c r="G46" t="n">
-        <v>122.3</v>
+        <v>116.1</v>
       </c>
       <c r="H46" t="n">
-        <v>20.1</v>
+        <v>31.1</v>
       </c>
       <c r="I46" t="n">
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>39.39</v>
+        <v>43.36</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.71</v>
+        <v>-1.04</v>
       </c>
       <c r="L46" t="n">
-        <v>39.39</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>2.51</v>
       </c>
       <c r="F47" t="n">
-        <v>7.81</v>
+        <v>8.74</v>
       </c>
       <c r="G47" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H47" t="n">
-        <v>25.3</v>
+        <v>20.4</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-19.04</v>
+        <v>-21.85</v>
       </c>
       <c r="K47" t="n">
-        <v>-57.54</v>
+        <v>-74.17</v>
       </c>
       <c r="L47" t="n">
-        <v>60.61</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>2.88</v>
       </c>
       <c r="F48" t="n">
-        <v>7.29</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>110.5</v>
+        <v>103.6</v>
       </c>
       <c r="H48" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-33.39</v>
+        <v>-34.16</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.33</v>
+        <v>-77.98999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>78.76000000000001</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>2.98</v>
       </c>
       <c r="F49" t="n">
-        <v>7.44</v>
+        <v>5.24</v>
       </c>
       <c r="G49" t="n">
-        <v>95.90000000000001</v>
+        <v>106.8</v>
       </c>
       <c r="H49" t="n">
-        <v>30.1</v>
+        <v>17.9</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-29.48</v>
+        <v>-28.45</v>
       </c>
       <c r="K49" t="n">
-        <v>95.23</v>
+        <v>96.05</v>
       </c>
       <c r="L49" t="n">
-        <v>99.68000000000001</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.69</v>
       </c>
       <c r="F50" t="n">
-        <v>8.029999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G50" t="n">
-        <v>104.7</v>
+        <v>118.5</v>
       </c>
       <c r="H50" t="n">
-        <v>28.1</v>
+        <v>22.3</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>66.01000000000001</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.86</v>
+        <v>-78.59</v>
       </c>
       <c r="L50" t="n">
-        <v>89.11</v>
+        <v>117.94</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>2.83</v>
       </c>
       <c r="F51" t="n">
-        <v>7.74</v>
+        <v>8.74</v>
       </c>
       <c r="G51" t="n">
-        <v>126.2</v>
+        <v>112.6</v>
       </c>
       <c r="H51" t="n">
-        <v>22.7</v>
+        <v>33</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-36.47</v>
+        <v>-15.28</v>
       </c>
       <c r="K51" t="n">
-        <v>-9.41</v>
+        <v>-13.84</v>
       </c>
       <c r="L51" t="n">
-        <v>37.67</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>2.57</v>
       </c>
       <c r="F52" t="n">
-        <v>7.43</v>
+        <v>7.3</v>
       </c>
       <c r="G52" t="n">
-        <v>125.4</v>
+        <v>106.4</v>
       </c>
       <c r="H52" t="n">
-        <v>24.9</v>
+        <v>32.7</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.05</v>
+        <v>-20.82</v>
       </c>
       <c r="K52" t="n">
-        <v>115.15</v>
+        <v>134.39</v>
       </c>
       <c r="L52" t="n">
-        <v>117.64</v>
+        <v>135.99</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>2.38</v>
       </c>
       <c r="F53" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="G53" t="n">
-        <v>131</v>
+        <v>102.5</v>
       </c>
       <c r="H53" t="n">
-        <v>20.4</v>
+        <v>35.5</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>146.05</v>
+        <v>174.77</v>
       </c>
       <c r="K53" t="n">
-        <v>-36.11</v>
+        <v>-38.9</v>
       </c>
       <c r="L53" t="n">
-        <v>150.45</v>
+        <v>179.05</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>2.77</v>
       </c>
       <c r="F54" t="n">
-        <v>7.43</v>
+        <v>7.83</v>
       </c>
       <c r="G54" t="n">
-        <v>118.6</v>
+        <v>106.5</v>
       </c>
       <c r="H54" t="n">
-        <v>24.7</v>
+        <v>29.2</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>9.15</v>
+        <v>93.84</v>
       </c>
       <c r="K54" t="n">
-        <v>2.25</v>
+        <v>-7.35</v>
       </c>
       <c r="L54" t="n">
-        <v>9.42</v>
+        <v>94.13</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.79</v>
       </c>
       <c r="F55" t="n">
-        <v>7.58</v>
+        <v>6.53</v>
       </c>
       <c r="G55" t="n">
-        <v>124</v>
+        <v>109.6</v>
       </c>
       <c r="H55" t="n">
-        <v>23.9</v>
+        <v>32</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-117.89</v>
+        <v>-111.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-43.39</v>
+        <v>-57.06</v>
       </c>
       <c r="L55" t="n">
-        <v>125.62</v>
+        <v>125.19</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>2.51</v>
       </c>
       <c r="F56" t="n">
-        <v>7.74</v>
+        <v>4.57</v>
       </c>
       <c r="G56" t="n">
-        <v>112.9</v>
+        <v>112.6</v>
       </c>
       <c r="H56" t="n">
-        <v>18.7</v>
+        <v>26.4</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-222.17</v>
+        <v>-186.83</v>
       </c>
       <c r="K56" t="n">
-        <v>-206.23</v>
+        <v>-203.26</v>
       </c>
       <c r="L56" t="n">
-        <v>303.13</v>
+        <v>276.08</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>2.79</v>
       </c>
       <c r="F57" t="n">
-        <v>7.11</v>
+        <v>6.93</v>
       </c>
       <c r="G57" t="n">
-        <v>101.5</v>
+        <v>100.1</v>
       </c>
       <c r="H57" t="n">
-        <v>23.2</v>
+        <v>20.7</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-208</v>
+        <v>-212.68</v>
       </c>
       <c r="K57" t="n">
-        <v>-62.6</v>
+        <v>-81</v>
       </c>
       <c r="L57" t="n">
-        <v>217.22</v>
+        <v>227.58</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>2.6</v>
       </c>
       <c r="F58" t="n">
-        <v>7.76</v>
+        <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>102</v>
+        <v>113.2</v>
       </c>
       <c r="H58" t="n">
-        <v>34.4</v>
+        <v>21</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>148.11</v>
+        <v>196.33</v>
       </c>
       <c r="K58" t="n">
-        <v>87.68000000000001</v>
+        <v>69.84</v>
       </c>
       <c r="L58" t="n">
-        <v>172.12</v>
+        <v>208.38</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>2.75</v>
       </c>
       <c r="F59" t="n">
-        <v>7.64</v>
+        <v>8.74</v>
       </c>
       <c r="G59" t="n">
-        <v>98.59999999999999</v>
+        <v>110.7</v>
       </c>
       <c r="H59" t="n">
-        <v>27.7</v>
+        <v>19.2</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.23</v>
+        <v>-47.86</v>
       </c>
       <c r="K59" t="n">
-        <v>-32.34</v>
+        <v>-36.91</v>
       </c>
       <c r="L59" t="n">
-        <v>53.98</v>
+        <v>60.44</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>2.79</v>
       </c>
       <c r="F60" t="n">
-        <v>7.72</v>
+        <v>8.74</v>
       </c>
       <c r="G60" t="n">
-        <v>117.4</v>
+        <v>112.2</v>
       </c>
       <c r="H60" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-32.04</v>
+        <v>-39.88</v>
       </c>
       <c r="K60" t="n">
-        <v>-26.9</v>
+        <v>-35.76</v>
       </c>
       <c r="L60" t="n">
-        <v>41.83</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>2.62</v>
       </c>
       <c r="F61" t="n">
-        <v>7.28</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>108.7</v>
+        <v>103.4</v>
       </c>
       <c r="H61" t="n">
-        <v>31.1</v>
+        <v>24.3</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-65.16</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>34.05</v>
+        <v>40.96</v>
       </c>
       <c r="L61" t="n">
-        <v>73.52</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>2.47</v>
       </c>
       <c r="F62" t="n">
-        <v>8.43</v>
+        <v>6.39</v>
       </c>
       <c r="G62" t="n">
-        <v>112.5</v>
+        <v>126.6</v>
       </c>
       <c r="H62" t="n">
-        <v>23</v>
+        <v>26.2</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-59.56</v>
+        <v>-69.27</v>
       </c>
       <c r="K62" t="n">
-        <v>4.08</v>
+        <v>3.02</v>
       </c>
       <c r="L62" t="n">
-        <v>59.69</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.19</v>
       </c>
       <c r="F63" t="n">
-        <v>7.67</v>
+        <v>8.74</v>
       </c>
       <c r="G63" t="n">
-        <v>101.9</v>
+        <v>111.3</v>
       </c>
       <c r="H63" t="n">
-        <v>25.6</v>
+        <v>20.9</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>74.5</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>43.24</v>
+        <v>46.91</v>
       </c>
       <c r="L63" t="n">
-        <v>86.14</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>2.5</v>
       </c>
       <c r="F64" t="n">
-        <v>7.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>102</v>
+        <v>101.3</v>
       </c>
       <c r="H64" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>23.54</v>
+        <v>28.33</v>
       </c>
       <c r="K64" t="n">
-        <v>64.79000000000001</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>68.94</v>
+        <v>76.98</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>2.89</v>
       </c>
       <c r="F65" t="n">
-        <v>8.24</v>
+        <v>7.31</v>
       </c>
       <c r="G65" t="n">
-        <v>101</v>
+        <v>122.8</v>
       </c>
       <c r="H65" t="n">
-        <v>27.9</v>
+        <v>20.5</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>48.75</v>
+        <v>56.79</v>
       </c>
       <c r="K65" t="n">
-        <v>-109.19</v>
+        <v>-120.87</v>
       </c>
       <c r="L65" t="n">
-        <v>119.58</v>
+        <v>133.55</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.01</v>
       </c>
       <c r="F66" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>98.3</v>
+        <v>112.1</v>
       </c>
       <c r="H66" t="n">
-        <v>26.7</v>
+        <v>19.1</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-72.66</v>
+        <v>-74.55</v>
       </c>
       <c r="K66" t="n">
-        <v>59.98</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>94.22</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>2.83</v>
       </c>
       <c r="F67" t="n">
-        <v>6.88</v>
+        <v>8.74</v>
       </c>
       <c r="G67" t="n">
-        <v>112.1</v>
+        <v>95.5</v>
       </c>
       <c r="H67" t="n">
-        <v>32.5</v>
+        <v>26</v>
       </c>
       <c r="I67" t="n">
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>13.01</v>
+        <v>26.87</v>
       </c>
       <c r="K67" t="n">
-        <v>97.48999999999999</v>
+        <v>112</v>
       </c>
       <c r="L67" t="n">
-        <v>98.36</v>
+        <v>115.18</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>2.89</v>
       </c>
       <c r="F68" t="n">
-        <v>7.85</v>
+        <v>8.4</v>
       </c>
       <c r="G68" t="n">
-        <v>117.6</v>
+        <v>114.8</v>
       </c>
       <c r="H68" t="n">
-        <v>24.7</v>
+        <v>28.7</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>51.52</v>
+        <v>78.22</v>
       </c>
       <c r="K68" t="n">
-        <v>-151.22</v>
+        <v>-181.01</v>
       </c>
       <c r="L68" t="n">
-        <v>159.75</v>
+        <v>197.19</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>2.97</v>
       </c>
       <c r="F69" t="n">
-        <v>8.17</v>
+        <v>8.74</v>
       </c>
       <c r="G69" t="n">
-        <v>112.2</v>
+        <v>121.2</v>
       </c>
       <c r="H69" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>35.07</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>155.54</v>
+        <v>178.66</v>
       </c>
       <c r="L69" t="n">
-        <v>159.45</v>
+        <v>191.64</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>3.32</v>
       </c>
       <c r="F70" t="n">
-        <v>7.78</v>
+        <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>106.2</v>
+        <v>113.5</v>
       </c>
       <c r="H70" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-147.05</v>
+        <v>-152.65</v>
       </c>
       <c r="K70" t="n">
-        <v>98.14</v>
+        <v>105.01</v>
       </c>
       <c r="L70" t="n">
-        <v>176.79</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>3.07</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H71" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="I71" t="n">
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-98.76000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K71" t="n">
-        <v>-53.92</v>
+        <v>-139.27</v>
       </c>
       <c r="L71" t="n">
-        <v>112.52</v>
+        <v>139.27</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.1</v>
       </c>
       <c r="F72" t="n">
-        <v>7.79</v>
+        <v>7.95</v>
       </c>
       <c r="G72" t="n">
-        <v>106.5</v>
+        <v>113.7</v>
       </c>
       <c r="H72" t="n">
-        <v>22.1</v>
+        <v>23.2</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-7.75</v>
+        <v>104.68</v>
       </c>
       <c r="K72" t="n">
-        <v>-34.75</v>
+        <v>-122.94</v>
       </c>
       <c r="L72" t="n">
-        <v>35.61</v>
+        <v>161.47</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>2.53</v>
       </c>
       <c r="F73" t="n">
-        <v>7.41</v>
+        <v>7.71</v>
       </c>
       <c r="G73" t="n">
-        <v>110.1</v>
+        <v>106.1</v>
       </c>
       <c r="H73" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>120.35</v>
+        <v>178.79</v>
       </c>
       <c r="K73" t="n">
-        <v>72.34</v>
+        <v>55.43</v>
       </c>
       <c r="L73" t="n">
-        <v>140.42</v>
+        <v>187.19</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>2.99</v>
       </c>
       <c r="F74" t="n">
-        <v>7.47</v>
+        <v>7.15</v>
       </c>
       <c r="G74" t="n">
-        <v>106.5</v>
+        <v>107.2</v>
       </c>
       <c r="H74" t="n">
-        <v>20.8</v>
+        <v>23.2</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.67</v>
+        <v>-22.63</v>
       </c>
       <c r="K74" t="n">
-        <v>-49.08</v>
+        <v>-53.97</v>
       </c>
       <c r="L74" t="n">
-        <v>53.65</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>2.88</v>
       </c>
       <c r="F75" t="n">
-        <v>7.24</v>
+        <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>104.4</v>
+        <v>102.6</v>
       </c>
       <c r="H75" t="n">
-        <v>23.4</v>
+        <v>22.2</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>92.95999999999999</v>
+        <v>101.63</v>
       </c>
       <c r="K75" t="n">
-        <v>13.57</v>
+        <v>14.63</v>
       </c>
       <c r="L75" t="n">
-        <v>93.95</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>3.05</v>
       </c>
       <c r="F76" t="n">
-        <v>7.83</v>
+        <v>8.74</v>
       </c>
       <c r="G76" t="n">
-        <v>116.2</v>
+        <v>114.4</v>
       </c>
       <c r="H76" t="n">
-        <v>25.4</v>
+        <v>28</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>4.72</v>
+        <v>7.52</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.1</v>
+        <v>-53.44</v>
       </c>
       <c r="L76" t="n">
-        <v>47.33</v>
+        <v>53.97</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>3.02</v>
       </c>
       <c r="F77" t="n">
-        <v>7.13</v>
+        <v>8.74</v>
       </c>
       <c r="G77" t="n">
-        <v>104.5</v>
+        <v>100.5</v>
       </c>
       <c r="H77" t="n">
-        <v>29.1</v>
+        <v>22.2</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.81</v>
+        <v>-77.3</v>
       </c>
       <c r="K77" t="n">
-        <v>-29.39</v>
+        <v>-36.16</v>
       </c>
       <c r="L77" t="n">
-        <v>72.08</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>2.68</v>
       </c>
       <c r="F78" t="n">
-        <v>7.52</v>
+        <v>7.47</v>
       </c>
       <c r="G78" t="n">
-        <v>111.1</v>
+        <v>108.2</v>
       </c>
       <c r="H78" t="n">
-        <v>23.6</v>
+        <v>25.5</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>74.09999999999999</v>
+        <v>80.37</v>
       </c>
       <c r="K78" t="n">
-        <v>23.27</v>
+        <v>24.02</v>
       </c>
       <c r="L78" t="n">
-        <v>77.67</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>2.79</v>
       </c>
       <c r="F79" t="n">
-        <v>7.98</v>
+        <v>5.85</v>
       </c>
       <c r="G79" t="n">
-        <v>118.3</v>
+        <v>117.4</v>
       </c>
       <c r="H79" t="n">
-        <v>18.7</v>
+        <v>29.1</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>76.91</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>33.07</v>
+        <v>32.25</v>
       </c>
       <c r="L79" t="n">
-        <v>83.72</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>2.98</v>
       </c>
       <c r="F80" t="n">
-        <v>7.5</v>
+        <v>8.74</v>
       </c>
       <c r="G80" t="n">
-        <v>111.1</v>
+        <v>108</v>
       </c>
       <c r="H80" t="n">
-        <v>27.4</v>
+        <v>25.5</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-112.22</v>
+        <v>-122.21</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.29</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>127.39</v>
+        <v>142.41</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>3.37</v>
       </c>
       <c r="F81" t="n">
-        <v>7.72</v>
+        <v>6.96</v>
       </c>
       <c r="G81" t="n">
-        <v>111.9</v>
+        <v>112.3</v>
       </c>
       <c r="H81" t="n">
-        <v>28.5</v>
+        <v>25.9</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>69.33</v>
+        <v>86.8</v>
       </c>
       <c r="K81" t="n">
-        <v>105.2</v>
+        <v>114.22</v>
       </c>
       <c r="L81" t="n">
-        <v>125.99</v>
+        <v>143.46</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>2.81</v>
       </c>
       <c r="F82" t="n">
-        <v>8.199999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>105.3</v>
+        <v>122</v>
       </c>
       <c r="H82" t="n">
-        <v>29.4</v>
+        <v>22.6</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-74.18000000000001</v>
+        <v>-87.52</v>
       </c>
       <c r="K82" t="n">
-        <v>99.52</v>
+        <v>120.12</v>
       </c>
       <c r="L82" t="n">
-        <v>124.12</v>
+        <v>148.62</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>2.66</v>
       </c>
       <c r="F83" t="n">
-        <v>7.35</v>
+        <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>110.7</v>
+        <v>104.9</v>
       </c>
       <c r="H83" t="n">
-        <v>29.1</v>
+        <v>25.3</v>
       </c>
       <c r="I83" t="n">
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-42.69</v>
+        <v>-21.06</v>
       </c>
       <c r="K83" t="n">
-        <v>120.13</v>
+        <v>146.69</v>
       </c>
       <c r="L83" t="n">
-        <v>127.49</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>2.85</v>
       </c>
       <c r="F84" t="n">
-        <v>7.55</v>
+        <v>6.07</v>
       </c>
       <c r="G84" t="n">
-        <v>105.1</v>
+        <v>109</v>
       </c>
       <c r="H84" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-157.36</v>
+        <v>-152.53</v>
       </c>
       <c r="K84" t="n">
-        <v>91.22</v>
+        <v>92.03</v>
       </c>
       <c r="L84" t="n">
-        <v>181.89</v>
+        <v>178.14</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>2.71</v>
       </c>
       <c r="F85" t="n">
-        <v>7.8</v>
+        <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>118.1</v>
+        <v>113.9</v>
       </c>
       <c r="H85" t="n">
-        <v>28.3</v>
+        <v>29</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>116.89</v>
+        <v>160.23</v>
       </c>
       <c r="K85" t="n">
-        <v>-47.11</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>126.03</v>
+        <v>172.68</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>2.71</v>
       </c>
       <c r="F86" t="n">
-        <v>7.28</v>
+        <v>7.94</v>
       </c>
       <c r="G86" t="n">
-        <v>101.1</v>
+        <v>103.5</v>
       </c>
       <c r="H86" t="n">
-        <v>24.3</v>
+        <v>20.5</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>184.66</v>
+        <v>215.02</v>
       </c>
       <c r="K86" t="n">
-        <v>-185.56</v>
+        <v>-193.01</v>
       </c>
       <c r="L86" t="n">
-        <v>261.79</v>
+        <v>288.94</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>2.97</v>
       </c>
       <c r="F87" t="n">
-        <v>7.49</v>
+        <v>8.02</v>
       </c>
       <c r="G87" t="n">
-        <v>103.1</v>
+        <v>107.8</v>
       </c>
       <c r="H87" t="n">
-        <v>28.6</v>
+        <v>21.5</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>158.84</v>
+        <v>194.6</v>
       </c>
       <c r="K87" t="n">
-        <v>-109.4</v>
+        <v>-120.53</v>
       </c>
       <c r="L87" t="n">
-        <v>192.87</v>
+        <v>228.9</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>3.28</v>
       </c>
       <c r="F88" t="n">
-        <v>7.9</v>
+        <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>108.4</v>
+        <v>115.8</v>
       </c>
       <c r="H88" t="n">
-        <v>26.8</v>
+        <v>24.1</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-45.06</v>
+        <v>41.54</v>
       </c>
       <c r="K88" t="n">
-        <v>-24.27</v>
+        <v>-95.68000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>51.18</v>
+        <v>104.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>91.42</v>
+        <v>104.02</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.05</v>
+        <v>-23.96</v>
       </c>
       <c r="L14" t="n">
-        <v>93.81</v>
+        <v>106.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.89</v>
+        <v>-23.77</v>
       </c>
       <c r="K15" t="n">
-        <v>-63.62</v>
+        <v>-72.39</v>
       </c>
       <c r="L15" t="n">
-        <v>66.95999999999999</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>26.88</v>
+        <v>29.32</v>
       </c>
       <c r="K16" t="n">
-        <v>46.32</v>
+        <v>50.53</v>
       </c>
       <c r="L16" t="n">
-        <v>53.55</v>
+        <v>58.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>87.98</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.69</v>
+        <v>-2.84</v>
       </c>
       <c r="L17" t="n">
-        <v>88.02</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>61.42</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-54.63</v>
+        <v>-57.73</v>
       </c>
       <c r="L18" t="n">
-        <v>82.2</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="K19" t="n">
-        <v>-81.81999999999999</v>
+        <v>-90.59</v>
       </c>
       <c r="L19" t="n">
-        <v>81.83</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.24</v>
+        <v>-11.34</v>
       </c>
       <c r="K20" t="n">
-        <v>-112.31</v>
+        <v>-124.35</v>
       </c>
       <c r="L20" t="n">
-        <v>112.78</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>121.64</v>
+        <v>134.68</v>
       </c>
       <c r="K21" t="n">
-        <v>4.38</v>
+        <v>4.85</v>
       </c>
       <c r="L21" t="n">
-        <v>121.72</v>
+        <v>134.76</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
+        <v>112.28</v>
       </c>
       <c r="K22" t="n">
-        <v>-37.38</v>
+        <v>-41.97</v>
       </c>
       <c r="L22" t="n">
-        <v>106.76</v>
+        <v>119.87</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-125.7</v>
+        <v>-139.16</v>
       </c>
       <c r="K23" t="n">
-        <v>-23.16</v>
+        <v>-25.64</v>
       </c>
       <c r="L23" t="n">
-        <v>127.81</v>
+        <v>141.51</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>34.17</v>
+        <v>38.88</v>
       </c>
       <c r="K24" t="n">
-        <v>146.53</v>
+        <v>166.74</v>
       </c>
       <c r="L24" t="n">
-        <v>150.46</v>
+        <v>171.22</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>81.08</v>
+        <v>85.67</v>
       </c>
       <c r="K25" t="n">
-        <v>51.29</v>
+        <v>54.19</v>
       </c>
       <c r="L25" t="n">
-        <v>95.94</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>236.56</v>
+        <v>261.91</v>
       </c>
       <c r="K26" t="n">
-        <v>-76.89</v>
+        <v>-85.13</v>
       </c>
       <c r="L26" t="n">
-        <v>248.74</v>
+        <v>275.39</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>146.49</v>
+        <v>159.81</v>
       </c>
       <c r="K27" t="n">
-        <v>22.8</v>
+        <v>24.87</v>
       </c>
       <c r="L27" t="n">
-        <v>148.26</v>
+        <v>161.73</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>169.44</v>
+        <v>190.25</v>
       </c>
       <c r="K28" t="n">
-        <v>-29.72</v>
+        <v>-33.37</v>
       </c>
       <c r="L28" t="n">
-        <v>172.02</v>
+        <v>193.15</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>62.31</v>
+        <v>65.84</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.06</v>
+        <v>-31.76</v>
       </c>
       <c r="L29" t="n">
-        <v>69.18000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-45.07</v>
+        <v>-47.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-45.26</v>
+        <v>-47.82</v>
       </c>
       <c r="L30" t="n">
-        <v>63.87</v>
+        <v>67.48999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.18</v>
+        <v>-9.18</v>
       </c>
       <c r="K31" t="n">
-        <v>87.7</v>
+        <v>98.47</v>
       </c>
       <c r="L31" t="n">
-        <v>88.08</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-59.62</v>
+        <v>-67.84999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-63.9</v>
+        <v>-72.70999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>87.40000000000001</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-66.40000000000001</v>
+        <v>-71.31999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>3.51</v>
+        <v>3.77</v>
       </c>
       <c r="L33" t="n">
-        <v>66.5</v>
+        <v>71.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>65.75</v>
+        <v>71.73</v>
       </c>
       <c r="K34" t="n">
-        <v>8.41</v>
+        <v>9.18</v>
       </c>
       <c r="L34" t="n">
-        <v>66.28</v>
+        <v>72.31</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>119.97</v>
+        <v>132.82</v>
       </c>
       <c r="K35" t="n">
-        <v>-33.38</v>
+        <v>-36.96</v>
       </c>
       <c r="L35" t="n">
-        <v>124.52</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-43.19</v>
+        <v>-49.15</v>
       </c>
       <c r="K36" t="n">
-        <v>-84.75</v>
+        <v>-96.44</v>
       </c>
       <c r="L36" t="n">
-        <v>95.12</v>
+        <v>108.24</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>111.41</v>
+        <v>126.77</v>
       </c>
       <c r="K37" t="n">
-        <v>-82.92</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>138.88</v>
+        <v>158.03</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-57.38</v>
+        <v>-60.63</v>
       </c>
       <c r="K38" t="n">
-        <v>126.16</v>
+        <v>133.3</v>
       </c>
       <c r="L38" t="n">
-        <v>138.6</v>
+        <v>146.44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-113.52</v>
+        <v>-119.94</v>
       </c>
       <c r="K39" t="n">
-        <v>-223.73</v>
+        <v>-236.39</v>
       </c>
       <c r="L39" t="n">
-        <v>250.88</v>
+        <v>265.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>43.97</v>
+        <v>49.37</v>
       </c>
       <c r="K40" t="n">
-        <v>109.2</v>
+        <v>122.61</v>
       </c>
       <c r="L40" t="n">
-        <v>117.72</v>
+        <v>132.18</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-116.65</v>
+        <v>-125.68</v>
       </c>
       <c r="K41" t="n">
-        <v>-131.48</v>
+        <v>-141.66</v>
       </c>
       <c r="L41" t="n">
-        <v>175.77</v>
+        <v>189.37</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>240.25</v>
+        <v>273.39</v>
       </c>
       <c r="K42" t="n">
-        <v>-149.53</v>
+        <v>-170.15</v>
       </c>
       <c r="L42" t="n">
-        <v>282.98</v>
+        <v>322.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>349.35</v>
+        <v>369.13</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="L43" t="n">
-        <v>349.35</v>
+        <v>369.13</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-70.73</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-60.63</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>93.16</v>
+        <v>106.01</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.11</v>
+        <v>-5.49</v>
       </c>
       <c r="K45" t="n">
-        <v>42.2</v>
+        <v>45.32</v>
       </c>
       <c r="L45" t="n">
-        <v>42.5</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>43.36</v>
+        <v>47.3</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.04</v>
+        <v>-1.14</v>
       </c>
       <c r="L46" t="n">
-        <v>43.37</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-21.85</v>
+        <v>-24.86</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.17</v>
+        <v>-84.41</v>
       </c>
       <c r="L47" t="n">
-        <v>77.33</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-34.16</v>
+        <v>-37.26</v>
       </c>
       <c r="K48" t="n">
-        <v>-77.98999999999999</v>
+        <v>-85.08</v>
       </c>
       <c r="L48" t="n">
-        <v>85.14</v>
+        <v>92.88</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.45</v>
+        <v>-32.38</v>
       </c>
       <c r="K49" t="n">
-        <v>96.05</v>
+        <v>109.3</v>
       </c>
       <c r="L49" t="n">
-        <v>100.17</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>87.93000000000001</v>
+        <v>100.06</v>
       </c>
       <c r="K50" t="n">
-        <v>-78.59</v>
+        <v>-89.43000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>117.94</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.28</v>
+        <v>-16.67</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.84</v>
+        <v>-15.1</v>
       </c>
       <c r="L51" t="n">
-        <v>20.62</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-20.82</v>
+        <v>-23.69</v>
       </c>
       <c r="K52" t="n">
-        <v>134.39</v>
+        <v>152.93</v>
       </c>
       <c r="L52" t="n">
-        <v>135.99</v>
+        <v>154.75</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>174.77</v>
+        <v>190.66</v>
       </c>
       <c r="K53" t="n">
-        <v>-38.9</v>
+        <v>-42.44</v>
       </c>
       <c r="L53" t="n">
-        <v>179.05</v>
+        <v>195.33</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>93.84</v>
+        <v>105.36</v>
       </c>
       <c r="K54" t="n">
-        <v>-7.35</v>
+        <v>-8.25</v>
       </c>
       <c r="L54" t="n">
-        <v>94.13</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-111.43</v>
+        <v>-117.74</v>
       </c>
       <c r="K55" t="n">
-        <v>-57.06</v>
+        <v>-60.28</v>
       </c>
       <c r="L55" t="n">
-        <v>125.19</v>
+        <v>132.28</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-186.83</v>
+        <v>-200.67</v>
       </c>
       <c r="K56" t="n">
-        <v>-203.26</v>
+        <v>-218.31</v>
       </c>
       <c r="L56" t="n">
-        <v>276.08</v>
+        <v>296.53</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-212.68</v>
+        <v>-235.47</v>
       </c>
       <c r="K57" t="n">
-        <v>-81</v>
+        <v>-89.68000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>227.58</v>
+        <v>251.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>196.33</v>
+        <v>210.88</v>
       </c>
       <c r="K58" t="n">
-        <v>69.84</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>208.38</v>
+        <v>223.82</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.86</v>
+        <v>-50.57</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.91</v>
+        <v>-39</v>
       </c>
       <c r="L59" t="n">
-        <v>60.44</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-39.88</v>
+        <v>-45.38</v>
       </c>
       <c r="K60" t="n">
-        <v>-35.76</v>
+        <v>-40.69</v>
       </c>
       <c r="L60" t="n">
-        <v>53.56</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-77.93000000000001</v>
+        <v>-88.68000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>40.96</v>
+        <v>46.61</v>
       </c>
       <c r="L61" t="n">
-        <v>88.04000000000001</v>
+        <v>100.18</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-69.27</v>
+        <v>-75.56</v>
       </c>
       <c r="K62" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="L62" t="n">
-        <v>69.33</v>
+        <v>75.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>85.20999999999999</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>46.91</v>
+        <v>53.38</v>
       </c>
       <c r="L63" t="n">
-        <v>97.27</v>
+        <v>110.68</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>28.33</v>
+        <v>30.91</v>
       </c>
       <c r="K64" t="n">
-        <v>71.56999999999999</v>
+        <v>78.08</v>
       </c>
       <c r="L64" t="n">
-        <v>76.98</v>
+        <v>83.98</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>56.79</v>
+        <v>60.99</v>
       </c>
       <c r="K65" t="n">
-        <v>-120.87</v>
+        <v>-129.83</v>
       </c>
       <c r="L65" t="n">
-        <v>133.55</v>
+        <v>143.44</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-74.55</v>
+        <v>-80.06999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>64.26000000000001</v>
+        <v>69.02</v>
       </c>
       <c r="L66" t="n">
-        <v>98.42</v>
+        <v>105.71</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>26.87</v>
+        <v>30.58</v>
       </c>
       <c r="K67" t="n">
-        <v>112</v>
+        <v>127.45</v>
       </c>
       <c r="L67" t="n">
-        <v>115.18</v>
+        <v>131.07</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>78.22</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-181.01</v>
+        <v>-205.97</v>
       </c>
       <c r="L68" t="n">
-        <v>197.19</v>
+        <v>224.38</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>69.31999999999999</v>
+        <v>78.89</v>
       </c>
       <c r="K69" t="n">
-        <v>178.66</v>
+        <v>203.31</v>
       </c>
       <c r="L69" t="n">
-        <v>191.64</v>
+        <v>218.08</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-152.65</v>
+        <v>-163.97</v>
       </c>
       <c r="K70" t="n">
-        <v>105.01</v>
+        <v>112.8</v>
       </c>
       <c r="L70" t="n">
-        <v>185.28</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K71" t="n">
-        <v>-139.27</v>
+        <v>-158.48</v>
       </c>
       <c r="L71" t="n">
-        <v>139.27</v>
+        <v>158.48</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>104.68</v>
+        <v>119.12</v>
       </c>
       <c r="K72" t="n">
-        <v>-122.94</v>
+        <v>-139.9</v>
       </c>
       <c r="L72" t="n">
-        <v>161.47</v>
+        <v>183.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>178.79</v>
+        <v>197.95</v>
       </c>
       <c r="K73" t="n">
-        <v>55.43</v>
+        <v>61.37</v>
       </c>
       <c r="L73" t="n">
-        <v>187.19</v>
+        <v>207.24</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-22.63</v>
+        <v>-23.91</v>
       </c>
       <c r="K74" t="n">
-        <v>-53.97</v>
+        <v>-57.02</v>
       </c>
       <c r="L74" t="n">
-        <v>58.52</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>101.63</v>
+        <v>114.11</v>
       </c>
       <c r="K75" t="n">
-        <v>14.63</v>
+        <v>16.43</v>
       </c>
       <c r="L75" t="n">
-        <v>102.67</v>
+        <v>115.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>7.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.44</v>
+        <v>-58.3</v>
       </c>
       <c r="L76" t="n">
-        <v>53.97</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-77.3</v>
+        <v>-86.79000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-36.16</v>
+        <v>-40.61</v>
       </c>
       <c r="L77" t="n">
-        <v>85.34</v>
+        <v>95.81999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>80.37</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>24.02</v>
+        <v>26.2</v>
       </c>
       <c r="L78" t="n">
-        <v>83.89</v>
+        <v>91.51000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>78.76000000000001</v>
+        <v>85.92</v>
       </c>
       <c r="K79" t="n">
-        <v>32.25</v>
+        <v>35.18</v>
       </c>
       <c r="L79" t="n">
-        <v>85.11</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-122.21</v>
+        <v>-139.07</v>
       </c>
       <c r="K80" t="n">
-        <v>-73.09999999999999</v>
+        <v>-83.18000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>142.41</v>
+        <v>162.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>86.8</v>
+        <v>98.75</v>
       </c>
       <c r="K81" t="n">
-        <v>114.22</v>
+        <v>129.95</v>
       </c>
       <c r="L81" t="n">
-        <v>143.46</v>
+        <v>163.22</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-87.52</v>
+        <v>-99.59</v>
       </c>
       <c r="K82" t="n">
-        <v>120.12</v>
+        <v>136.68</v>
       </c>
       <c r="L82" t="n">
-        <v>148.62</v>
+        <v>169.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-21.06</v>
+        <v>-23.96</v>
       </c>
       <c r="K83" t="n">
-        <v>146.69</v>
+        <v>166.93</v>
       </c>
       <c r="L83" t="n">
-        <v>148.2</v>
+        <v>168.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>-152.53</v>
+        <v>-171.26</v>
       </c>
       <c r="K84" t="n">
-        <v>92.03</v>
+        <v>103.33</v>
       </c>
       <c r="L84" t="n">
-        <v>178.14</v>
+        <v>200.02</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>160.23</v>
+        <v>182.33</v>
       </c>
       <c r="K85" t="n">
-        <v>-64.40000000000001</v>
+        <v>-73.28</v>
       </c>
       <c r="L85" t="n">
-        <v>172.68</v>
+        <v>196.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>215.02</v>
+        <v>230.94</v>
       </c>
       <c r="K86" t="n">
-        <v>-193.01</v>
+        <v>-207.31</v>
       </c>
       <c r="L86" t="n">
-        <v>288.94</v>
+        <v>310.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>194.6</v>
+        <v>218.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-120.53</v>
+        <v>-135.33</v>
       </c>
       <c r="L87" t="n">
-        <v>228.9</v>
+        <v>257.01</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>41.54</v>
+        <v>45.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-95.68000000000001</v>
+        <v>-104.41</v>
       </c>
       <c r="L88" t="n">
-        <v>104.31</v>
+        <v>113.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="F14" t="n">
-        <v>7.3</v>
+        <v>7.05</v>
       </c>
       <c r="G14" t="n">
-        <v>110.6</v>
+        <v>119.1</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>55.7</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>104.02</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-23.96</v>
+        <v>31.09</v>
       </c>
       <c r="L14" t="n">
-        <v>106.75</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:37</t>
+          <t>06:38:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="F15" t="n">
-        <v>6.71</v>
+        <v>8.74</v>
       </c>
       <c r="G15" t="n">
-        <v>103.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>24.9</v>
+        <v>61.7</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>-23.77</v>
+        <v>-1.41</v>
       </c>
       <c r="K15" t="n">
-        <v>-72.39</v>
+        <v>-47.78</v>
       </c>
       <c r="L15" t="n">
-        <v>76.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:39:55</t>
+          <t>06:39:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="F16" t="n">
-        <v>6.34</v>
+        <v>6.22</v>
       </c>
       <c r="G16" t="n">
-        <v>108.3</v>
+        <v>101.3</v>
       </c>
       <c r="H16" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>29.32</v>
+        <v>51.46</v>
       </c>
       <c r="K16" t="n">
-        <v>50.53</v>
+        <v>23.34</v>
       </c>
       <c r="L16" t="n">
-        <v>58.42</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:43:57</t>
+          <t>06:43:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="F17" t="n">
-        <v>5.39</v>
+        <v>4.39</v>
       </c>
       <c r="G17" t="n">
-        <v>115.5</v>
+        <v>114.8</v>
       </c>
       <c r="H17" t="n">
-        <v>29.5</v>
+        <v>60.3</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>92.95999999999999</v>
+        <v>52.58</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.84</v>
+        <v>14.55</v>
       </c>
       <c r="L17" t="n">
-        <v>93</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:45:00</t>
+          <t>06:46:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="F18" t="n">
         <v>8.74</v>
       </c>
       <c r="G18" t="n">
-        <v>110.8</v>
+        <v>93.2</v>
       </c>
       <c r="H18" t="n">
-        <v>26.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>64.90000000000001</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-57.73</v>
+        <v>32.96</v>
       </c>
       <c r="L18" t="n">
-        <v>86.86</v>
+        <v>81.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:45:56</t>
+          <t>06:48:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="F19" t="n">
-        <v>7.37</v>
+        <v>7.04</v>
       </c>
       <c r="G19" t="n">
-        <v>106.4</v>
+        <v>121.6</v>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>57.9</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>1.14</v>
+        <v>57.01</v>
       </c>
       <c r="K19" t="n">
-        <v>-90.59</v>
+        <v>22.76</v>
       </c>
       <c r="L19" t="n">
-        <v>90.59999999999999</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:49:16</t>
+          <t>06:52:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="F20" t="n">
-        <v>6.54</v>
+        <v>8.43</v>
       </c>
       <c r="G20" t="n">
-        <v>126.1</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>28.1</v>
+        <v>69.2</v>
       </c>
       <c r="I20" t="n">
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.34</v>
+        <v>-32.1</v>
       </c>
       <c r="K20" t="n">
-        <v>-124.35</v>
+        <v>123.56</v>
       </c>
       <c r="L20" t="n">
-        <v>124.86</v>
+        <v>127.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:51:52</t>
+          <t>06:52:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="F21" t="n">
-        <v>8.74</v>
+        <v>4.04</v>
       </c>
       <c r="G21" t="n">
-        <v>119.2</v>
+        <v>117.9</v>
       </c>
       <c r="H21" t="n">
-        <v>31.1</v>
+        <v>36.8</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>134.68</v>
+        <v>30.23</v>
       </c>
       <c r="K21" t="n">
-        <v>4.85</v>
+        <v>-46.97</v>
       </c>
       <c r="L21" t="n">
-        <v>134.76</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:52:37</t>
+          <t>06:54:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="F22" t="n">
-        <v>6.7</v>
+        <v>6.78</v>
       </c>
       <c r="G22" t="n">
-        <v>108.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>21.7</v>
+        <v>41</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>112.28</v>
+        <v>-105.51</v>
       </c>
       <c r="K22" t="n">
-        <v>-41.97</v>
+        <v>-23.31</v>
       </c>
       <c r="L22" t="n">
-        <v>119.87</v>
+        <v>108.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:57:31</t>
+          <t>07:00:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.07</v>
+        <v>2.53</v>
       </c>
       <c r="F23" t="n">
-        <v>3.94</v>
+        <v>7.99</v>
       </c>
       <c r="G23" t="n">
-        <v>116.3</v>
+        <v>119.1</v>
       </c>
       <c r="H23" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-139.16</v>
+        <v>-91.72</v>
       </c>
       <c r="K23" t="n">
-        <v>-25.64</v>
+        <v>-122.47</v>
       </c>
       <c r="L23" t="n">
-        <v>141.51</v>
+        <v>153.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:59:54</t>
+          <t>07:02:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="F24" t="n">
-        <v>5.91</v>
+        <v>6.93</v>
       </c>
       <c r="G24" t="n">
-        <v>112.6</v>
+        <v>110.6</v>
       </c>
       <c r="H24" t="n">
-        <v>26.1</v>
+        <v>31.3</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>38.88</v>
+        <v>44.26</v>
       </c>
       <c r="K24" t="n">
-        <v>166.74</v>
+        <v>149.57</v>
       </c>
       <c r="L24" t="n">
-        <v>171.22</v>
+        <v>155.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:01:10</t>
+          <t>07:03:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98</v>
+        <v>2.71</v>
       </c>
       <c r="F25" t="n">
-        <v>3.32</v>
+        <v>8.73</v>
       </c>
       <c r="G25" t="n">
-        <v>116.2</v>
+        <v>113</v>
       </c>
       <c r="H25" t="n">
-        <v>28.2</v>
+        <v>42.2</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>85.67</v>
+        <v>-70.79000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>54.19</v>
+        <v>134.73</v>
       </c>
       <c r="L25" t="n">
-        <v>101.37</v>
+        <v>152.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:05:30</t>
+          <t>07:08:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="F26" t="n">
-        <v>6.24</v>
+        <v>6.09</v>
       </c>
       <c r="G26" t="n">
-        <v>114.7</v>
+        <v>105.1</v>
       </c>
       <c r="H26" t="n">
-        <v>19.2</v>
+        <v>42.5</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>261.91</v>
+        <v>22.39</v>
       </c>
       <c r="K26" t="n">
-        <v>-85.13</v>
+        <v>-165.38</v>
       </c>
       <c r="L26" t="n">
-        <v>275.39</v>
+        <v>166.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:08:03</t>
+          <t>07:09:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="F27" t="n">
-        <v>2.85</v>
+        <v>5.08</v>
       </c>
       <c r="G27" t="n">
-        <v>91</v>
+        <v>111.9</v>
       </c>
       <c r="H27" t="n">
-        <v>25.2</v>
+        <v>37.8</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>159.81</v>
+        <v>-14.81</v>
       </c>
       <c r="K27" t="n">
-        <v>24.87</v>
+        <v>-195</v>
       </c>
       <c r="L27" t="n">
-        <v>161.73</v>
+        <v>195.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:08:52</t>
+          <t>07:11:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.69</v>
+        <v>2.29</v>
       </c>
       <c r="F28" t="n">
-        <v>7.34</v>
+        <v>6.41</v>
       </c>
       <c r="G28" t="n">
-        <v>110.3</v>
+        <v>109.1</v>
       </c>
       <c r="H28" t="n">
-        <v>28.4</v>
+        <v>21.1</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>190.25</v>
+        <v>-85.66</v>
       </c>
       <c r="K28" t="n">
-        <v>-33.37</v>
+        <v>145.07</v>
       </c>
       <c r="L28" t="n">
-        <v>193.15</v>
+        <v>168.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:17:59</t>
+          <t>07:21:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="F29" t="n">
-        <v>5.85</v>
+        <v>8.74</v>
       </c>
       <c r="G29" t="n">
-        <v>112.2</v>
+        <v>115.9</v>
       </c>
       <c r="H29" t="n">
-        <v>30.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>65.84</v>
+        <v>25.56</v>
       </c>
       <c r="K29" t="n">
-        <v>-31.76</v>
+        <v>44.44</v>
       </c>
       <c r="L29" t="n">
-        <v>73.09999999999999</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:20:02</t>
+          <t>07:23:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="F30" t="n">
-        <v>7.45</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>113.5</v>
+        <v>99.2</v>
       </c>
       <c r="H30" t="n">
-        <v>19.3</v>
+        <v>44.6</v>
       </c>
       <c r="I30" t="n">
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.62</v>
+        <v>37.17</v>
       </c>
       <c r="K30" t="n">
-        <v>-47.82</v>
+        <v>-17.8</v>
       </c>
       <c r="L30" t="n">
-        <v>67.48999999999999</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:21:40</t>
+          <t>07:24:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="F31" t="n">
-        <v>6.76</v>
+        <v>7.74</v>
       </c>
       <c r="G31" t="n">
-        <v>111.8</v>
+        <v>121.4</v>
       </c>
       <c r="H31" t="n">
-        <v>22.5</v>
+        <v>47.9</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.18</v>
+        <v>-23.75</v>
       </c>
       <c r="K31" t="n">
-        <v>98.47</v>
+        <v>-51.14</v>
       </c>
       <c r="L31" t="n">
-        <v>98.90000000000001</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:26:15</t>
+          <t>07:29:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="F32" t="n">
-        <v>8.18</v>
+        <v>4.18</v>
       </c>
       <c r="G32" t="n">
-        <v>115.3</v>
+        <v>104.2</v>
       </c>
       <c r="H32" t="n">
-        <v>29.4</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-67.84999999999999</v>
+        <v>27.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.70999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="L32" t="n">
-        <v>99.45</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:28:13</t>
+          <t>07:30:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="F33" t="n">
-        <v>5.99</v>
+        <v>5.12</v>
       </c>
       <c r="G33" t="n">
-        <v>120</v>
+        <v>116.4</v>
       </c>
       <c r="H33" t="n">
-        <v>28.6</v>
+        <v>37.6</v>
       </c>
       <c r="I33" t="n">
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-71.31999999999999</v>
+        <v>38.77</v>
       </c>
       <c r="K33" t="n">
-        <v>3.77</v>
+        <v>5.45</v>
       </c>
       <c r="L33" t="n">
-        <v>71.42</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:31:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="F34" t="n">
-        <v>7.95</v>
+        <v>6.07</v>
       </c>
       <c r="G34" t="n">
-        <v>108.2</v>
+        <v>110.9</v>
       </c>
       <c r="H34" t="n">
-        <v>31.2</v>
+        <v>15.7</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>71.73</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>9.18</v>
+        <v>-17.19</v>
       </c>
       <c r="L34" t="n">
-        <v>72.31</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:34:43</t>
+          <t>07:37:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="F35" t="n">
-        <v>6.02</v>
+        <v>7.39</v>
       </c>
       <c r="G35" t="n">
-        <v>114</v>
+        <v>111.9</v>
       </c>
       <c r="H35" t="n">
-        <v>18.3</v>
+        <v>31</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>132.82</v>
+        <v>12.79</v>
       </c>
       <c r="K35" t="n">
-        <v>-36.96</v>
+        <v>115.21</v>
       </c>
       <c r="L35" t="n">
-        <v>137.87</v>
+        <v>115.91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:36:41</t>
+          <t>07:39:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="F36" t="n">
-        <v>7.72</v>
+        <v>8.74</v>
       </c>
       <c r="G36" t="n">
-        <v>112.2</v>
+        <v>100.2</v>
       </c>
       <c r="H36" t="n">
-        <v>28.4</v>
+        <v>15.5</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-49.15</v>
+        <v>102.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-96.44</v>
+        <v>40.93</v>
       </c>
       <c r="L36" t="n">
-        <v>108.24</v>
+        <v>109.98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:38:11</t>
+          <t>07:40:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="F37" t="n">
-        <v>6.75</v>
+        <v>6.77</v>
       </c>
       <c r="G37" t="n">
-        <v>102.5</v>
+        <v>106.3</v>
       </c>
       <c r="H37" t="n">
-        <v>29.3</v>
+        <v>60.3</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>126.77</v>
+        <v>-108</v>
       </c>
       <c r="K37" t="n">
-        <v>-94.34999999999999</v>
+        <v>66.86</v>
       </c>
       <c r="L37" t="n">
-        <v>158.03</v>
+        <v>127.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:43:40</t>
+          <t>07:45:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="F38" t="n">
-        <v>5.12</v>
+        <v>5.91</v>
       </c>
       <c r="G38" t="n">
-        <v>110.1</v>
+        <v>118.3</v>
       </c>
       <c r="H38" t="n">
-        <v>28.6</v>
+        <v>48.8</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-60.63</v>
+        <v>48.21</v>
       </c>
       <c r="K38" t="n">
-        <v>133.3</v>
+        <v>-113.99</v>
       </c>
       <c r="L38" t="n">
-        <v>146.44</v>
+        <v>123.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:44:40</t>
+          <t>07:47:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="F39" t="n">
-        <v>7.07</v>
+        <v>7.4</v>
       </c>
       <c r="G39" t="n">
-        <v>118.5</v>
+        <v>102.6</v>
       </c>
       <c r="H39" t="n">
-        <v>27.9</v>
+        <v>33</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-119.94</v>
+        <v>-26.45</v>
       </c>
       <c r="K39" t="n">
-        <v>-236.39</v>
+        <v>198.89</v>
       </c>
       <c r="L39" t="n">
-        <v>265.08</v>
+        <v>200.64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:45:34</t>
+          <t>07:48:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.78</v>
+        <v>3.11</v>
       </c>
       <c r="F40" t="n">
-        <v>5.3</v>
+        <v>8.74</v>
       </c>
       <c r="G40" t="n">
-        <v>106.3</v>
+        <v>106</v>
       </c>
       <c r="H40" t="n">
-        <v>25.3</v>
+        <v>59.2</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>49.37</v>
+        <v>137.35</v>
       </c>
       <c r="K40" t="n">
-        <v>122.61</v>
+        <v>11.44</v>
       </c>
       <c r="L40" t="n">
-        <v>132.18</v>
+        <v>137.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:50:17</t>
+          <t>07:53:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.62</v>
+        <v>2.61</v>
       </c>
       <c r="F41" t="n">
-        <v>7.23</v>
+        <v>6.51</v>
       </c>
       <c r="G41" t="n">
-        <v>106.9</v>
+        <v>105.9</v>
       </c>
       <c r="H41" t="n">
-        <v>25.9</v>
+        <v>58.5</v>
       </c>
       <c r="I41" t="n">
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-125.68</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-141.66</v>
+        <v>202.6</v>
       </c>
       <c r="L41" t="n">
-        <v>189.37</v>
+        <v>222.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:51:26</t>
+          <t>07:55:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.86</v>
+        <v>3.27</v>
       </c>
       <c r="F42" t="n">
-        <v>8.74</v>
+        <v>8.41</v>
       </c>
       <c r="G42" t="n">
-        <v>102.4</v>
+        <v>107.8</v>
       </c>
       <c r="H42" t="n">
-        <v>18.7</v>
+        <v>61.5</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>273.39</v>
+        <v>-256.09</v>
       </c>
       <c r="K42" t="n">
-        <v>-170.15</v>
+        <v>7.45</v>
       </c>
       <c r="L42" t="n">
-        <v>322.01</v>
+        <v>256.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:53:23</t>
+          <t>07:58:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="F43" t="n">
-        <v>7.99</v>
+        <v>8.74</v>
       </c>
       <c r="G43" t="n">
-        <v>100.2</v>
+        <v>101.2</v>
       </c>
       <c r="H43" t="n">
-        <v>25.6</v>
+        <v>61</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>369.13</v>
+        <v>216.12</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.16</v>
+        <v>123.89</v>
       </c>
       <c r="L43" t="n">
-        <v>369.13</v>
+        <v>249.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:01:45</t>
+          <t>08:10:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="F44" t="n">
-        <v>6.2</v>
+        <v>8.17</v>
       </c>
       <c r="G44" t="n">
-        <v>99.5</v>
+        <v>106.5</v>
       </c>
       <c r="H44" t="n">
-        <v>26.3</v>
+        <v>23.9</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-80.48999999999999</v>
+        <v>-43.52</v>
       </c>
       <c r="K44" t="n">
-        <v>-68.98999999999999</v>
+        <v>-21.99</v>
       </c>
       <c r="L44" t="n">
-        <v>106.01</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:03:42</t>
+          <t>08:12:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="F45" t="n">
-        <v>7.02</v>
+        <v>6.94</v>
       </c>
       <c r="G45" t="n">
-        <v>119</v>
+        <v>103.1</v>
       </c>
       <c r="H45" t="n">
-        <v>25.5</v>
+        <v>34.7</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.49</v>
+        <v>4.7</v>
       </c>
       <c r="K45" t="n">
-        <v>45.32</v>
+        <v>-32.58</v>
       </c>
       <c r="L45" t="n">
-        <v>45.65</v>
+        <v>32.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:05:48</t>
+          <t>08:14:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="F46" t="n">
-        <v>4.54</v>
+        <v>6.29</v>
       </c>
       <c r="G46" t="n">
-        <v>116.1</v>
+        <v>110.6</v>
       </c>
       <c r="H46" t="n">
-        <v>31.1</v>
+        <v>45.5</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>47.3</v>
+        <v>24.93</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.14</v>
+        <v>-38.21</v>
       </c>
       <c r="L46" t="n">
-        <v>47.31</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:11:33</t>
+          <t>08:20:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="F47" t="n">
         <v>8.74</v>
       </c>
       <c r="G47" t="n">
-        <v>114</v>
+        <v>118.2</v>
       </c>
       <c r="H47" t="n">
-        <v>20.4</v>
+        <v>46.5</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-24.86</v>
+        <v>51.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-84.41</v>
+        <v>-31.84</v>
       </c>
       <c r="L47" t="n">
-        <v>87.98999999999999</v>
+        <v>60.43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:13:27</t>
+          <t>08:21:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="F48" t="n">
-        <v>8.710000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="G48" t="n">
-        <v>103.6</v>
+        <v>117.2</v>
       </c>
       <c r="H48" t="n">
-        <v>25.2</v>
+        <v>44.8</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-37.26</v>
+        <v>60.26</v>
       </c>
       <c r="K48" t="n">
-        <v>-85.08</v>
+        <v>10.84</v>
       </c>
       <c r="L48" t="n">
-        <v>92.88</v>
+        <v>61.23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:14:19</t>
+          <t>08:23:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="F49" t="n">
-        <v>5.24</v>
+        <v>7.56</v>
       </c>
       <c r="G49" t="n">
-        <v>106.8</v>
+        <v>118.3</v>
       </c>
       <c r="H49" t="n">
-        <v>17.9</v>
+        <v>50.1</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-32.38</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>109.3</v>
+        <v>-76.01000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>113.99</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:17:57</t>
+          <t>08:27:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="F50" t="n">
-        <v>8.74</v>
+        <v>5.69</v>
       </c>
       <c r="G50" t="n">
-        <v>118.5</v>
+        <v>113.9</v>
       </c>
       <c r="H50" t="n">
-        <v>22.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>100.06</v>
+        <v>67.36</v>
       </c>
       <c r="K50" t="n">
-        <v>-89.43000000000001</v>
+        <v>51.09</v>
       </c>
       <c r="L50" t="n">
-        <v>134.2</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:19:11</t>
+          <t>08:29:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.83</v>
+        <v>3.11</v>
       </c>
       <c r="F51" t="n">
         <v>8.74</v>
       </c>
       <c r="G51" t="n">
-        <v>112.6</v>
+        <v>125</v>
       </c>
       <c r="H51" t="n">
-        <v>33</v>
+        <v>43.5</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.67</v>
+        <v>-95.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-15.1</v>
+        <v>83.66</v>
       </c>
       <c r="L51" t="n">
-        <v>22.49</v>
+        <v>127.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:20:21</t>
+          <t>08:31:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.57</v>
+        <v>3.01</v>
       </c>
       <c r="F52" t="n">
-        <v>7.3</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>106.4</v>
+        <v>121.3</v>
       </c>
       <c r="H52" t="n">
-        <v>32.7</v>
+        <v>27.2</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-23.69</v>
+        <v>-93.19</v>
       </c>
       <c r="K52" t="n">
-        <v>152.93</v>
+        <v>10.98</v>
       </c>
       <c r="L52" t="n">
-        <v>154.75</v>
+        <v>93.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:25:22</t>
+          <t>08:34:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="F53" t="n">
-        <v>7.33</v>
+        <v>8.74</v>
       </c>
       <c r="G53" t="n">
-        <v>102.5</v>
+        <v>123.3</v>
       </c>
       <c r="H53" t="n">
-        <v>35.5</v>
+        <v>58.7</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>190.66</v>
+        <v>7.52</v>
       </c>
       <c r="K53" t="n">
-        <v>-42.44</v>
+        <v>-150.2</v>
       </c>
       <c r="L53" t="n">
-        <v>195.33</v>
+        <v>150.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:26:34</t>
+          <t>08:36:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="F54" t="n">
-        <v>7.83</v>
+        <v>8.74</v>
       </c>
       <c r="G54" t="n">
-        <v>106.5</v>
+        <v>98.3</v>
       </c>
       <c r="H54" t="n">
-        <v>29.2</v>
+        <v>31.4</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>105.36</v>
+        <v>-216.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-8.25</v>
+        <v>-6.23</v>
       </c>
       <c r="L54" t="n">
-        <v>105.69</v>
+        <v>216.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:28:22</t>
+          <t>08:37:31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.79</v>
+        <v>2.44</v>
       </c>
       <c r="F55" t="n">
-        <v>6.53</v>
+        <v>7.98</v>
       </c>
       <c r="G55" t="n">
-        <v>109.6</v>
+        <v>113.9</v>
       </c>
       <c r="H55" t="n">
-        <v>32</v>
+        <v>6.3</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-117.74</v>
+        <v>103.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-60.28</v>
+        <v>-103.6</v>
       </c>
       <c r="L55" t="n">
-        <v>132.28</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:32:49</t>
+          <t>08:41:54</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="F56" t="n">
-        <v>4.57</v>
+        <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>112.6</v>
+        <v>113.4</v>
       </c>
       <c r="H56" t="n">
-        <v>26.4</v>
+        <v>36.1</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-200.67</v>
+        <v>189.97</v>
       </c>
       <c r="K56" t="n">
-        <v>-218.31</v>
+        <v>-57.19</v>
       </c>
       <c r="L56" t="n">
-        <v>296.53</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:34:23</t>
+          <t>08:43:36</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>6.93</v>
+        <v>8.74</v>
       </c>
       <c r="G57" t="n">
-        <v>100.1</v>
+        <v>115.8</v>
       </c>
       <c r="H57" t="n">
-        <v>20.7</v>
+        <v>51.4</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>-235.47</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>-89.68000000000001</v>
+        <v>-182.63</v>
       </c>
       <c r="L57" t="n">
-        <v>251.97</v>
+        <v>193.87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:36:52</t>
+          <t>08:45:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="F58" t="n">
         <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>113.2</v>
+        <v>110.1</v>
       </c>
       <c r="H58" t="n">
-        <v>21</v>
+        <v>30.4</v>
       </c>
       <c r="I58" t="n">
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>210.88</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>75.01000000000001</v>
+        <v>-232.68</v>
       </c>
       <c r="L58" t="n">
-        <v>223.82</v>
+        <v>247.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:49:06</t>
+          <t>08:57:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="F59" t="n">
-        <v>8.74</v>
+        <v>5.48</v>
       </c>
       <c r="G59" t="n">
-        <v>110.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>19.2</v>
+        <v>15.7</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-50.57</v>
+        <v>15.49</v>
       </c>
       <c r="K59" t="n">
-        <v>-39</v>
+        <v>-15.4</v>
       </c>
       <c r="L59" t="n">
-        <v>63.86</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:50:18</t>
+          <t>08:59:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.79</v>
+        <v>2.39</v>
       </c>
       <c r="F60" t="n">
-        <v>8.74</v>
+        <v>6.99</v>
       </c>
       <c r="G60" t="n">
-        <v>112.2</v>
+        <v>111.9</v>
       </c>
       <c r="H60" t="n">
-        <v>28.6</v>
+        <v>59.5</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.38</v>
+        <v>23.25</v>
       </c>
       <c r="K60" t="n">
-        <v>-40.69</v>
+        <v>-5.6</v>
       </c>
       <c r="L60" t="n">
-        <v>60.95</v>
+        <v>23.91</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:52:53</t>
+          <t>09:01:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="F61" t="n">
-        <v>8.220000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G61" t="n">
-        <v>103.4</v>
+        <v>122.6</v>
       </c>
       <c r="H61" t="n">
-        <v>24.3</v>
+        <v>50.9</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-88.68000000000001</v>
+        <v>71.16</v>
       </c>
       <c r="K61" t="n">
-        <v>46.61</v>
+        <v>-36.03</v>
       </c>
       <c r="L61" t="n">
-        <v>100.18</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:56:56</t>
+          <t>09:06:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.47</v>
+        <v>3.19</v>
       </c>
       <c r="F62" t="n">
-        <v>6.39</v>
+        <v>8.74</v>
       </c>
       <c r="G62" t="n">
-        <v>126.6</v>
+        <v>111.9</v>
       </c>
       <c r="H62" t="n">
-        <v>26.2</v>
+        <v>7</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-75.56</v>
+        <v>28.25</v>
       </c>
       <c r="K62" t="n">
-        <v>3.29</v>
+        <v>-82.20999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>75.63</v>
+        <v>86.93000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:58:59</t>
+          <t>09:07:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="F63" t="n">
-        <v>8.74</v>
+        <v>7.5</v>
       </c>
       <c r="G63" t="n">
-        <v>111.3</v>
+        <v>106.7</v>
       </c>
       <c r="H63" t="n">
-        <v>20.9</v>
+        <v>48.2</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>96.95999999999999</v>
+        <v>-85</v>
       </c>
       <c r="K63" t="n">
-        <v>53.38</v>
+        <v>-20.93</v>
       </c>
       <c r="L63" t="n">
-        <v>110.68</v>
+        <v>87.54000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:00:35</t>
+          <t>09:08:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="F64" t="n">
-        <v>8.199999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>101.3</v>
+        <v>107.9</v>
       </c>
       <c r="H64" t="n">
-        <v>21</v>
+        <v>29.1</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>30.91</v>
+        <v>32.05</v>
       </c>
       <c r="K64" t="n">
-        <v>78.08</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>83.98</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:05:24</t>
+          <t>09:13:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="F65" t="n">
-        <v>7.31</v>
+        <v>7.62</v>
       </c>
       <c r="G65" t="n">
-        <v>122.8</v>
+        <v>115.6</v>
       </c>
       <c r="H65" t="n">
-        <v>20.5</v>
+        <v>41.9</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>60.99</v>
+        <v>57.91</v>
       </c>
       <c r="K65" t="n">
-        <v>-129.83</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>143.44</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:07:32</t>
+          <t>09:14:30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.01</v>
+        <v>2.6</v>
       </c>
       <c r="F66" t="n">
         <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>112.1</v>
+        <v>115.4</v>
       </c>
       <c r="H66" t="n">
-        <v>19.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-80.06999999999999</v>
+        <v>86.02</v>
       </c>
       <c r="K66" t="n">
-        <v>69.02</v>
+        <v>-70.41</v>
       </c>
       <c r="L66" t="n">
-        <v>105.71</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:09:11</t>
+          <t>09:16:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="F67" t="n">
         <v>8.74</v>
       </c>
       <c r="G67" t="n">
-        <v>95.5</v>
+        <v>119.7</v>
       </c>
       <c r="H67" t="n">
-        <v>26</v>
+        <v>55.6</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>30.58</v>
+        <v>110.64</v>
       </c>
       <c r="K67" t="n">
-        <v>127.45</v>
+        <v>68.58</v>
       </c>
       <c r="L67" t="n">
-        <v>131.07</v>
+        <v>130.18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:13:19</t>
+          <t>09:20:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F68" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="G68" t="n">
-        <v>114.8</v>
+        <v>121.7</v>
       </c>
       <c r="H68" t="n">
-        <v>28.7</v>
+        <v>20.3</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>89.01000000000001</v>
+        <v>100.71</v>
       </c>
       <c r="K68" t="n">
-        <v>-205.97</v>
+        <v>-78.83</v>
       </c>
       <c r="L68" t="n">
-        <v>224.38</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:15:07</t>
+          <t>09:21:39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.97</v>
+        <v>2.46</v>
       </c>
       <c r="F69" t="n">
-        <v>8.74</v>
+        <v>4.88</v>
       </c>
       <c r="G69" t="n">
-        <v>121.2</v>
+        <v>104.8</v>
       </c>
       <c r="H69" t="n">
-        <v>26</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>78.89</v>
+        <v>-10.67</v>
       </c>
       <c r="K69" t="n">
-        <v>203.31</v>
+        <v>-152.39</v>
       </c>
       <c r="L69" t="n">
-        <v>218.08</v>
+        <v>152.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:16:49</t>
+          <t>09:23:43</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="F70" t="n">
         <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>113.5</v>
+        <v>120.4</v>
       </c>
       <c r="H70" t="n">
-        <v>23</v>
+        <v>38.8</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-163.97</v>
+        <v>148.89</v>
       </c>
       <c r="K70" t="n">
-        <v>112.8</v>
+        <v>21.01</v>
       </c>
       <c r="L70" t="n">
-        <v>199.02</v>
+        <v>150.37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:21:00</t>
+          <t>09:28:58</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="F71" t="n">
         <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>118</v>
+        <v>117.4</v>
       </c>
       <c r="H71" t="n">
-        <v>25.9</v>
+        <v>24.3</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>0.45</v>
+        <v>-210.71</v>
       </c>
       <c r="K71" t="n">
-        <v>-158.48</v>
+        <v>110.36</v>
       </c>
       <c r="L71" t="n">
-        <v>158.48</v>
+        <v>237.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:22:00</t>
+          <t>09:30:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="F72" t="n">
-        <v>7.95</v>
+        <v>7.69</v>
       </c>
       <c r="G72" t="n">
-        <v>113.7</v>
+        <v>102.4</v>
       </c>
       <c r="H72" t="n">
-        <v>23.2</v>
+        <v>83.2</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>119.12</v>
+        <v>235.96</v>
       </c>
       <c r="K72" t="n">
-        <v>-139.9</v>
+        <v>-141.18</v>
       </c>
       <c r="L72" t="n">
-        <v>183.74</v>
+        <v>274.97</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:23:56</t>
+          <t>09:31:53</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.53</v>
+        <v>3.01</v>
       </c>
       <c r="F73" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
       <c r="G73" t="n">
-        <v>106.1</v>
+        <v>113.9</v>
       </c>
       <c r="H73" t="n">
-        <v>25</v>
+        <v>54.2</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>197.95</v>
+        <v>99.97</v>
       </c>
       <c r="K73" t="n">
-        <v>61.37</v>
+        <v>133.66</v>
       </c>
       <c r="L73" t="n">
-        <v>207.24</v>
+        <v>166.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:33:25</t>
+          <t>09:40:38</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.99</v>
+        <v>2.56</v>
       </c>
       <c r="F74" t="n">
-        <v>7.15</v>
+        <v>8.32</v>
       </c>
       <c r="G74" t="n">
-        <v>107.2</v>
+        <v>123.4</v>
       </c>
       <c r="H74" t="n">
-        <v>23.2</v>
+        <v>53.6</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-23.91</v>
+        <v>-32.66</v>
       </c>
       <c r="K74" t="n">
-        <v>-57.02</v>
+        <v>-24.34</v>
       </c>
       <c r="L74" t="n">
-        <v>61.83</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:34:21</t>
+          <t>09:42:51</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="F75" t="n">
-        <v>8.74</v>
+        <v>8.4</v>
       </c>
       <c r="G75" t="n">
-        <v>102.6</v>
+        <v>104.4</v>
       </c>
       <c r="H75" t="n">
-        <v>22.2</v>
+        <v>62.8</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>114.11</v>
+        <v>16.87</v>
       </c>
       <c r="K75" t="n">
-        <v>16.43</v>
+        <v>-45.42</v>
       </c>
       <c r="L75" t="n">
-        <v>115.28</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:35:31</t>
+          <t>09:45:03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="F76" t="n">
         <v>8.74</v>
       </c>
       <c r="G76" t="n">
-        <v>114.4</v>
+        <v>100.6</v>
       </c>
       <c r="H76" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>8.199999999999999</v>
+        <v>-54.14</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.3</v>
+        <v>34.6</v>
       </c>
       <c r="L76" t="n">
-        <v>58.87</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:40:43</t>
+          <t>09:49:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="F77" t="n">
-        <v>8.74</v>
+        <v>4.89</v>
       </c>
       <c r="G77" t="n">
-        <v>100.5</v>
+        <v>110</v>
       </c>
       <c r="H77" t="n">
-        <v>22.2</v>
+        <v>43.5</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-86.79000000000001</v>
+        <v>-65.8</v>
       </c>
       <c r="K77" t="n">
-        <v>-40.61</v>
+        <v>14.45</v>
       </c>
       <c r="L77" t="n">
-        <v>95.81999999999999</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:42:48</t>
+          <t>09:52:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="F78" t="n">
-        <v>7.47</v>
+        <v>4.62</v>
       </c>
       <c r="G78" t="n">
-        <v>108.2</v>
+        <v>117.3</v>
       </c>
       <c r="H78" t="n">
-        <v>25.5</v>
+        <v>69.7</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>87.68000000000001</v>
+        <v>-40.8</v>
       </c>
       <c r="K78" t="n">
-        <v>26.2</v>
+        <v>39.63</v>
       </c>
       <c r="L78" t="n">
-        <v>91.51000000000001</v>
+        <v>56.88</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:44:36</t>
+          <t>09:53:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="F79" t="n">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="G79" t="n">
-        <v>117.4</v>
+        <v>117.9</v>
       </c>
       <c r="H79" t="n">
-        <v>29.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>85.92</v>
+        <v>-60.56</v>
       </c>
       <c r="K79" t="n">
-        <v>35.18</v>
+        <v>-30.57</v>
       </c>
       <c r="L79" t="n">
-        <v>92.84</v>
+        <v>67.84</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:50:33</t>
+          <t>09:59:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="F80" t="n">
-        <v>8.74</v>
+        <v>6.07</v>
       </c>
       <c r="G80" t="n">
-        <v>108</v>
+        <v>109.5</v>
       </c>
       <c r="H80" t="n">
-        <v>25.5</v>
+        <v>57.5</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-139.07</v>
+        <v>-38.6</v>
       </c>
       <c r="K80" t="n">
-        <v>-83.18000000000001</v>
+        <v>108.04</v>
       </c>
       <c r="L80" t="n">
-        <v>162.05</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:51:31</t>
+          <t>10:00:55</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.37</v>
+        <v>2.74</v>
       </c>
       <c r="F81" t="n">
-        <v>6.96</v>
+        <v>7.93</v>
       </c>
       <c r="G81" t="n">
-        <v>112.3</v>
+        <v>109.1</v>
       </c>
       <c r="H81" t="n">
-        <v>25.9</v>
+        <v>49.9</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>98.75</v>
+        <v>-44.15</v>
       </c>
       <c r="K81" t="n">
-        <v>129.95</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>163.22</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:53:28</t>
+          <t>10:02:02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>8.74</v>
+        <v>8.52</v>
       </c>
       <c r="G82" t="n">
-        <v>122</v>
+        <v>118.8</v>
       </c>
       <c r="H82" t="n">
-        <v>22.6</v>
+        <v>59.2</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-99.59</v>
+        <v>2.06</v>
       </c>
       <c r="K82" t="n">
-        <v>136.68</v>
+        <v>127.02</v>
       </c>
       <c r="L82" t="n">
-        <v>169.12</v>
+        <v>127.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:58:55</t>
+          <t>10:05:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="F83" t="n">
-        <v>8.74</v>
+        <v>6.98</v>
       </c>
       <c r="G83" t="n">
-        <v>104.9</v>
+        <v>112.5</v>
       </c>
       <c r="H83" t="n">
-        <v>25.3</v>
+        <v>59.8</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-23.96</v>
+        <v>196.49</v>
       </c>
       <c r="K83" t="n">
-        <v>166.93</v>
+        <v>51.26</v>
       </c>
       <c r="L83" t="n">
-        <v>168.64</v>
+        <v>203.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:01:11</t>
+          <t>10:07:04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.85</v>
+        <v>3.03</v>
       </c>
       <c r="F84" t="n">
-        <v>6.07</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>109</v>
+        <v>106.3</v>
       </c>
       <c r="H84" t="n">
-        <v>22.5</v>
+        <v>56.2</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-171.26</v>
+        <v>130.59</v>
       </c>
       <c r="K84" t="n">
-        <v>103.33</v>
+        <v>69.08</v>
       </c>
       <c r="L84" t="n">
-        <v>200.02</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:02:24</t>
+          <t>10:09:10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="F85" t="n">
         <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>113.9</v>
+        <v>118.5</v>
       </c>
       <c r="H85" t="n">
-        <v>29</v>
+        <v>40.2</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>182.33</v>
+        <v>-128.23</v>
       </c>
       <c r="K85" t="n">
-        <v>-73.28</v>
+        <v>-91.95</v>
       </c>
       <c r="L85" t="n">
-        <v>196.5</v>
+        <v>157.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:08:05</t>
+          <t>10:12:11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="F86" t="n">
-        <v>7.94</v>
+        <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>103.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>230.94</v>
+        <v>110.59</v>
       </c>
       <c r="K86" t="n">
-        <v>-207.31</v>
+        <v>184.42</v>
       </c>
       <c r="L86" t="n">
-        <v>310.34</v>
+        <v>215.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:09:10</t>
+          <t>10:14:02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="F87" t="n">
-        <v>8.02</v>
+        <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>107.8</v>
+        <v>123.7</v>
       </c>
       <c r="H87" t="n">
-        <v>21.5</v>
+        <v>13.5</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>218.49</v>
+        <v>-150.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-135.33</v>
+        <v>-168.66</v>
       </c>
       <c r="L87" t="n">
-        <v>257.01</v>
+        <v>226.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:11:27</t>
+          <t>10:15:28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="F88" t="n">
         <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>115.8</v>
+        <v>100.1</v>
       </c>
       <c r="H88" t="n">
-        <v>24.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>45.33</v>
+        <v>235.9</v>
       </c>
       <c r="K88" t="n">
-        <v>-104.41</v>
+        <v>121.87</v>
       </c>
       <c r="L88" t="n">
-        <v>113.82</v>
+        <v>265.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="F14" t="n">
-        <v>7.05</v>
+        <v>4.49</v>
       </c>
       <c r="G14" t="n">
-        <v>119.1</v>
+        <v>115.2</v>
       </c>
       <c r="H14" t="n">
-        <v>55.7</v>
+        <v>42.9</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.550000000000001</v>
+        <v>-13.3</v>
       </c>
       <c r="K14" t="n">
-        <v>31.09</v>
+        <v>-43.5</v>
       </c>
       <c r="L14" t="n">
-        <v>32.52</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:38:19</t>
+          <t>06:37:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>8.74</v>
+        <v>4.86</v>
       </c>
       <c r="G15" t="n">
-        <v>99.40000000000001</v>
+        <v>101.1</v>
       </c>
       <c r="H15" t="n">
-        <v>61.7</v>
+        <v>36.9</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.41</v>
+        <v>12.25</v>
       </c>
       <c r="K15" t="n">
-        <v>-47.78</v>
+        <v>-35.57</v>
       </c>
       <c r="L15" t="n">
-        <v>47.8</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:39:51</t>
+          <t>06:39:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="F16" t="n">
-        <v>6.22</v>
+        <v>4.89</v>
       </c>
       <c r="G16" t="n">
-        <v>101.3</v>
+        <v>111.8</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>55.7</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>51.46</v>
+        <v>-29.89</v>
       </c>
       <c r="K16" t="n">
-        <v>23.34</v>
+        <v>22.75</v>
       </c>
       <c r="L16" t="n">
-        <v>56.5</v>
+        <v>37.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:43:45</t>
+          <t>06:44:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="F17" t="n">
-        <v>4.39</v>
+        <v>5.64</v>
       </c>
       <c r="G17" t="n">
-        <v>114.8</v>
+        <v>112.2</v>
       </c>
       <c r="H17" t="n">
-        <v>60.3</v>
+        <v>62.8</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>52.58</v>
+        <v>52.87</v>
       </c>
       <c r="K17" t="n">
-        <v>14.55</v>
+        <v>-0.57</v>
       </c>
       <c r="L17" t="n">
-        <v>54.56</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:40</t>
+          <t>06:46:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="F18" t="n">
-        <v>8.74</v>
+        <v>7.33</v>
       </c>
       <c r="G18" t="n">
-        <v>93.2</v>
+        <v>102.1</v>
       </c>
       <c r="H18" t="n">
-        <v>64.59999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>74.04000000000001</v>
+        <v>24.37</v>
       </c>
       <c r="K18" t="n">
-        <v>32.96</v>
+        <v>-46.9</v>
       </c>
       <c r="L18" t="n">
-        <v>81.05</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:48:29</t>
+          <t>06:47:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="F19" t="n">
-        <v>7.04</v>
+        <v>7.36</v>
       </c>
       <c r="G19" t="n">
-        <v>121.6</v>
+        <v>111.2</v>
       </c>
       <c r="H19" t="n">
-        <v>57.9</v>
+        <v>36.2</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>57.01</v>
+        <v>90.08</v>
       </c>
       <c r="K19" t="n">
-        <v>22.76</v>
+        <v>-31.38</v>
       </c>
       <c r="L19" t="n">
-        <v>61.38</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:52:05</t>
+          <t>06:53:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="F20" t="n">
-        <v>8.43</v>
+        <v>4.52</v>
       </c>
       <c r="G20" t="n">
-        <v>99.40000000000001</v>
+        <v>122.4</v>
       </c>
       <c r="H20" t="n">
-        <v>69.2</v>
+        <v>63.1</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-32.1</v>
+        <v>-65.58</v>
       </c>
       <c r="K20" t="n">
-        <v>123.56</v>
+        <v>-27.2</v>
       </c>
       <c r="L20" t="n">
-        <v>127.67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:52:52</t>
+          <t>06:55:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="F21" t="n">
-        <v>4.04</v>
+        <v>6.16</v>
       </c>
       <c r="G21" t="n">
-        <v>117.9</v>
+        <v>102.6</v>
       </c>
       <c r="H21" t="n">
-        <v>36.8</v>
+        <v>41.5</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>30.23</v>
+        <v>97.06</v>
       </c>
       <c r="K21" t="n">
-        <v>-46.97</v>
+        <v>6.21</v>
       </c>
       <c r="L21" t="n">
-        <v>55.86</v>
+        <v>97.26000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:54:58</t>
+          <t>06:57:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="F22" t="n">
-        <v>6.78</v>
+        <v>8.74</v>
       </c>
       <c r="G22" t="n">
-        <v>99.40000000000001</v>
+        <v>117.5</v>
       </c>
       <c r="H22" t="n">
-        <v>41</v>
+        <v>26.8</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-105.51</v>
+        <v>-6.54</v>
       </c>
       <c r="K22" t="n">
-        <v>-23.31</v>
+        <v>85.89</v>
       </c>
       <c r="L22" t="n">
-        <v>108.06</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:00:04</t>
+          <t>07:01:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="F23" t="n">
-        <v>7.99</v>
+        <v>6.28</v>
       </c>
       <c r="G23" t="n">
-        <v>119.1</v>
+        <v>110.1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-91.72</v>
+        <v>-104.64</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.47</v>
+        <v>63.23</v>
       </c>
       <c r="L23" t="n">
-        <v>153.01</v>
+        <v>122.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:02:10</t>
+          <t>07:02:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="F24" t="n">
-        <v>6.93</v>
+        <v>7.1</v>
       </c>
       <c r="G24" t="n">
-        <v>110.6</v>
+        <v>99.5</v>
       </c>
       <c r="H24" t="n">
-        <v>31.3</v>
+        <v>22.2</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>44.26</v>
+        <v>129.85</v>
       </c>
       <c r="K24" t="n">
-        <v>149.57</v>
+        <v>18.77</v>
       </c>
       <c r="L24" t="n">
-        <v>155.98</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:03:20</t>
+          <t>07:04:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.71</v>
+        <v>2.27</v>
       </c>
       <c r="F25" t="n">
-        <v>8.73</v>
+        <v>3.44</v>
       </c>
       <c r="G25" t="n">
-        <v>113</v>
+        <v>106.5</v>
       </c>
       <c r="H25" t="n">
-        <v>42.2</v>
+        <v>78.5</v>
       </c>
       <c r="I25" t="n">
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-70.79000000000001</v>
+        <v>116.96</v>
       </c>
       <c r="K25" t="n">
-        <v>134.73</v>
+        <v>-20.68</v>
       </c>
       <c r="L25" t="n">
-        <v>152.19</v>
+        <v>118.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:08:06</t>
+          <t>07:10:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="F26" t="n">
-        <v>6.09</v>
+        <v>8.74</v>
       </c>
       <c r="G26" t="n">
-        <v>105.1</v>
+        <v>124.9</v>
       </c>
       <c r="H26" t="n">
-        <v>42.5</v>
+        <v>23.2</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>22.39</v>
+        <v>-102.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-165.38</v>
+        <v>-147.33</v>
       </c>
       <c r="L26" t="n">
-        <v>166.89</v>
+        <v>179.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:09:44</t>
+          <t>07:12:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="F27" t="n">
-        <v>5.08</v>
+        <v>5.51</v>
       </c>
       <c r="G27" t="n">
-        <v>111.9</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>37.8</v>
+        <v>7.7</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-14.81</v>
+        <v>15.96</v>
       </c>
       <c r="K27" t="n">
-        <v>-195</v>
+        <v>-101.26</v>
       </c>
       <c r="L27" t="n">
-        <v>195.56</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:11:54</t>
+          <t>07:13:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="F28" t="n">
-        <v>6.41</v>
+        <v>8.74</v>
       </c>
       <c r="G28" t="n">
-        <v>109.1</v>
+        <v>117.9</v>
       </c>
       <c r="H28" t="n">
-        <v>21.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-85.66</v>
+        <v>36.37</v>
       </c>
       <c r="K28" t="n">
-        <v>145.07</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>168.47</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:21:02</t>
+          <t>07:22:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.75</v>
+        <v>3.91</v>
       </c>
       <c r="F29" t="n">
-        <v>8.74</v>
+        <v>7.88</v>
       </c>
       <c r="G29" t="n">
-        <v>115.9</v>
+        <v>103</v>
       </c>
       <c r="H29" t="n">
-        <v>81.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>25.56</v>
+        <v>-60.16</v>
       </c>
       <c r="K29" t="n">
-        <v>44.44</v>
+        <v>-25.03</v>
       </c>
       <c r="L29" t="n">
-        <v>51.27</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:23:08</t>
+          <t>07:23:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="F30" t="n">
-        <v>8.029999999999999</v>
+        <v>4.73</v>
       </c>
       <c r="G30" t="n">
-        <v>99.2</v>
+        <v>117.9</v>
       </c>
       <c r="H30" t="n">
-        <v>44.6</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>37.17</v>
+        <v>30.37</v>
       </c>
       <c r="K30" t="n">
-        <v>-17.8</v>
+        <v>6.23</v>
       </c>
       <c r="L30" t="n">
-        <v>41.21</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:24:43</t>
+          <t>07:25:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="F31" t="n">
-        <v>7.74</v>
+        <v>8.74</v>
       </c>
       <c r="G31" t="n">
-        <v>121.4</v>
+        <v>114.3</v>
       </c>
       <c r="H31" t="n">
-        <v>47.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.75</v>
+        <v>-20.49</v>
       </c>
       <c r="K31" t="n">
-        <v>-51.14</v>
+        <v>32.59</v>
       </c>
       <c r="L31" t="n">
-        <v>56.39</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:29:27</t>
+          <t>07:30:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
       <c r="F32" t="n">
-        <v>4.18</v>
+        <v>5.09</v>
       </c>
       <c r="G32" t="n">
-        <v>104.2</v>
+        <v>113.5</v>
       </c>
       <c r="H32" t="n">
-        <v>80.90000000000001</v>
+        <v>38.3</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>27.32</v>
+        <v>16.39</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.66</v>
+        <v>-46.03</v>
       </c>
       <c r="L32" t="n">
-        <v>27.32</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:30:53</t>
+          <t>07:31:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="F33" t="n">
-        <v>5.12</v>
+        <v>6.78</v>
       </c>
       <c r="G33" t="n">
-        <v>116.4</v>
+        <v>106.7</v>
       </c>
       <c r="H33" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>38.77</v>
+        <v>-55.29</v>
       </c>
       <c r="K33" t="n">
-        <v>5.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>39.15</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:31:37</t>
+          <t>07:31:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="F34" t="n">
-        <v>6.07</v>
+        <v>5.24</v>
       </c>
       <c r="G34" t="n">
-        <v>110.9</v>
+        <v>122.4</v>
       </c>
       <c r="H34" t="n">
-        <v>15.7</v>
+        <v>51.3</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>68.15000000000001</v>
+        <v>-39.23</v>
       </c>
       <c r="K34" t="n">
-        <v>-17.19</v>
+        <v>-58.51</v>
       </c>
       <c r="L34" t="n">
-        <v>70.28</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:37:27</t>
+          <t>07:35:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.79</v>
+        <v>2.23</v>
       </c>
       <c r="F35" t="n">
-        <v>7.39</v>
+        <v>6.72</v>
       </c>
       <c r="G35" t="n">
-        <v>111.9</v>
+        <v>115.7</v>
       </c>
       <c r="H35" t="n">
-        <v>31</v>
+        <v>51.3</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>12.79</v>
+        <v>-59.89</v>
       </c>
       <c r="K35" t="n">
-        <v>115.21</v>
+        <v>46.32</v>
       </c>
       <c r="L35" t="n">
-        <v>115.91</v>
+        <v>75.70999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:39:02</t>
+          <t>07:36:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="F36" t="n">
-        <v>8.74</v>
+        <v>4.98</v>
       </c>
       <c r="G36" t="n">
-        <v>100.2</v>
+        <v>116.6</v>
       </c>
       <c r="H36" t="n">
-        <v>15.5</v>
+        <v>47.8</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>102.08</v>
+        <v>64.64</v>
       </c>
       <c r="K36" t="n">
-        <v>40.93</v>
+        <v>57.13</v>
       </c>
       <c r="L36" t="n">
-        <v>109.98</v>
+        <v>86.26000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:40:37</t>
+          <t>07:37:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="F37" t="n">
-        <v>6.77</v>
+        <v>8.74</v>
       </c>
       <c r="G37" t="n">
-        <v>106.3</v>
+        <v>108.6</v>
       </c>
       <c r="H37" t="n">
-        <v>60.3</v>
+        <v>39.1</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-108</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>66.86</v>
+        <v>-39.34</v>
       </c>
       <c r="L37" t="n">
-        <v>127.02</v>
+        <v>75.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:45:02</t>
+          <t>07:42:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>5.91</v>
+        <v>8.01</v>
       </c>
       <c r="G38" t="n">
-        <v>118.3</v>
+        <v>103.5</v>
       </c>
       <c r="H38" t="n">
-        <v>48.8</v>
+        <v>24.6</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>48.21</v>
+        <v>-115.44</v>
       </c>
       <c r="K38" t="n">
-        <v>-113.99</v>
+        <v>55.87</v>
       </c>
       <c r="L38" t="n">
-        <v>123.77</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:47:05</t>
+          <t>07:43:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="F39" t="n">
-        <v>7.4</v>
+        <v>5.52</v>
       </c>
       <c r="G39" t="n">
-        <v>102.6</v>
+        <v>103.4</v>
       </c>
       <c r="H39" t="n">
-        <v>33</v>
+        <v>43.8</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-26.45</v>
+        <v>-125.07</v>
       </c>
       <c r="K39" t="n">
-        <v>198.89</v>
+        <v>71.94</v>
       </c>
       <c r="L39" t="n">
-        <v>200.64</v>
+        <v>144.29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:48:04</t>
+          <t>07:45:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.11</v>
+        <v>2.76</v>
       </c>
       <c r="F40" t="n">
-        <v>8.74</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>106</v>
+        <v>119.2</v>
       </c>
       <c r="H40" t="n">
-        <v>59.2</v>
+        <v>58</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>137.35</v>
+        <v>-114.02</v>
       </c>
       <c r="K40" t="n">
-        <v>11.44</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>137.82</v>
+        <v>140.33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:53:22</t>
+          <t>07:50:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="F41" t="n">
-        <v>6.51</v>
+        <v>6.8</v>
       </c>
       <c r="G41" t="n">
-        <v>105.9</v>
+        <v>104.9</v>
       </c>
       <c r="H41" t="n">
-        <v>58.5</v>
+        <v>41.2</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>90.81999999999999</v>
+        <v>-98.42</v>
       </c>
       <c r="K41" t="n">
-        <v>202.6</v>
+        <v>-110.79</v>
       </c>
       <c r="L41" t="n">
-        <v>222.02</v>
+        <v>148.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:55:36</t>
+          <t>07:52:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="F42" t="n">
-        <v>8.41</v>
+        <v>6.83</v>
       </c>
       <c r="G42" t="n">
-        <v>107.8</v>
+        <v>108.9</v>
       </c>
       <c r="H42" t="n">
-        <v>61.5</v>
+        <v>50.7</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-256.09</v>
+        <v>-46.94</v>
       </c>
       <c r="K42" t="n">
-        <v>7.45</v>
+        <v>-210.81</v>
       </c>
       <c r="L42" t="n">
-        <v>256.2</v>
+        <v>215.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:58:20</t>
+          <t>07:54:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="F43" t="n">
-        <v>8.74</v>
+        <v>3.17</v>
       </c>
       <c r="G43" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="H43" t="n">
-        <v>61</v>
+        <v>30.5</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>216.12</v>
+        <v>0.22</v>
       </c>
       <c r="K43" t="n">
-        <v>123.89</v>
+        <v>150.51</v>
       </c>
       <c r="L43" t="n">
-        <v>249.11</v>
+        <v>150.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:10:08</t>
+          <t>08:06:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="F44" t="n">
-        <v>8.17</v>
+        <v>4.51</v>
       </c>
       <c r="G44" t="n">
-        <v>106.5</v>
+        <v>101.2</v>
       </c>
       <c r="H44" t="n">
-        <v>23.9</v>
+        <v>29.2</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-43.52</v>
+        <v>-36.22</v>
       </c>
       <c r="K44" t="n">
-        <v>-21.99</v>
+        <v>-5.15</v>
       </c>
       <c r="L44" t="n">
-        <v>48.76</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:12:14</t>
+          <t>08:08:13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="F45" t="n">
-        <v>6.94</v>
+        <v>8.74</v>
       </c>
       <c r="G45" t="n">
-        <v>103.1</v>
+        <v>100.6</v>
       </c>
       <c r="H45" t="n">
-        <v>34.7</v>
+        <v>40.3</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>4.7</v>
+        <v>34.11</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.58</v>
+        <v>3.45</v>
       </c>
       <c r="L45" t="n">
-        <v>32.92</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:14:37</t>
+          <t>08:10:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="F46" t="n">
-        <v>6.29</v>
+        <v>7.84</v>
       </c>
       <c r="G46" t="n">
-        <v>110.6</v>
+        <v>121.3</v>
       </c>
       <c r="H46" t="n">
-        <v>45.5</v>
+        <v>35.2</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>24.93</v>
+        <v>10.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-38.21</v>
+        <v>48.68</v>
       </c>
       <c r="L46" t="n">
-        <v>45.62</v>
+        <v>49.79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:20:37</t>
+          <t>08:15:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="F47" t="n">
         <v>8.74</v>
       </c>
       <c r="G47" t="n">
-        <v>118.2</v>
+        <v>105.6</v>
       </c>
       <c r="H47" t="n">
-        <v>46.5</v>
+        <v>45.4</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>51.37</v>
+        <v>71.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-31.84</v>
+        <v>-11.17</v>
       </c>
       <c r="L47" t="n">
-        <v>60.43</v>
+        <v>72.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:21:26</t>
+          <t>08:16:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="F48" t="n">
-        <v>7.11</v>
+        <v>5.15</v>
       </c>
       <c r="G48" t="n">
-        <v>117.2</v>
+        <v>121.6</v>
       </c>
       <c r="H48" t="n">
-        <v>44.8</v>
+        <v>25.6</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>60.26</v>
+        <v>-38.57</v>
       </c>
       <c r="K48" t="n">
-        <v>10.84</v>
+        <v>15.18</v>
       </c>
       <c r="L48" t="n">
-        <v>61.23</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:23:00</t>
+          <t>08:18:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="F49" t="n">
-        <v>7.56</v>
+        <v>8.74</v>
       </c>
       <c r="G49" t="n">
-        <v>118.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>50.1</v>
+        <v>43.7</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>74.40000000000001</v>
+        <v>-30.14</v>
       </c>
       <c r="K49" t="n">
-        <v>-76.01000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="L49" t="n">
-        <v>106.36</v>
+        <v>91.45999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:27:47</t>
+          <t>08:23:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="F50" t="n">
-        <v>5.69</v>
+        <v>8.74</v>
       </c>
       <c r="G50" t="n">
-        <v>113.9</v>
+        <v>113.4</v>
       </c>
       <c r="H50" t="n">
-        <v>72.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>67.36</v>
+        <v>-58.01</v>
       </c>
       <c r="K50" t="n">
-        <v>51.09</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>84.55</v>
+        <v>107.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:29:42</t>
+          <t>08:25:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.11</v>
+        <v>2.71</v>
       </c>
       <c r="F51" t="n">
-        <v>8.74</v>
+        <v>7.43</v>
       </c>
       <c r="G51" t="n">
-        <v>125</v>
+        <v>115.8</v>
       </c>
       <c r="H51" t="n">
-        <v>43.5</v>
+        <v>78.5</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-95.58</v>
+        <v>63.79</v>
       </c>
       <c r="K51" t="n">
-        <v>83.66</v>
+        <v>-57.24</v>
       </c>
       <c r="L51" t="n">
-        <v>127.02</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:26:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="F52" t="n">
-        <v>8.050000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>121.3</v>
+        <v>127.7</v>
       </c>
       <c r="H52" t="n">
-        <v>27.2</v>
+        <v>30.4</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-93.19</v>
+        <v>-68.45</v>
       </c>
       <c r="K52" t="n">
-        <v>10.98</v>
+        <v>-97.26000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>93.84</v>
+        <v>118.93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:34:18</t>
+          <t>08:31:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.96</v>
+        <v>2.47</v>
       </c>
       <c r="F53" t="n">
-        <v>8.74</v>
+        <v>7.71</v>
       </c>
       <c r="G53" t="n">
-        <v>123.3</v>
+        <v>112</v>
       </c>
       <c r="H53" t="n">
-        <v>58.7</v>
+        <v>50</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>7.52</v>
+        <v>-55.04</v>
       </c>
       <c r="K53" t="n">
-        <v>-150.2</v>
+        <v>84.09</v>
       </c>
       <c r="L53" t="n">
-        <v>150.39</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:36:33</t>
+          <t>08:33:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="F54" t="n">
-        <v>8.74</v>
+        <v>8.16</v>
       </c>
       <c r="G54" t="n">
-        <v>98.3</v>
+        <v>111.9</v>
       </c>
       <c r="H54" t="n">
-        <v>31.4</v>
+        <v>40.9</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-216.82</v>
+        <v>194.85</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.23</v>
+        <v>41.61</v>
       </c>
       <c r="L54" t="n">
-        <v>216.91</v>
+        <v>199.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:37:31</t>
+          <t>08:35:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="F55" t="n">
-        <v>7.98</v>
+        <v>8.74</v>
       </c>
       <c r="G55" t="n">
-        <v>113.9</v>
+        <v>116.2</v>
       </c>
       <c r="H55" t="n">
-        <v>6.3</v>
+        <v>60.5</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>103.43</v>
+        <v>108.04</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.6</v>
+        <v>40.15</v>
       </c>
       <c r="L55" t="n">
-        <v>146.39</v>
+        <v>115.26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:41:54</t>
+          <t>08:38:28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.5</v>
+        <v>3.51</v>
       </c>
       <c r="F56" t="n">
         <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>113.4</v>
+        <v>99.3</v>
       </c>
       <c r="H56" t="n">
-        <v>36.1</v>
+        <v>27.2</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>189.97</v>
+        <v>244.12</v>
       </c>
       <c r="K56" t="n">
-        <v>-57.19</v>
+        <v>-165.19</v>
       </c>
       <c r="L56" t="n">
-        <v>198.39</v>
+        <v>294.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:43:36</t>
+          <t>08:40:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="F57" t="n">
-        <v>8.74</v>
+        <v>5.7</v>
       </c>
       <c r="G57" t="n">
-        <v>115.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>51.4</v>
+        <v>41</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>65.04000000000001</v>
+        <v>-239.35</v>
       </c>
       <c r="K57" t="n">
-        <v>-182.63</v>
+        <v>-41.15</v>
       </c>
       <c r="L57" t="n">
-        <v>193.87</v>
+        <v>242.86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:45:06</t>
+          <t>08:42:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.27</v>
+        <v>2.82</v>
       </c>
       <c r="F58" t="n">
         <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>110.1</v>
+        <v>83.7</v>
       </c>
       <c r="H58" t="n">
-        <v>30.4</v>
+        <v>52.8</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>84.48999999999999</v>
+        <v>-200.06</v>
       </c>
       <c r="K58" t="n">
-        <v>-232.68</v>
+        <v>36.65</v>
       </c>
       <c r="L58" t="n">
-        <v>247.54</v>
+        <v>203.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:57:57</t>
+          <t>08:53:03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="F59" t="n">
-        <v>5.48</v>
+        <v>7.28</v>
       </c>
       <c r="G59" t="n">
-        <v>98.90000000000001</v>
+        <v>114.5</v>
       </c>
       <c r="H59" t="n">
-        <v>15.7</v>
+        <v>24.3</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>15.49</v>
+        <v>46.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.4</v>
+        <v>-24.61</v>
       </c>
       <c r="L59" t="n">
-        <v>21.84</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:59:40</t>
+          <t>08:53:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.39</v>
+        <v>3.01</v>
       </c>
       <c r="F60" t="n">
-        <v>6.99</v>
+        <v>8.74</v>
       </c>
       <c r="G60" t="n">
-        <v>111.9</v>
+        <v>116.7</v>
       </c>
       <c r="H60" t="n">
-        <v>59.5</v>
+        <v>51.6</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>23.25</v>
+        <v>3.3</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.6</v>
+        <v>-52.39</v>
       </c>
       <c r="L60" t="n">
-        <v>23.91</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:01:12</t>
+          <t>08:55:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="F61" t="n">
-        <v>8.74</v>
+        <v>8.33</v>
       </c>
       <c r="G61" t="n">
-        <v>122.6</v>
+        <v>109.3</v>
       </c>
       <c r="H61" t="n">
-        <v>50.9</v>
+        <v>43</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>71.16</v>
+        <v>41.97</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.03</v>
+        <v>14.45</v>
       </c>
       <c r="L61" t="n">
-        <v>79.77</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:06:10</t>
+          <t>09:01:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.19</v>
+        <v>2.72</v>
       </c>
       <c r="F62" t="n">
-        <v>8.74</v>
+        <v>7.51</v>
       </c>
       <c r="G62" t="n">
-        <v>111.9</v>
+        <v>102.6</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>28.25</v>
+        <v>-39.62</v>
       </c>
       <c r="K62" t="n">
-        <v>-82.20999999999999</v>
+        <v>58.69</v>
       </c>
       <c r="L62" t="n">
-        <v>86.93000000000001</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:07:13</t>
+          <t>09:03:31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="F63" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="G63" t="n">
-        <v>106.7</v>
+        <v>110.9</v>
       </c>
       <c r="H63" t="n">
-        <v>48.2</v>
+        <v>30</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-85</v>
+        <v>-41</v>
       </c>
       <c r="K63" t="n">
-        <v>-20.93</v>
+        <v>-51.33</v>
       </c>
       <c r="L63" t="n">
-        <v>87.54000000000001</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:08:50</t>
+          <t>09:06:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="F64" t="n">
-        <v>8.210000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G64" t="n">
-        <v>107.9</v>
+        <v>119.7</v>
       </c>
       <c r="H64" t="n">
-        <v>29.1</v>
+        <v>66</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>32.05</v>
+        <v>-80.63</v>
       </c>
       <c r="K64" t="n">
-        <v>87.31999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="L64" t="n">
-        <v>93.01000000000001</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:13:39</t>
+          <t>09:09:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.93</v>
+        <v>3.73</v>
       </c>
       <c r="F65" t="n">
-        <v>7.62</v>
+        <v>8.74</v>
       </c>
       <c r="G65" t="n">
-        <v>115.6</v>
+        <v>110.2</v>
       </c>
       <c r="H65" t="n">
-        <v>41.9</v>
+        <v>49.8</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>57.91</v>
+        <v>-1.1</v>
       </c>
       <c r="K65" t="n">
-        <v>75.98999999999999</v>
+        <v>129.54</v>
       </c>
       <c r="L65" t="n">
-        <v>95.54000000000001</v>
+        <v>129.54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:14:30</t>
+          <t>09:11:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="F66" t="n">
         <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>115.4</v>
+        <v>104.6</v>
       </c>
       <c r="H66" t="n">
-        <v>65.09999999999999</v>
+        <v>45.7</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>86.02</v>
+        <v>-84.22</v>
       </c>
       <c r="K66" t="n">
-        <v>-70.41</v>
+        <v>51.68</v>
       </c>
       <c r="L66" t="n">
-        <v>111.16</v>
+        <v>98.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:16:30</t>
+          <t>09:12:40</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="F67" t="n">
-        <v>8.74</v>
+        <v>6.56</v>
       </c>
       <c r="G67" t="n">
-        <v>119.7</v>
+        <v>100.3</v>
       </c>
       <c r="H67" t="n">
-        <v>55.6</v>
+        <v>12.1</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>110.64</v>
+        <v>-92.16</v>
       </c>
       <c r="K67" t="n">
-        <v>68.58</v>
+        <v>-24.97</v>
       </c>
       <c r="L67" t="n">
-        <v>130.18</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:20:26</t>
+          <t>09:16:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="F68" t="n">
-        <v>7.8</v>
+        <v>8.74</v>
       </c>
       <c r="G68" t="n">
-        <v>121.7</v>
+        <v>104.2</v>
       </c>
       <c r="H68" t="n">
-        <v>20.3</v>
+        <v>30.1</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>100.71</v>
+        <v>142.5</v>
       </c>
       <c r="K68" t="n">
-        <v>-78.83</v>
+        <v>-33.57</v>
       </c>
       <c r="L68" t="n">
-        <v>127.9</v>
+        <v>146.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:21:39</t>
+          <t>09:19:06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="F69" t="n">
-        <v>4.88</v>
+        <v>7.45</v>
       </c>
       <c r="G69" t="n">
-        <v>104.8</v>
+        <v>102.6</v>
       </c>
       <c r="H69" t="n">
-        <v>75.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.67</v>
+        <v>7.36</v>
       </c>
       <c r="K69" t="n">
-        <v>-152.39</v>
+        <v>-151.89</v>
       </c>
       <c r="L69" t="n">
-        <v>152.76</v>
+        <v>152.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:23:43</t>
+          <t>09:20:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="F70" t="n">
         <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>120.4</v>
+        <v>111.9</v>
       </c>
       <c r="H70" t="n">
-        <v>38.8</v>
+        <v>31</v>
       </c>
       <c r="I70" t="n">
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>148.89</v>
+        <v>-157.68</v>
       </c>
       <c r="K70" t="n">
-        <v>21.01</v>
+        <v>-12.02</v>
       </c>
       <c r="L70" t="n">
-        <v>150.37</v>
+        <v>158.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:28:58</t>
+          <t>09:24:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="F71" t="n">
-        <v>8.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>117.4</v>
+        <v>113</v>
       </c>
       <c r="H71" t="n">
-        <v>24.3</v>
+        <v>39.8</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-210.71</v>
+        <v>-76.78</v>
       </c>
       <c r="K71" t="n">
-        <v>110.36</v>
+        <v>-140.68</v>
       </c>
       <c r="L71" t="n">
-        <v>237.86</v>
+        <v>160.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:30:27</t>
+          <t>09:26:45</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="F72" t="n">
-        <v>7.69</v>
+        <v>8.74</v>
       </c>
       <c r="G72" t="n">
-        <v>102.4</v>
+        <v>121.3</v>
       </c>
       <c r="H72" t="n">
-        <v>83.2</v>
+        <v>28.2</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>235.96</v>
+        <v>-242.34</v>
       </c>
       <c r="K72" t="n">
-        <v>-141.18</v>
+        <v>-145.24</v>
       </c>
       <c r="L72" t="n">
-        <v>274.97</v>
+        <v>282.53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:31:53</t>
+          <t>09:28:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="F73" t="n">
-        <v>8.74</v>
+        <v>5.02</v>
       </c>
       <c r="G73" t="n">
-        <v>113.9</v>
+        <v>118.3</v>
       </c>
       <c r="H73" t="n">
-        <v>54.2</v>
+        <v>48.8</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>99.97</v>
+        <v>41.24</v>
       </c>
       <c r="K73" t="n">
-        <v>133.66</v>
+        <v>-153.75</v>
       </c>
       <c r="L73" t="n">
-        <v>166.91</v>
+        <v>159.19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:40:38</t>
+          <t>09:41:11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="F74" t="n">
-        <v>8.32</v>
+        <v>8.74</v>
       </c>
       <c r="G74" t="n">
-        <v>123.4</v>
+        <v>105.6</v>
       </c>
       <c r="H74" t="n">
-        <v>53.6</v>
+        <v>56.8</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-32.66</v>
+        <v>38.32</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.34</v>
+        <v>-21.14</v>
       </c>
       <c r="L74" t="n">
-        <v>40.73</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:42:51</t>
+          <t>09:43:38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.55</v>
+        <v>3.32</v>
       </c>
       <c r="F75" t="n">
-        <v>8.4</v>
+        <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>104.4</v>
+        <v>106</v>
       </c>
       <c r="H75" t="n">
-        <v>62.8</v>
+        <v>59.2</v>
       </c>
       <c r="I75" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>16.87</v>
+        <v>41.06</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.42</v>
+        <v>7.15</v>
       </c>
       <c r="L75" t="n">
-        <v>48.45</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:45:03</t>
+          <t>09:45:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="F76" t="n">
-        <v>8.74</v>
+        <v>7.86</v>
       </c>
       <c r="G76" t="n">
-        <v>100.6</v>
+        <v>115.8</v>
       </c>
       <c r="H76" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-54.14</v>
+        <v>-21.67</v>
       </c>
       <c r="K76" t="n">
-        <v>34.6</v>
+        <v>-54.02</v>
       </c>
       <c r="L76" t="n">
-        <v>64.25</v>
+        <v>58.21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:49:46</t>
+          <t>09:49:14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.58</v>
+        <v>3.16</v>
       </c>
       <c r="F77" t="n">
-        <v>4.89</v>
+        <v>8.74</v>
       </c>
       <c r="G77" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H77" t="n">
-        <v>43.5</v>
+        <v>34.9</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.8</v>
+        <v>-59.28</v>
       </c>
       <c r="K77" t="n">
-        <v>14.45</v>
+        <v>55.07</v>
       </c>
       <c r="L77" t="n">
-        <v>67.36</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:52:20</t>
+          <t>09:50:49</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="F78" t="n">
-        <v>4.62</v>
+        <v>8.74</v>
       </c>
       <c r="G78" t="n">
-        <v>117.3</v>
+        <v>114.5</v>
       </c>
       <c r="H78" t="n">
-        <v>69.7</v>
+        <v>79.7</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-40.8</v>
+        <v>46.36</v>
       </c>
       <c r="K78" t="n">
-        <v>39.63</v>
+        <v>55.92</v>
       </c>
       <c r="L78" t="n">
-        <v>56.88</v>
+        <v>72.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:53:40</t>
+          <t>09:51:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="F79" t="n">
-        <v>5.75</v>
+        <v>8.74</v>
       </c>
       <c r="G79" t="n">
-        <v>117.9</v>
+        <v>102</v>
       </c>
       <c r="H79" t="n">
-        <v>71.40000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-60.56</v>
+        <v>64.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-30.57</v>
+        <v>-3.62</v>
       </c>
       <c r="L79" t="n">
-        <v>67.84</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:59:13</t>
+          <t>09:55:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="F80" t="n">
-        <v>6.07</v>
+        <v>8.74</v>
       </c>
       <c r="G80" t="n">
-        <v>109.5</v>
+        <v>109.9</v>
       </c>
       <c r="H80" t="n">
-        <v>57.5</v>
+        <v>48.7</v>
       </c>
       <c r="I80" t="n">
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-38.6</v>
+        <v>-87.91</v>
       </c>
       <c r="K80" t="n">
-        <v>108.04</v>
+        <v>36.14</v>
       </c>
       <c r="L80" t="n">
-        <v>114.73</v>
+        <v>95.05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:00:55</t>
+          <t>09:56:51</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="F81" t="n">
-        <v>7.93</v>
+        <v>7.53</v>
       </c>
       <c r="G81" t="n">
-        <v>109.1</v>
+        <v>110.6</v>
       </c>
       <c r="H81" t="n">
-        <v>49.9</v>
+        <v>29.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-44.15</v>
+        <v>-120.61</v>
       </c>
       <c r="K81" t="n">
-        <v>74.54000000000001</v>
+        <v>-3.06</v>
       </c>
       <c r="L81" t="n">
-        <v>86.63</v>
+        <v>120.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:02:02</t>
+          <t>09:58:10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="F82" t="n">
-        <v>8.52</v>
+        <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>118.8</v>
+        <v>113.3</v>
       </c>
       <c r="H82" t="n">
-        <v>59.2</v>
+        <v>60.8</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>2.06</v>
+        <v>-82.37</v>
       </c>
       <c r="K82" t="n">
-        <v>127.02</v>
+        <v>62.92</v>
       </c>
       <c r="L82" t="n">
-        <v>127.04</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:05:04</t>
+          <t>10:03:32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="F83" t="n">
-        <v>6.98</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>112.5</v>
+        <v>110.3</v>
       </c>
       <c r="H83" t="n">
-        <v>59.8</v>
+        <v>40.9</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>196.49</v>
+        <v>-176.59</v>
       </c>
       <c r="K83" t="n">
-        <v>51.26</v>
+        <v>19.49</v>
       </c>
       <c r="L83" t="n">
-        <v>203.07</v>
+        <v>177.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:07:04</t>
+          <t>10:05:53</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.03</v>
+        <v>2.65</v>
       </c>
       <c r="F84" t="n">
-        <v>8.109999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>106.3</v>
+        <v>103.6</v>
       </c>
       <c r="H84" t="n">
-        <v>56.2</v>
+        <v>44.8</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>130.59</v>
+        <v>-122.36</v>
       </c>
       <c r="K84" t="n">
-        <v>69.08</v>
+        <v>-113.81</v>
       </c>
       <c r="L84" t="n">
-        <v>147.73</v>
+        <v>167.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:09:10</t>
+          <t>10:08:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="F85" t="n">
         <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>118.5</v>
+        <v>105.1</v>
       </c>
       <c r="H85" t="n">
-        <v>40.2</v>
+        <v>16.3</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-128.23</v>
+        <v>56.32</v>
       </c>
       <c r="K85" t="n">
-        <v>-91.95</v>
+        <v>201.65</v>
       </c>
       <c r="L85" t="n">
-        <v>157.79</v>
+        <v>209.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:12:11</t>
+          <t>10:11:54</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="F86" t="n">
-        <v>8.74</v>
+        <v>7.19</v>
       </c>
       <c r="G86" t="n">
-        <v>90.09999999999999</v>
+        <v>122</v>
       </c>
       <c r="H86" t="n">
-        <v>19.5</v>
+        <v>71</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>110.59</v>
+        <v>62.99</v>
       </c>
       <c r="K86" t="n">
-        <v>184.42</v>
+        <v>193.35</v>
       </c>
       <c r="L86" t="n">
-        <v>215.03</v>
+        <v>203.36</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:14:02</t>
+          <t>10:13:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="F87" t="n">
         <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>123.7</v>
+        <v>118.5</v>
       </c>
       <c r="H87" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-150.72</v>
+        <v>123.1</v>
       </c>
       <c r="K87" t="n">
-        <v>-168.66</v>
+        <v>-125.54</v>
       </c>
       <c r="L87" t="n">
-        <v>226.2</v>
+        <v>175.83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:15:28</t>
+          <t>10:15:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.26</v>
+        <v>2.66</v>
       </c>
       <c r="F88" t="n">
-        <v>8.74</v>
+        <v>8.15</v>
       </c>
       <c r="G88" t="n">
-        <v>100.1</v>
+        <v>116.4</v>
       </c>
       <c r="H88" t="n">
-        <v>65.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>235.9</v>
+        <v>-180.49</v>
       </c>
       <c r="K88" t="n">
-        <v>121.87</v>
+        <v>114.05</v>
       </c>
       <c r="L88" t="n">
-        <v>265.52</v>
+        <v>213.51</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>85.15000000000001</v>
+        <v>81.61</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.38</v>
+        <v>-18.57</v>
       </c>
       <c r="L14" t="n">
-        <v>87.33</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.32</v>
+        <v>-19.86</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.54</v>
+        <v>-58.12</v>
       </c>
       <c r="L15" t="n">
-        <v>59.75</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>24.14</v>
+        <v>25.05</v>
       </c>
       <c r="K16" t="n">
-        <v>42.91</v>
+        <v>44.54</v>
       </c>
       <c r="L16" t="n">
-        <v>49.23</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>81.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.07</v>
+        <v>-2.04</v>
       </c>
       <c r="L17" t="n">
-        <v>81.95</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>51.83</v>
+        <v>54.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-47.16</v>
+        <v>-49.8</v>
       </c>
       <c r="L18" t="n">
-        <v>70.06999999999999</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.76</v>
+        <v>-0.79</v>
       </c>
       <c r="K19" t="n">
-        <v>-73.68000000000001</v>
+        <v>-77.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>73.68000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.32</v>
+        <v>-16.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-95.12</v>
+        <v>-104.31</v>
       </c>
       <c r="L20" t="n">
-        <v>96.34</v>
+        <v>105.65</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>94.04000000000001</v>
+        <v>103.32</v>
       </c>
       <c r="K21" t="n">
-        <v>7.22</v>
+        <v>7.93</v>
       </c>
       <c r="L21" t="n">
-        <v>94.31999999999999</v>
+        <v>103.62</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>85.66</v>
+        <v>96.31</v>
       </c>
       <c r="K22" t="n">
-        <v>-31.71</v>
+        <v>-35.65</v>
       </c>
       <c r="L22" t="n">
-        <v>91.34</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-126.66</v>
+        <v>-139.05</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.75</v>
+        <v>-16.19</v>
       </c>
       <c r="L23" t="n">
-        <v>127.51</v>
+        <v>139.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>14.96</v>
+        <v>16.51</v>
       </c>
       <c r="K24" t="n">
-        <v>129.54</v>
+        <v>143.02</v>
       </c>
       <c r="L24" t="n">
-        <v>130.4</v>
+        <v>143.97</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>62.74</v>
+        <v>75.63</v>
       </c>
       <c r="K25" t="n">
-        <v>65.28</v>
+        <v>78.7</v>
       </c>
       <c r="L25" t="n">
-        <v>90.54000000000001</v>
+        <v>109.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>194.13</v>
+        <v>220.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-56.23</v>
+        <v>-63.78</v>
       </c>
       <c r="L26" t="n">
-        <v>202.11</v>
+        <v>229.25</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>79.45999999999999</v>
+        <v>102.12</v>
       </c>
       <c r="K27" t="n">
-        <v>14.09</v>
+        <v>18.11</v>
       </c>
       <c r="L27" t="n">
-        <v>80.7</v>
+        <v>103.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>63.2</v>
+        <v>81.38</v>
       </c>
       <c r="K28" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="L28" t="n">
-        <v>63.22</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>62.94</v>
+        <v>62.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.55</v>
+        <v>-30.22</v>
       </c>
       <c r="L29" t="n">
-        <v>69.95999999999999</v>
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-40.63</v>
+        <v>-39.94</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.07</v>
+        <v>-39.38</v>
       </c>
       <c r="L30" t="n">
-        <v>57.06</v>
+        <v>56.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.130000000000001</v>
+        <v>-7.76</v>
       </c>
       <c r="K31" t="n">
-        <v>82.81</v>
+        <v>79.08</v>
       </c>
       <c r="L31" t="n">
-        <v>83.2</v>
+        <v>79.45999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-48.91</v>
+        <v>-51.06</v>
       </c>
       <c r="K32" t="n">
-        <v>-49.94</v>
+        <v>-52.14</v>
       </c>
       <c r="L32" t="n">
-        <v>69.91</v>
+        <v>72.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-60.73</v>
+        <v>-65.66</v>
       </c>
       <c r="K33" t="n">
-        <v>4.29</v>
+        <v>4.64</v>
       </c>
       <c r="L33" t="n">
-        <v>60.88</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>54.12</v>
+        <v>60.84</v>
       </c>
       <c r="K34" t="n">
-        <v>7.69</v>
+        <v>8.65</v>
       </c>
       <c r="L34" t="n">
-        <v>54.66</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>111.03</v>
+        <v>118.35</v>
       </c>
       <c r="K35" t="n">
-        <v>-28.31</v>
+        <v>-30.18</v>
       </c>
       <c r="L35" t="n">
-        <v>114.58</v>
+        <v>122.14</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-47.92</v>
+        <v>-56.26</v>
       </c>
       <c r="K36" t="n">
-        <v>-60.35</v>
+        <v>-70.84999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>77.06999999999999</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>95.56</v>
+        <v>102.39</v>
       </c>
       <c r="K37" t="n">
-        <v>-77.28</v>
+        <v>-82.79000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>122.9</v>
+        <v>131.67</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-70.5</v>
+        <v>-77.25</v>
       </c>
       <c r="K38" t="n">
-        <v>124.25</v>
+        <v>136.15</v>
       </c>
       <c r="L38" t="n">
-        <v>142.85</v>
+        <v>156.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-116.43</v>
+        <v>-115.01</v>
       </c>
       <c r="K39" t="n">
-        <v>-205.15</v>
+        <v>-202.64</v>
       </c>
       <c r="L39" t="n">
-        <v>235.89</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="K40" t="n">
-        <v>108.27</v>
+        <v>130.73</v>
       </c>
       <c r="L40" t="n">
-        <v>108.31</v>
+        <v>130.77</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-147.89</v>
+        <v>-187.02</v>
       </c>
       <c r="K41" t="n">
-        <v>-91.58</v>
+        <v>-115.8</v>
       </c>
       <c r="L41" t="n">
-        <v>173.95</v>
+        <v>219.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>179.58</v>
+        <v>204.27</v>
       </c>
       <c r="K42" t="n">
-        <v>-122.8</v>
+        <v>-139.68</v>
       </c>
       <c r="L42" t="n">
-        <v>217.55</v>
+        <v>247.46</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>302.88</v>
+        <v>318.49</v>
       </c>
       <c r="K43" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="L43" t="n">
-        <v>302.89</v>
+        <v>318.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-66.19</v>
+        <v>-63.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-56.25</v>
+        <v>-54.21</v>
       </c>
       <c r="L44" t="n">
-        <v>86.86</v>
+        <v>83.70999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.37</v>
+        <v>-5.96</v>
       </c>
       <c r="K45" t="n">
-        <v>35.76</v>
+        <v>39.71</v>
       </c>
       <c r="L45" t="n">
-        <v>36.16</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>39.39</v>
+        <v>41.76</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.71</v>
+        <v>-0.75</v>
       </c>
       <c r="L46" t="n">
-        <v>39.39</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-19.04</v>
+        <v>-20.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-57.54</v>
+        <v>-61.57</v>
       </c>
       <c r="L47" t="n">
-        <v>60.61</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-33.39</v>
+        <v>-34.85</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.33</v>
+        <v>-74.44</v>
       </c>
       <c r="L48" t="n">
-        <v>78.76000000000001</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-29.48</v>
+        <v>-29.32</v>
       </c>
       <c r="K49" t="n">
-        <v>95.23</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>99.68000000000001</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>66.01000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.86</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>89.11</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-36.47</v>
+        <v>-43.89</v>
       </c>
       <c r="K51" t="n">
-        <v>-9.41</v>
+        <v>-11.32</v>
       </c>
       <c r="L51" t="n">
-        <v>37.67</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.05</v>
+        <v>-25.17</v>
       </c>
       <c r="K52" t="n">
-        <v>115.15</v>
+        <v>120.48</v>
       </c>
       <c r="L52" t="n">
-        <v>117.64</v>
+        <v>123.08</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>146.05</v>
+        <v>155.62</v>
       </c>
       <c r="K53" t="n">
-        <v>-36.11</v>
+        <v>-38.47</v>
       </c>
       <c r="L53" t="n">
-        <v>150.45</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>9.15</v>
+        <v>10.91</v>
       </c>
       <c r="K54" t="n">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="L54" t="n">
-        <v>9.42</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-117.89</v>
+        <v>-135.76</v>
       </c>
       <c r="K55" t="n">
-        <v>-43.39</v>
+        <v>-49.96</v>
       </c>
       <c r="L55" t="n">
-        <v>125.62</v>
+        <v>144.66</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-222.17</v>
+        <v>-235.01</v>
       </c>
       <c r="K56" t="n">
-        <v>-206.23</v>
+        <v>-218.16</v>
       </c>
       <c r="L56" t="n">
-        <v>303.13</v>
+        <v>320.66</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-208</v>
+        <v>-233.07</v>
       </c>
       <c r="K57" t="n">
-        <v>-62.6</v>
+        <v>-70.15000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>217.22</v>
+        <v>243.4</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>148.11</v>
+        <v>178.24</v>
       </c>
       <c r="K58" t="n">
-        <v>87.68000000000001</v>
+        <v>105.52</v>
       </c>
       <c r="L58" t="n">
-        <v>172.12</v>
+        <v>207.13</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.23</v>
+        <v>-45.22</v>
       </c>
       <c r="K59" t="n">
-        <v>-32.34</v>
+        <v>-33.83</v>
       </c>
       <c r="L59" t="n">
-        <v>53.98</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-32.04</v>
+        <v>-36.2</v>
       </c>
       <c r="K60" t="n">
-        <v>-26.9</v>
+        <v>-30.39</v>
       </c>
       <c r="L60" t="n">
-        <v>41.83</v>
+        <v>47.27</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-65.16</v>
+        <v>-62.83</v>
       </c>
       <c r="K61" t="n">
-        <v>34.05</v>
+        <v>32.84</v>
       </c>
       <c r="L61" t="n">
-        <v>73.52</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-59.56</v>
+        <v>-63.12</v>
       </c>
       <c r="K62" t="n">
-        <v>4.08</v>
+        <v>4.32</v>
       </c>
       <c r="L62" t="n">
-        <v>59.69</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>74.5</v>
+        <v>77.23</v>
       </c>
       <c r="K63" t="n">
-        <v>43.24</v>
+        <v>44.82</v>
       </c>
       <c r="L63" t="n">
-        <v>86.14</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>23.54</v>
+        <v>25.03</v>
       </c>
       <c r="K64" t="n">
-        <v>64.79000000000001</v>
+        <v>68.87</v>
       </c>
       <c r="L64" t="n">
-        <v>68.94</v>
+        <v>73.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>48.75</v>
+        <v>51.11</v>
       </c>
       <c r="K65" t="n">
-        <v>-109.19</v>
+        <v>-114.48</v>
       </c>
       <c r="L65" t="n">
-        <v>119.58</v>
+        <v>125.37</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-72.66</v>
+        <v>-82.64</v>
       </c>
       <c r="K66" t="n">
-        <v>59.98</v>
+        <v>68.22</v>
       </c>
       <c r="L66" t="n">
-        <v>94.22</v>
+        <v>107.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>13.01</v>
+        <v>14.75</v>
       </c>
       <c r="K67" t="n">
-        <v>97.48999999999999</v>
+        <v>110.55</v>
       </c>
       <c r="L67" t="n">
-        <v>98.36</v>
+        <v>111.53</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>51.52</v>
+        <v>56.52</v>
       </c>
       <c r="K68" t="n">
-        <v>-151.22</v>
+        <v>-165.9</v>
       </c>
       <c r="L68" t="n">
-        <v>159.75</v>
+        <v>175.26</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>35.07</v>
+        <v>39.56</v>
       </c>
       <c r="K69" t="n">
-        <v>155.54</v>
+        <v>175.49</v>
       </c>
       <c r="L69" t="n">
-        <v>159.45</v>
+        <v>179.89</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-147.05</v>
+        <v>-159.75</v>
       </c>
       <c r="K70" t="n">
-        <v>98.14</v>
+        <v>106.62</v>
       </c>
       <c r="L70" t="n">
-        <v>176.79</v>
+        <v>192.06</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-98.76000000000001</v>
+        <v>-130.02</v>
       </c>
       <c r="K71" t="n">
-        <v>-53.92</v>
+        <v>-70.98999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>112.52</v>
+        <v>148.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-7.75</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>-34.75</v>
+        <v>-44.34</v>
       </c>
       <c r="L72" t="n">
-        <v>35.61</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>120.35</v>
+        <v>150.25</v>
       </c>
       <c r="K73" t="n">
-        <v>72.34</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>140.42</v>
+        <v>175.31</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.67</v>
+        <v>-23.04</v>
       </c>
       <c r="K74" t="n">
-        <v>-49.08</v>
+        <v>-52.19</v>
       </c>
       <c r="L74" t="n">
-        <v>53.65</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>92.95999999999999</v>
+        <v>88.88</v>
       </c>
       <c r="K75" t="n">
-        <v>13.57</v>
+        <v>12.97</v>
       </c>
       <c r="L75" t="n">
-        <v>93.95</v>
+        <v>89.81999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>4.72</v>
+        <v>5.42</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.1</v>
+        <v>-54.09</v>
       </c>
       <c r="L76" t="n">
-        <v>47.33</v>
+        <v>54.36</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.81</v>
+        <v>-70.2</v>
       </c>
       <c r="K77" t="n">
-        <v>-29.39</v>
+        <v>-31.35</v>
       </c>
       <c r="L77" t="n">
-        <v>72.08</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>74.09999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K78" t="n">
-        <v>23.27</v>
+        <v>24.3</v>
       </c>
       <c r="L78" t="n">
-        <v>77.67</v>
+        <v>81.11</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>76.91</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>33.07</v>
+        <v>33.86</v>
       </c>
       <c r="L79" t="n">
-        <v>83.72</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-112.22</v>
+        <v>-119.71</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.29</v>
+        <v>-64.31</v>
       </c>
       <c r="L80" t="n">
-        <v>127.39</v>
+        <v>135.89</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>69.33</v>
+        <v>73.92</v>
       </c>
       <c r="K81" t="n">
-        <v>105.2</v>
+        <v>112.16</v>
       </c>
       <c r="L81" t="n">
-        <v>125.99</v>
+        <v>134.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-74.18000000000001</v>
+        <v>-77.61</v>
       </c>
       <c r="K82" t="n">
-        <v>99.52</v>
+        <v>104.12</v>
       </c>
       <c r="L82" t="n">
-        <v>124.12</v>
+        <v>129.86</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-42.69</v>
+        <v>-50.19</v>
       </c>
       <c r="K83" t="n">
-        <v>120.13</v>
+        <v>141.23</v>
       </c>
       <c r="L83" t="n">
-        <v>127.49</v>
+        <v>149.88</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-157.36</v>
+        <v>-169.66</v>
       </c>
       <c r="K84" t="n">
-        <v>91.22</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>181.89</v>
+        <v>196.11</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>116.89</v>
+        <v>133.91</v>
       </c>
       <c r="K85" t="n">
-        <v>-47.11</v>
+        <v>-53.96</v>
       </c>
       <c r="L85" t="n">
-        <v>126.03</v>
+        <v>144.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>17</v>
       </c>
       <c r="J86" t="n">
-        <v>184.66</v>
+        <v>204.45</v>
       </c>
       <c r="K86" t="n">
-        <v>-185.56</v>
+        <v>-205.45</v>
       </c>
       <c r="L86" t="n">
-        <v>261.79</v>
+        <v>289.85</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>158.84</v>
+        <v>192.15</v>
       </c>
       <c r="K87" t="n">
-        <v>-109.4</v>
+        <v>-132.35</v>
       </c>
       <c r="L87" t="n">
-        <v>192.87</v>
+        <v>233.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-45.06</v>
+        <v>-58.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-24.27</v>
+        <v>-31.5</v>
       </c>
       <c r="L88" t="n">
-        <v>51.18</v>
+        <v>66.44</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-10.xlsx
+++ b/output/2025-09-10.xlsx
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-63.79</v>
+        <v>-65.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-54.21</v>
+        <v>-55.73</v>
       </c>
       <c r="L44" t="n">
-        <v>83.70999999999999</v>
+        <v>86.06</v>
       </c>
     </row>
     <row r="45">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>77.23</v>
+        <v>78.77</v>
       </c>
       <c r="K63" t="n">
-        <v>44.82</v>
+        <v>45.72</v>
       </c>
       <c r="L63" t="n">
-        <v>89.29000000000001</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="64">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.09</v>
+        <v>-54.4</v>
       </c>
       <c r="L76" t="n">
-        <v>54.36</v>
+        <v>54.67</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-70.2</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-31.35</v>
+        <v>-31.39</v>
       </c>
       <c r="L77" t="n">
-        <v>76.88</v>
+        <v>76.98</v>
       </c>
     </row>
     <row r="78">
